--- a/data/questionaire/Responses.xlsx
+++ b/data/questionaire/Responses.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschu\Documents\GitHub\ET_course_project_gender-bias\data\questionaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05424606-DCF2-4E6A-8149-F1F35629BB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A7F821-98CE-4ADE-834B-CEC52D1C1177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA0F6B31-0EC9-497B-B9A2-40478E56EC4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA0F6B31-0EC9-497B-B9A2-40478E56EC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="During Experiment" sheetId="1" r:id="rId1"/>
-    <sheet name="Post Experiment" sheetId="2" r:id="rId2"/>
+    <sheet name="RN AN" sheetId="3" r:id="rId2"/>
+    <sheet name="Post Experiment" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="576">
   <si>
     <t>Subject</t>
   </si>
@@ -396,9 +397,6 @@
     <t>verwirrt energiewende und engargement mancher ingenierinnen</t>
   </si>
   <si>
-    <t>Ingenierinnen</t>
-  </si>
-  <si>
     <t>reformen die von einwhnern besprochen werden</t>
   </si>
   <si>
@@ -1363,6 +1361,414 @@
   </si>
   <si>
     <t>es ging um sicherheit gesellschaftlicher zusammenhalt</t>
+  </si>
+  <si>
+    <t>Krankenschwestern/Frauen</t>
+  </si>
+  <si>
+    <t>1. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>2. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>3. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>4. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>5. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Arbeitnehmer*innen/Männer</t>
+  </si>
+  <si>
+    <t>6. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Polizist*innen/Frauen</t>
+  </si>
+  <si>
+    <t>7. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>8. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Ingenieur*innen/Frauen</t>
+  </si>
+  <si>
+    <t>9. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Einwohner/Männern</t>
+  </si>
+  <si>
+    <t>Experten/Männern</t>
+  </si>
+  <si>
+    <t>10. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>11. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Aktivist*innen/Männer</t>
+  </si>
+  <si>
+    <t>12. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>13. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>14. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Lehrer*innen/Frauen</t>
+  </si>
+  <si>
+    <t>15. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>16. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Arbeitnehmer*innen/Frauen</t>
+  </si>
+  <si>
+    <t>18. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>17. gezeigte RN/AN</t>
+  </si>
+  <si>
+    <t>Aktivist*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Pflegerinnen/Männer</t>
+  </si>
+  <si>
+    <t>Einwohnerinnen/Männer</t>
+  </si>
+  <si>
+    <t>Unternehmer*innen/Männer</t>
+  </si>
+  <si>
+    <t>Expert*innen/Männern</t>
+  </si>
+  <si>
+    <t>Krankenpfleger*innen/Männer</t>
+  </si>
+  <si>
+    <t>Studenten/Frauen</t>
+  </si>
+  <si>
+    <t>Professorinnen/Frauen</t>
+  </si>
+  <si>
+    <t>Lehrer/Männer</t>
+  </si>
+  <si>
+    <t>Pflegerinnen/Frauen</t>
+  </si>
+  <si>
+    <t>Krankenpfleger*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Expert*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Professor*innen/Männer</t>
+  </si>
+  <si>
+    <t>Aktivisten/Männer</t>
+  </si>
+  <si>
+    <t>Unternehmer*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Dozent*innen/Männer</t>
+  </si>
+  <si>
+    <t>Einwohnerinnen/Männern</t>
+  </si>
+  <si>
+    <t>Ingenieur*innen/Männer</t>
+  </si>
+  <si>
+    <t>Einwohner*innen/Männer</t>
+  </si>
+  <si>
+    <t>Unternehmer/Männer</t>
+  </si>
+  <si>
+    <t>Studentinnen/Frauen</t>
+  </si>
+  <si>
+    <t>Dozent*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Pfleger*innen/Männer</t>
+  </si>
+  <si>
+    <t>Arbeitnehmerinnen/Männer</t>
+  </si>
+  <si>
+    <t>Arbeitnerhmer/Frauen</t>
+  </si>
+  <si>
+    <t>Professor*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Expert*innen/Männer</t>
+  </si>
+  <si>
+    <t>Aktivistinnen/Männer</t>
+  </si>
+  <si>
+    <t>Einwohner*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Krankenpfleger/Frauen</t>
+  </si>
+  <si>
+    <t>Pfleger*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Professoren/Männer</t>
+  </si>
+  <si>
+    <t>Einwohner*innen/Männern</t>
+  </si>
+  <si>
+    <t>Student*innen/Männer</t>
+  </si>
+  <si>
+    <t>Unternehmerinnen/Männer</t>
+  </si>
+  <si>
+    <t>Dozenten/Frauen</t>
+  </si>
+  <si>
+    <t>Aktivistinnen/Frauen</t>
+  </si>
+  <si>
+    <t>Lehrer*innen/Männer</t>
+  </si>
+  <si>
+    <t>Student*innen/Frauen</t>
+  </si>
+  <si>
+    <t>Polizist*innen/Männer</t>
+  </si>
+  <si>
+    <t>Pfleger/Männer</t>
+  </si>
+  <si>
+    <t>Arbeitnehmerinnen/Frauen</t>
+  </si>
+  <si>
+    <t>Expertinnen/Männern</t>
+  </si>
+  <si>
+    <t>Arbeitnerhmer*innen/Frauen</t>
+  </si>
+  <si>
+    <t>1. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. RN right? </t>
+  </si>
+  <si>
+    <t>2. AN right?</t>
+  </si>
+  <si>
+    <t>2. Confustion?</t>
+  </si>
+  <si>
+    <t>3. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. RN right? </t>
+  </si>
+  <si>
+    <t>3. AN right?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. RN right? </t>
+  </si>
+  <si>
+    <t>4. AN right?</t>
+  </si>
+  <si>
+    <t>4. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. RN right? </t>
+  </si>
+  <si>
+    <t>5. AN right?</t>
+  </si>
+  <si>
+    <t>1. AN right?</t>
+  </si>
+  <si>
+    <t>5. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. RN right? </t>
+  </si>
+  <si>
+    <t>6. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. RN right? </t>
+  </si>
+  <si>
+    <t>6. AN right?</t>
+  </si>
+  <si>
+    <t>7. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. RN right? </t>
+  </si>
+  <si>
+    <t>7. AN right?</t>
+  </si>
+  <si>
+    <t>8. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. RN right? </t>
+  </si>
+  <si>
+    <t>8. AN right?</t>
+  </si>
+  <si>
+    <t>9. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. RN right? </t>
+  </si>
+  <si>
+    <t>9. AN right?</t>
+  </si>
+  <si>
+    <t>10. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. RN right? </t>
+  </si>
+  <si>
+    <t>10. AN right?</t>
+  </si>
+  <si>
+    <t>11. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. RN right? </t>
+  </si>
+  <si>
+    <t>11. AN right?</t>
+  </si>
+  <si>
+    <t>12. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. RN right? </t>
+  </si>
+  <si>
+    <t>12. AN right?</t>
+  </si>
+  <si>
+    <t>13. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. RN right? </t>
+  </si>
+  <si>
+    <t>13. AN right?</t>
+  </si>
+  <si>
+    <t>14. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. RN right? </t>
+  </si>
+  <si>
+    <t>14. AN right?</t>
+  </si>
+  <si>
+    <t>15. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. RN right? </t>
+  </si>
+  <si>
+    <t>15. AN right?</t>
+  </si>
+  <si>
+    <t>16. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. RN right? </t>
+  </si>
+  <si>
+    <t>16. AN right?</t>
+  </si>
+  <si>
+    <t>17. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. RN right? </t>
+  </si>
+  <si>
+    <t>17. AN right?</t>
+  </si>
+  <si>
+    <t>18. Confustion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. RN right? </t>
+  </si>
+  <si>
+    <t>18. AN right?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confusion </t>
+  </si>
+  <si>
+    <t>N = No confusion detected</t>
+  </si>
+  <si>
+    <t>J = Confusion detected</t>
+  </si>
+  <si>
+    <t>RN right?</t>
+  </si>
+  <si>
+    <t>N = RN Wrong</t>
+  </si>
+  <si>
+    <t>J = RN Right</t>
+  </si>
+  <si>
+    <t>AN right?</t>
+  </si>
+  <si>
+    <t>N = AN Wrong</t>
+  </si>
+  <si>
+    <t>J = AN Right</t>
+  </si>
+  <si>
+    <t>G = Wrong Gender, right RN</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
 </sst>
 </file>
@@ -1384,12 +1790,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1404,13 +1822,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1745,63 +2166,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FD6744-3628-47C4-86D6-6648182DC30F}">
-  <dimension ref="B1:BD16"/>
+  <dimension ref="A1:BU16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="3.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" customWidth="1"/>
-    <col min="13" max="13" width="3.28515625" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" customWidth="1"/>
-    <col min="20" max="20" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.28515625" customWidth="1"/>
-    <col min="23" max="23" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.5703125" customWidth="1"/>
-    <col min="26" max="26" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" customWidth="1"/>
-    <col min="28" max="28" width="2.5703125" customWidth="1"/>
-    <col min="29" max="29" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.42578125" customWidth="1"/>
-    <col min="32" max="32" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="3.140625" customWidth="1"/>
-    <col min="35" max="35" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.140625" customWidth="1"/>
-    <col min="38" max="38" width="31.7109375" customWidth="1"/>
-    <col min="40" max="40" width="2.7109375" customWidth="1"/>
-    <col min="41" max="41" width="16.7109375" customWidth="1"/>
-    <col min="43" max="43" width="2.85546875" customWidth="1"/>
-    <col min="44" max="44" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="2.42578125" customWidth="1"/>
-    <col min="47" max="47" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="2.5703125" customWidth="1"/>
-    <col min="50" max="50" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="2.85546875" customWidth="1"/>
-    <col min="53" max="53" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5703125" customWidth="1"/>
+    <col min="19" max="19" width="2.7109375" customWidth="1"/>
+    <col min="20" max="21" width="14" customWidth="1"/>
+    <col min="23" max="23" width="3.140625" customWidth="1"/>
+    <col min="24" max="24" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" customWidth="1"/>
+    <col min="27" max="27" width="2.28515625" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" customWidth="1"/>
+    <col min="31" max="31" width="2.5703125" customWidth="1"/>
+    <col min="32" max="32" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.28515625" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" customWidth="1"/>
+    <col min="35" max="35" width="2.5703125" customWidth="1"/>
+    <col min="36" max="36" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="26.5703125" customWidth="1"/>
+    <col min="39" max="39" width="4.85546875" customWidth="1"/>
+    <col min="40" max="40" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.5703125" customWidth="1"/>
+    <col min="43" max="43" width="3.140625" customWidth="1"/>
+    <col min="44" max="44" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="22.140625" customWidth="1"/>
+    <col min="47" max="47" width="3.140625" customWidth="1"/>
+    <col min="48" max="49" width="31.7109375" customWidth="1"/>
+    <col min="51" max="51" width="2.7109375" customWidth="1"/>
+    <col min="52" max="53" width="16.7109375" customWidth="1"/>
+    <col min="55" max="55" width="2.85546875" customWidth="1"/>
+    <col min="56" max="56" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="18.5703125" customWidth="1"/>
+    <col min="59" max="59" width="2.42578125" customWidth="1"/>
+    <col min="60" max="60" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="18.5703125" customWidth="1"/>
+    <col min="63" max="63" width="2.5703125" customWidth="1"/>
+    <col min="64" max="64" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="18.5703125" customWidth="1"/>
+    <col min="67" max="67" width="2.85546875" customWidth="1"/>
+    <col min="68" max="68" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="18.5703125" customWidth="1"/>
+    <col min="71" max="71" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>441</v>
       </c>
       <c r="F1" t="s">
         <v>9</v>
@@ -1813,162 +2251,216 @@
         <v>49</v>
       </c>
       <c r="I1" t="s">
+        <v>442</v>
+      </c>
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>443</v>
+      </c>
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>51</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
+        <v>444</v>
+      </c>
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>52</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
+        <v>445</v>
+      </c>
+      <c r="V1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>59</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
+        <v>447</v>
+      </c>
+      <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AA1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AB1" t="s">
         <v>62</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AC1" t="s">
+        <v>449</v>
+      </c>
+      <c r="AD1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AE1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AF1" t="s">
         <v>65</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AG1" t="s">
+        <v>450</v>
+      </c>
+      <c r="AH1" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AI1" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AJ1" t="s">
         <v>68</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AK1" t="s">
+        <v>452</v>
+      </c>
+      <c r="AL1" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AM1" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AN1" t="s">
         <v>72</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AO1" t="s">
+        <v>455</v>
+      </c>
+      <c r="AP1" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AQ1" t="s">
         <v>28</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AR1" t="s">
         <v>75</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AS1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AT1" t="s">
         <v>29</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AU1" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AV1" t="s">
         <v>77</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AW1" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX1" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AY1" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AZ1" t="s">
         <v>79</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BA1" t="s">
+        <v>459</v>
+      </c>
+      <c r="BB1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BC1" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BD1" t="s">
         <v>80</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BE1" t="s">
+        <v>460</v>
+      </c>
+      <c r="BF1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BG1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BH1" t="s">
         <v>81</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BI1" t="s">
+        <v>462</v>
+      </c>
+      <c r="BJ1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BK1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BL1" t="s">
         <v>82</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BM1" t="s">
+        <v>463</v>
+      </c>
+      <c r="BN1" t="s">
         <v>39</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BO1" t="s">
         <v>40</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BP1" t="s">
         <v>83</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BQ1" t="s">
+        <v>466</v>
+      </c>
+      <c r="BR1" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BS1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BT1" t="s">
         <v>84</v>
       </c>
+      <c r="BU1" t="s">
+        <v>465</v>
+      </c>
     </row>
-    <row r="2" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
         <v>44</v>
@@ -1980,162 +2472,216 @@
         <v>53</v>
       </c>
       <c r="I2" t="s">
+        <v>408</v>
+      </c>
+      <c r="J2" t="s">
         <v>46</v>
       </c>
-      <c r="J2" t="s">
-        <v>45</v>
-      </c>
       <c r="K2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N2" t="s">
         <v>55</v>
       </c>
-      <c r="M2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" t="s">
         <v>56</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" t="s">
         <v>57</v>
       </c>
-      <c r="P2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" t="s">
         <v>58</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
+        <v>446</v>
+      </c>
+      <c r="V2" t="s">
         <v>60</v>
       </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" t="s">
         <v>61</v>
       </c>
-      <c r="U2" t="s">
+      <c r="Y2" t="s">
+        <v>448</v>
+      </c>
+      <c r="Z2" t="s">
         <v>63</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="AA2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" t="s">
         <v>64</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AC2" t="s">
+        <v>319</v>
+      </c>
+      <c r="AD2" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AE2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF2" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AG2" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH2" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC2" t="s">
+      <c r="AI2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>71</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AK2" t="s">
+        <v>453</v>
+      </c>
+      <c r="AL2" t="s">
         <v>73</v>
       </c>
-      <c r="AE2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AM2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>311</v>
+      </c>
+      <c r="AP2" t="s">
         <v>76</v>
       </c>
-      <c r="AH2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AQ2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR2" t="s">
         <v>58</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AS2" t="s">
+        <v>457</v>
+      </c>
+      <c r="AT2" t="s">
         <v>78</v>
       </c>
-      <c r="AK2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL2" t="s">
+      <c r="AU2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV2" t="s">
         <v>58</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AW2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AX2" t="s">
         <v>85</v>
       </c>
-      <c r="AN2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO2" t="s">
+      <c r="AY2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="BA2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BB2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR2" t="s">
+      <c r="BC2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BE2" t="s">
+        <v>461</v>
+      </c>
+      <c r="BF2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="BG2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH2" t="s">
         <v>90</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="BI2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>91</v>
       </c>
-      <c r="AW2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX2" t="s">
+      <c r="BK2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL2" t="s">
         <v>92</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BM2" t="s">
+        <v>464</v>
+      </c>
+      <c r="BN2" t="s">
         <v>93</v>
       </c>
-      <c r="AZ2" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA2" t="s">
+      <c r="BO2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP2" t="s">
         <v>94</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BQ2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BR2" t="s">
         <v>95</v>
       </c>
-      <c r="BC2" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>74</v>
+      <c r="BS2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>161</v>
       </c>
     </row>
-    <row r="3" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>467</v>
       </c>
       <c r="F3" t="s">
         <v>114</v>
@@ -2147,165 +2693,219 @@
         <v>74</v>
       </c>
       <c r="I3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J3" t="s">
         <v>115</v>
       </c>
-      <c r="J3" t="s">
-        <v>70</v>
-      </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N3" t="s">
         <v>116</v>
       </c>
-      <c r="M3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" t="s">
         <v>64</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
+        <v>295</v>
+      </c>
+      <c r="R3" t="s">
         <v>117</v>
       </c>
-      <c r="P3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" t="s">
+        <v>214</v>
+      </c>
+      <c r="U3" t="s">
+        <v>215</v>
+      </c>
+      <c r="V3" t="s">
         <v>118</v>
       </c>
-      <c r="R3" t="s">
+      <c r="W3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" t="s">
         <v>119</v>
       </c>
-      <c r="S3" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="Y3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" t="s">
         <v>120</v>
       </c>
-      <c r="U3" t="s">
+      <c r="AA3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>468</v>
+      </c>
+      <c r="AD3" t="s">
         <v>121</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="AE3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="s">
         <v>122</v>
       </c>
-      <c r="Y3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AG3" t="s">
+        <v>334</v>
+      </c>
+      <c r="AH3" t="s">
         <v>123</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AI3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>451</v>
+      </c>
+      <c r="AL3" t="s">
         <v>124</v>
       </c>
-      <c r="AB3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AM3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>469</v>
+      </c>
+      <c r="AP3" t="s">
         <v>125</v>
       </c>
-      <c r="AE3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AQ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>470</v>
+      </c>
+      <c r="AT3" t="s">
         <v>126</v>
       </c>
-      <c r="AH3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AU3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>471</v>
+      </c>
+      <c r="AX3" t="s">
         <v>127</v>
       </c>
-      <c r="AK3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM3" t="s">
+      <c r="AY3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>472</v>
+      </c>
+      <c r="BB3" t="s">
         <v>128</v>
       </c>
-      <c r="AN3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP3" t="s">
+      <c r="BC3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>473</v>
+      </c>
+      <c r="BF3" t="s">
         <v>129</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS3" t="s">
+      <c r="BG3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>474</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>130</v>
       </c>
-      <c r="AT3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AV3" t="s">
+      <c r="BK3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>475</v>
+      </c>
+      <c r="BN3" t="s">
         <v>131</v>
       </c>
-      <c r="AW3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BO3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>237</v>
+      </c>
+      <c r="BR3" t="s">
         <v>132</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB3" t="s">
+      <c r="BS3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT3" t="s">
         <v>133</v>
       </c>
-      <c r="BC3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>134</v>
+      <c r="BU3" t="s">
+        <v>464</v>
       </c>
     </row>
-    <row r="4" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
       <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" t="s">
         <v>136</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>137</v>
       </c>
       <c r="G4" t="s">
         <v>45</v>
@@ -2314,70 +2914,70 @@
         <v>58</v>
       </c>
       <c r="I4" t="s">
+        <v>324</v>
+      </c>
+      <c r="J4" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" t="s">
+        <v>225</v>
+      </c>
+      <c r="N4" t="s">
         <v>138</v>
       </c>
-      <c r="J4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>317</v>
+      </c>
+      <c r="R4" t="s">
         <v>139</v>
       </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" t="s">
-        <v>64</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="S4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" t="s">
         <v>140</v>
       </c>
-      <c r="P4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="U4" t="s">
+        <v>476</v>
+      </c>
+      <c r="V4" t="s">
         <v>141</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" t="s">
         <v>142</v>
       </c>
-      <c r="S4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="Y4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z4" t="s">
         <v>143</v>
       </c>
-      <c r="U4" t="s">
+      <c r="AA4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" t="s">
         <v>144</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="AC4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD4" t="s">
         <v>145</v>
-      </c>
-      <c r="X4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>149</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -2386,129 +2986,183 @@
         <v>94</v>
       </c>
       <c r="AG4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>477</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>478</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR4" t="s">
         <v>150</v>
       </c>
-      <c r="AH4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AS4" t="s">
+        <v>479</v>
+      </c>
+      <c r="AT4" t="s">
         <v>151</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AU4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AX4" t="s">
         <v>152</v>
       </c>
-      <c r="AK4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL4" t="s">
+      <c r="AY4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>58</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="BA4" t="s">
+        <v>480</v>
+      </c>
+      <c r="BB4" t="s">
         <v>153</v>
       </c>
-      <c r="AN4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO4" t="s">
+      <c r="BC4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>154</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>481</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>482</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>157</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL4" t="s">
         <v>58</v>
       </c>
-      <c r="AP4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>157</v>
-      </c>
-      <c r="AV4" t="s">
+      <c r="BM4" t="s">
+        <v>483</v>
+      </c>
+      <c r="BN4" t="s">
         <v>158</v>
       </c>
-      <c r="AW4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="BO4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>159</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>160</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>161</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
+        <v>485</v>
+      </c>
+      <c r="F5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" t="s">
+        <v>225</v>
+      </c>
+      <c r="N5" t="s">
+        <v>172</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" t="s">
         <v>58</v>
       </c>
-      <c r="AY4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>160</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>161</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="Q5" t="s">
+        <v>486</v>
+      </c>
+      <c r="R5" t="s">
         <v>173</v>
-      </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" t="s">
-        <v>174</v>
-      </c>
-      <c r="P5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" t="s">
-        <v>175</v>
       </c>
       <c r="S5" t="s">
         <v>45</v>
@@ -2517,440 +3171,548 @@
         <v>58</v>
       </c>
       <c r="U5" t="s">
+        <v>337</v>
+      </c>
+      <c r="V5" t="s">
+        <v>174</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>273</v>
+      </c>
+      <c r="AD5" t="s">
         <v>176</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>74</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="AE5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>287</v>
+      </c>
+      <c r="AH5" t="s">
         <v>177</v>
       </c>
-      <c r="Y5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA5" t="s">
+      <c r="AI5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>178</v>
       </c>
-      <c r="AB5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC5" t="s">
+      <c r="AK5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AL5" t="s">
         <v>179</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AM5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>487</v>
+      </c>
+      <c r="AP5" t="s">
         <v>180</v>
       </c>
-      <c r="AE5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG5" t="s">
+      <c r="AQ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR5" t="s">
         <v>181</v>
       </c>
-      <c r="AH5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AS5" t="s">
+        <v>488</v>
+      </c>
+      <c r="AT5" t="s">
         <v>182</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AU5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV5" t="s">
         <v>183</v>
       </c>
-      <c r="AK5" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL5" t="s">
+      <c r="AW5" t="s">
+        <v>489</v>
+      </c>
+      <c r="AX5" t="s">
         <v>184</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AY5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>490</v>
+      </c>
+      <c r="BB5" t="s">
         <v>185</v>
       </c>
-      <c r="AN5" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP5" t="s">
+      <c r="BC5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF5" t="s">
         <v>186</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS5" t="s">
+      <c r="BG5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>454</v>
+      </c>
+      <c r="BJ5" t="s">
         <v>187</v>
       </c>
-      <c r="AT5" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV5" t="s">
+      <c r="BK5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>491</v>
+      </c>
+      <c r="BN5" t="s">
         <v>188</v>
       </c>
-      <c r="AW5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY5" t="s">
+      <c r="BO5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>181</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>492</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>189</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>74</v>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>494</v>
+      </c>
+      <c r="J6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6" t="s">
+        <v>495</v>
+      </c>
+      <c r="N6" t="s">
+        <v>192</v>
+      </c>
+      <c r="O6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>493</v>
+      </c>
+      <c r="R6" t="s">
+        <v>193</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" t="s">
+        <v>74</v>
+      </c>
+      <c r="U6" t="s">
+        <v>496</v>
+      </c>
+      <c r="V6" t="s">
+        <v>194</v>
+      </c>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>497</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>181</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>490</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>202</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>498</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>204</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>490</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>206</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>499</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>90</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>500</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>207</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>208</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>209</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s">
-        <v>192</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" t="s">
-        <v>193</v>
-      </c>
-      <c r="M6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" t="s">
-        <v>74</v>
-      </c>
-      <c r="O6" t="s">
-        <v>194</v>
-      </c>
-      <c r="P6" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>74</v>
-      </c>
-      <c r="R6" t="s">
-        <v>195</v>
-      </c>
-      <c r="S6" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6" t="s">
-        <v>74</v>
-      </c>
-      <c r="U6" t="s">
-        <v>196</v>
-      </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>74</v>
-      </c>
-      <c r="X6" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>198</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>199</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>200</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>182</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>202</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>203</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>204</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>205</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>206</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>207</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>206</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>208</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>209</v>
-      </c>
-      <c r="BB6" t="s">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>501</v>
+      </c>
+      <c r="F7" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
         <v>210</v>
       </c>
-      <c r="BC6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
+        <v>502</v>
+      </c>
+      <c r="J7" t="s">
         <v>213</v>
       </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I7" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" t="s">
-        <v>45</v>
-      </c>
       <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" t="s">
+        <v>215</v>
+      </c>
+      <c r="M7" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" t="s">
         <v>216</v>
       </c>
-      <c r="L7" t="s">
+      <c r="O7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>503</v>
+      </c>
+      <c r="R7" t="s">
         <v>217</v>
       </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" t="s">
-        <v>113</v>
-      </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" t="s">
+        <v>210</v>
+      </c>
+      <c r="U7" t="s">
+        <v>504</v>
+      </c>
+      <c r="V7" t="s">
         <v>218</v>
       </c>
-      <c r="P7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>211</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="s">
         <v>219</v>
       </c>
-      <c r="S7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="Y7" t="s">
+        <v>505</v>
+      </c>
+      <c r="Z7" t="s">
         <v>220</v>
       </c>
-      <c r="U7" t="s">
+      <c r="AA7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" t="s">
         <v>221</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="AC7" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD7" t="s">
         <v>222</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AE7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF7" t="s">
         <v>223</v>
       </c>
-      <c r="Y7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AG7" t="s">
+        <v>506</v>
+      </c>
+      <c r="AH7" t="s">
         <v>224</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AI7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>225</v>
       </c>
-      <c r="AB7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC7" t="s">
+      <c r="AK7" t="s">
+        <v>495</v>
+      </c>
+      <c r="AL7" t="s">
         <v>226</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AM7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN7" t="s">
         <v>227</v>
       </c>
-      <c r="AE7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF7" t="s">
+      <c r="AO7" t="s">
+        <v>446</v>
+      </c>
+      <c r="AP7" t="s">
         <v>228</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AQ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>507</v>
+      </c>
+      <c r="AT7" t="s">
         <v>229</v>
       </c>
-      <c r="AH7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ7" t="s">
+      <c r="AU7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV7" t="s">
         <v>230</v>
       </c>
-      <c r="AK7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL7" t="s">
+      <c r="AW7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX7" t="s">
         <v>231</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AY7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB7" t="s">
         <v>232</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>233</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>234</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>236</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>237</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>238</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>239</v>
       </c>
       <c r="BC7" t="s">
         <v>45</v>
@@ -2958,261 +3720,369 @@
       <c r="BD7" t="s">
         <v>54</v>
       </c>
+      <c r="BE7" t="s">
+        <v>311</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>233</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>234</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>508</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>235</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>236</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>237</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>509</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>238</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>54</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>478</v>
+      </c>
     </row>
-    <row r="8" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>248</v>
+      </c>
       <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
         <v>249</v>
       </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
+        <v>453</v>
+      </c>
+      <c r="J8" t="s">
         <v>250</v>
       </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" t="s">
+        <v>461</v>
+      </c>
+      <c r="N8" t="s">
         <v>251</v>
       </c>
-      <c r="J8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>484</v>
+      </c>
+      <c r="R8" t="s">
         <v>252</v>
       </c>
-      <c r="M8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="S8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" t="s">
+        <v>448</v>
+      </c>
+      <c r="V8" t="s">
         <v>253</v>
       </c>
-      <c r="P8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="W8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z8" t="s">
         <v>254</v>
       </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="AA8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD8" t="s">
         <v>255</v>
       </c>
-      <c r="V8" t="s">
-        <v>45</v>
-      </c>
-      <c r="W8" t="s">
-        <v>74</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="AE8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>510</v>
+      </c>
+      <c r="AH8" t="s">
         <v>256</v>
       </c>
-      <c r="Y8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA8" t="s">
+      <c r="AI8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>247</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>247</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>247</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP8" t="s">
         <v>257</v>
       </c>
-      <c r="AB8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>248</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>248</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>248</v>
-      </c>
-      <c r="AG8" t="s">
+      <c r="AQ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>440</v>
+      </c>
+      <c r="AT8" t="s">
         <v>258</v>
       </c>
-      <c r="AH8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ8" t="s">
+      <c r="AU8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>295</v>
+      </c>
+      <c r="AX8" t="s">
         <v>259</v>
       </c>
-      <c r="AK8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM8" t="s">
+      <c r="AY8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>311</v>
+      </c>
+      <c r="BB8" t="s">
         <v>260</v>
       </c>
-      <c r="AN8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP8" t="s">
+      <c r="BC8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD8" t="s">
         <v>261</v>
       </c>
-      <c r="AQ8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR8" t="s">
+      <c r="BE8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF8" t="s">
         <v>262</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="BG8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>53</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>408</v>
+      </c>
+      <c r="BJ8" t="s">
         <v>263</v>
       </c>
-      <c r="AT8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV8" t="s">
+      <c r="BK8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL8" t="s">
         <v>264</v>
       </c>
-      <c r="AW8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX8" t="s">
+      <c r="BM8" t="s">
+        <v>319</v>
+      </c>
+      <c r="BN8" t="s">
         <v>265</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="BO8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP8" t="s">
         <v>266</v>
       </c>
-      <c r="AZ8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA8" t="s">
+      <c r="BQ8" t="s">
+        <v>446</v>
+      </c>
+      <c r="BR8" t="s">
         <v>267</v>
       </c>
-      <c r="BB8" t="s">
-        <v>268</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>74</v>
+      <c r="BS8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>457</v>
       </c>
     </row>
-    <row r="9" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>271</v>
+      </c>
       <c r="C9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
         <v>272</v>
       </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>273</v>
+      </c>
+      <c r="I9" t="s">
+        <v>467</v>
+      </c>
+      <c r="J9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" t="s">
-        <v>273</v>
-      </c>
-      <c r="G9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="M9" t="s">
+        <v>474</v>
+      </c>
+      <c r="N9" t="s">
         <v>275</v>
       </c>
-      <c r="J9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" t="s">
         <v>64</v>
       </c>
-      <c r="L9" t="s">
+      <c r="Q9" t="s">
+        <v>215</v>
+      </c>
+      <c r="R9" t="s">
         <v>276</v>
       </c>
-      <c r="M9" t="s">
-        <v>70</v>
-      </c>
-      <c r="N9" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9" t="s">
+        <v>237</v>
+      </c>
+      <c r="U9" t="s">
+        <v>237</v>
+      </c>
+      <c r="V9" t="s">
         <v>277</v>
       </c>
-      <c r="P9" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>238</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="W9" t="s">
+        <v>70</v>
+      </c>
+      <c r="X9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z9" t="s">
         <v>278</v>
       </c>
-      <c r="S9" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="AA9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB9" t="s">
         <v>58</v>
       </c>
-      <c r="U9" t="s">
+      <c r="AC9" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD9" t="s">
         <v>279</v>
-      </c>
-      <c r="V9" t="s">
-        <v>45</v>
-      </c>
-      <c r="W9" t="s">
-        <v>58</v>
-      </c>
-      <c r="X9" t="s">
-        <v>280</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>281</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>282</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>283</v>
       </c>
       <c r="AE9" t="s">
         <v>70</v>
@@ -3221,93 +4091,147 @@
         <v>64</v>
       </c>
       <c r="AG9" t="s">
+        <v>473</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>469</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>464</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>283</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>468</v>
+      </c>
+      <c r="AT9" t="s">
         <v>284</v>
       </c>
-      <c r="AH9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ9" t="s">
+      <c r="AU9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV9" t="s">
         <v>285</v>
       </c>
-      <c r="AK9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL9" t="s">
+      <c r="AW9" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX9" t="s">
         <v>286</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AY9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ9" t="s">
         <v>287</v>
       </c>
-      <c r="AN9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO9" t="s">
+      <c r="BA9" t="s">
+        <v>472</v>
+      </c>
+      <c r="BB9" t="s">
         <v>288</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="BC9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD9" t="s">
         <v>289</v>
       </c>
-      <c r="AQ9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR9" t="s">
+      <c r="BE9" t="s">
+        <v>289</v>
+      </c>
+      <c r="BF9" t="s">
         <v>290</v>
       </c>
-      <c r="AS9" t="s">
+      <c r="BG9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>237</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>471</v>
+      </c>
+      <c r="BJ9" t="s">
         <v>291</v>
       </c>
-      <c r="AT9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>238</v>
-      </c>
-      <c r="AV9" t="s">
+      <c r="BK9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>181</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>334</v>
+      </c>
+      <c r="BN9" t="s">
         <v>292</v>
       </c>
-      <c r="AW9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>182</v>
-      </c>
-      <c r="AY9" t="s">
+      <c r="BO9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP9" t="s">
         <v>293</v>
       </c>
-      <c r="AZ9" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA9" t="s">
+      <c r="BQ9" t="s">
+        <v>451</v>
+      </c>
+      <c r="BR9" t="s">
         <v>294</v>
       </c>
-      <c r="BB9" t="s">
+      <c r="BS9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT9" t="s">
         <v>295</v>
       </c>
-      <c r="BC9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>296</v>
+      <c r="BU9" t="s">
+        <v>295</v>
       </c>
     </row>
-    <row r="10" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="10" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>299</v>
+      </c>
       <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
         <v>300</v>
       </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" t="s">
+        <v>476</v>
+      </c>
+      <c r="F10" t="s">
         <v>301</v>
-      </c>
-      <c r="F10" t="s">
-        <v>302</v>
       </c>
       <c r="G10" t="s">
         <v>70</v>
@@ -3316,833 +4240,1103 @@
         <v>56</v>
       </c>
       <c r="I10" t="s">
+        <v>225</v>
+      </c>
+      <c r="J10" t="s">
+        <v>302</v>
+      </c>
+      <c r="K10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" t="s">
         <v>303</v>
       </c>
-      <c r="J10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
+        <v>144</v>
+      </c>
+      <c r="N10" t="s">
         <v>304</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O10" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>94</v>
+      </c>
+      <c r="R10" t="s">
         <v>305</v>
       </c>
-      <c r="M10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" t="s">
-        <v>296</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
+        <v>70</v>
+      </c>
+      <c r="T10" t="s">
+        <v>156</v>
+      </c>
+      <c r="U10" t="s">
+        <v>482</v>
+      </c>
+      <c r="V10" t="s">
         <v>306</v>
       </c>
-      <c r="P10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>157</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="W10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" t="s">
         <v>307</v>
       </c>
-      <c r="S10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="Y10" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z10" t="s">
         <v>308</v>
       </c>
-      <c r="U10" t="s">
+      <c r="AA10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>483</v>
+      </c>
+      <c r="AD10" t="s">
         <v>309</v>
       </c>
-      <c r="V10" t="s">
-        <v>70</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="AE10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>310</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>311</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>312</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>477</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>313</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>479</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>314</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>484</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>315</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>295</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>478</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>316</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>317</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>317</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>318</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>319</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>481</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>320</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>321</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>322</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>480</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>323</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>324</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>325</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>490</v>
+      </c>
+      <c r="F11" t="s">
+        <v>326</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" t="s">
+        <v>489</v>
+      </c>
+      <c r="J11" t="s">
+        <v>327</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" t="s">
+        <v>454</v>
+      </c>
+      <c r="N11" t="s">
+        <v>328</v>
+      </c>
+      <c r="O11" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>225</v>
+      </c>
+      <c r="R11" t="s">
+        <v>329</v>
+      </c>
+      <c r="S11" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" t="s">
+        <v>221</v>
+      </c>
+      <c r="U11" t="s">
+        <v>492</v>
+      </c>
+      <c r="V11" t="s">
+        <v>330</v>
+      </c>
+      <c r="W11" t="s">
+        <v>45</v>
+      </c>
+      <c r="X11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>493</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>332</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>333</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>334</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>488</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>335</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>451</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>336</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>219</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>487</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>338</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>337</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>337</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>339</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>223</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>223</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>340</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>341</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>273</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>342</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>343</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>344</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>266</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>317</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>345</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>485</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>346</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>486</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>347</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" t="s">
+        <v>478</v>
+      </c>
+      <c r="F12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>324</v>
+      </c>
+      <c r="J12" t="s">
+        <v>352</v>
+      </c>
+      <c r="K12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" t="s">
+        <v>490</v>
+      </c>
+      <c r="N12" t="s">
+        <v>353</v>
+      </c>
+      <c r="O12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>508</v>
+      </c>
+      <c r="R12" t="s">
+        <v>354</v>
+      </c>
+      <c r="S12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T12" t="s">
+        <v>74</v>
+      </c>
+      <c r="U12" t="s">
+        <v>494</v>
+      </c>
+      <c r="V12" t="s">
+        <v>355</v>
+      </c>
+      <c r="W12" t="s">
+        <v>70</v>
+      </c>
+      <c r="X12" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>356</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>499</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>359</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>498</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>360</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>493</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>361</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>161</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>362</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>303</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>363</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>496</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>364</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>154</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>365</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>90</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>500</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>366</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>64</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>495</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>367</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ12" t="s">
+        <v>88</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>368</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>369</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>502</v>
+      </c>
+      <c r="F13" t="s">
+        <v>377</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>507</v>
+      </c>
+      <c r="J13" t="s">
+        <v>378</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" t="s">
+        <v>495</v>
+      </c>
+      <c r="N13" t="s">
+        <v>379</v>
+      </c>
+      <c r="O13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>478</v>
+      </c>
+      <c r="R13" t="s">
+        <v>380</v>
+      </c>
+      <c r="S13" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" t="s">
+        <v>74</v>
+      </c>
+      <c r="U13" t="s">
+        <v>509</v>
+      </c>
+      <c r="V13" t="s">
+        <v>381</v>
+      </c>
+      <c r="W13" t="s">
+        <v>45</v>
+      </c>
+      <c r="X13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>503</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>382</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>501</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>383</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>504</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>384</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>446</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>385</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>311</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>386</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>215</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>387</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>505</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>388</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA13" t="s">
         <v>71</v>
       </c>
-      <c r="X10" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>313</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>314</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI10" t="s">
+      <c r="BB13" t="s">
+        <v>389</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>506</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>390</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>391</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>508</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>392</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>67</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>393</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>401</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>483</v>
+      </c>
+      <c r="F14" t="s">
+        <v>402</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>479</v>
+      </c>
+      <c r="J14" t="s">
+        <v>403</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" t="s">
+        <v>404</v>
+      </c>
+      <c r="O14" t="s">
+        <v>45</v>
+      </c>
+      <c r="P14" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>94</v>
+      </c>
+      <c r="R14" t="s">
+        <v>405</v>
+      </c>
+      <c r="S14" t="s">
+        <v>45</v>
+      </c>
+      <c r="T14" t="s">
+        <v>74</v>
+      </c>
+      <c r="U14" t="s">
+        <v>482</v>
+      </c>
+      <c r="V14" t="s">
+        <v>406</v>
+      </c>
+      <c r="W14" t="s">
+        <v>45</v>
+      </c>
+      <c r="X14" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>407</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>476</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>409</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>410</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ14" t="s">
         <v>58</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>315</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>316</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>296</v>
-      </c>
-      <c r="AP10" t="s">
+      <c r="AK14" t="s">
+        <v>480</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>411</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>324</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>307</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>413</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>481</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>414</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>478</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>415</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>416</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>225</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>417</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>64</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>144</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>418</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>178</v>
+      </c>
+      <c r="BQ14" t="s">
+        <v>484</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>419</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>420</v>
+      </c>
+      <c r="BU14" t="s">
         <v>317</v>
       </c>
-      <c r="AQ10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>318</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>319</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>321</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AY10" t="s">
-        <v>322</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>323</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>324</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>325</v>
-      </c>
     </row>
-    <row r="11" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>326</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" t="s">
-        <v>327</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" t="s">
-        <v>141</v>
-      </c>
-      <c r="I11" t="s">
-        <v>328</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" t="s">
-        <v>329</v>
-      </c>
-      <c r="M11" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" t="s">
-        <v>74</v>
-      </c>
-      <c r="O11" t="s">
-        <v>330</v>
-      </c>
-      <c r="P11" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>222</v>
-      </c>
-      <c r="R11" t="s">
-        <v>331</v>
-      </c>
-      <c r="S11" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11" t="s">
-        <v>58</v>
-      </c>
-      <c r="U11" t="s">
-        <v>332</v>
-      </c>
-      <c r="V11" t="s">
-        <v>45</v>
-      </c>
-      <c r="W11" t="s">
-        <v>333</v>
-      </c>
-      <c r="X11" t="s">
-        <v>334</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>335</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>336</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>337</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>220</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>339</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>338</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>340</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>224</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>341</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>342</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>343</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>344</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>345</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>267</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>346</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>347</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA11" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>348</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="12" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>351</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
-        <v>352</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" t="s">
-        <v>353</v>
-      </c>
-      <c r="J12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" t="s">
-        <v>92</v>
-      </c>
-      <c r="L12" t="s">
-        <v>354</v>
-      </c>
-      <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" t="s">
-        <v>64</v>
-      </c>
-      <c r="O12" t="s">
-        <v>355</v>
-      </c>
-      <c r="P12" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>74</v>
-      </c>
-      <c r="R12" t="s">
-        <v>356</v>
-      </c>
-      <c r="S12" t="s">
-        <v>70</v>
-      </c>
-      <c r="T12" t="s">
-        <v>74</v>
-      </c>
-      <c r="U12" t="s">
-        <v>357</v>
-      </c>
-      <c r="V12" t="s">
-        <v>45</v>
-      </c>
-      <c r="W12" t="s">
-        <v>58</v>
-      </c>
-      <c r="X12" t="s">
-        <v>358</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>360</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>361</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>362</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>363</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>304</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>364</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>365</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>366</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>367</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>368</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>369</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="13" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>377</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" t="s">
-        <v>378</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" t="s">
-        <v>379</v>
-      </c>
-      <c r="J13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" t="s">
-        <v>380</v>
-      </c>
-      <c r="M13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" t="s">
-        <v>381</v>
-      </c>
-      <c r="P13" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>74</v>
-      </c>
-      <c r="R13" t="s">
-        <v>382</v>
-      </c>
-      <c r="S13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" t="s">
-        <v>74</v>
-      </c>
-      <c r="U13" t="s">
-        <v>383</v>
-      </c>
-      <c r="V13" t="s">
-        <v>70</v>
-      </c>
-      <c r="W13" t="s">
-        <v>74</v>
-      </c>
-      <c r="X13" t="s">
-        <v>384</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>385</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>386</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>387</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>388</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>389</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>390</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>391</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>392</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>393</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>394</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>402</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" t="s">
-        <v>403</v>
-      </c>
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" t="s">
-        <v>404</v>
-      </c>
-      <c r="J14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" t="s">
-        <v>61</v>
-      </c>
-      <c r="L14" t="s">
-        <v>405</v>
-      </c>
-      <c r="M14" t="s">
-        <v>45</v>
-      </c>
-      <c r="N14" t="s">
-        <v>74</v>
-      </c>
-      <c r="O14" t="s">
-        <v>406</v>
-      </c>
-      <c r="P14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>74</v>
-      </c>
-      <c r="R14" t="s">
-        <v>407</v>
-      </c>
-      <c r="S14" t="s">
-        <v>45</v>
-      </c>
-      <c r="T14" t="s">
-        <v>64</v>
-      </c>
-      <c r="U14" t="s">
-        <v>408</v>
-      </c>
-      <c r="V14" t="s">
-        <v>45</v>
-      </c>
-      <c r="W14" t="s">
-        <v>409</v>
-      </c>
-      <c r="X14" t="s">
-        <v>410</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>412</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>413</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>414</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>415</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>416</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>417</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>418</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY14" t="s">
-        <v>419</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA14" t="s">
-        <v>179</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>420</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD14" t="s">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="15" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>14</v>
-      </c>
       <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s">
         <v>422</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" t="s">
-        <v>423</v>
       </c>
       <c r="G15" t="s">
         <v>45</v>
@@ -4151,153 +5345,204 @@
         <v>64</v>
       </c>
       <c r="I15" t="s">
+        <v>440</v>
+      </c>
+      <c r="J15" t="s">
+        <v>423</v>
+      </c>
+      <c r="K15" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" t="s">
+        <v>446</v>
+      </c>
+      <c r="N15" t="s">
         <v>424</v>
       </c>
-      <c r="J15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="O15" t="s">
+        <v>45</v>
+      </c>
+      <c r="P15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>319</v>
+      </c>
+      <c r="R15" t="s">
         <v>425</v>
       </c>
-      <c r="M15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N15" t="s">
-        <v>74</v>
-      </c>
-      <c r="O15" t="s">
+      <c r="S15" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" t="s">
+        <v>74</v>
+      </c>
+      <c r="U15" t="s">
+        <v>464</v>
+      </c>
+      <c r="V15" t="s">
         <v>426</v>
       </c>
-      <c r="P15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>74</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>311</v>
+      </c>
+      <c r="Z15" t="s">
         <v>427</v>
       </c>
-      <c r="S15" t="s">
-        <v>45</v>
-      </c>
-      <c r="T15" t="s">
-        <v>74</v>
-      </c>
-      <c r="U15" t="s">
+      <c r="AA15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>461</v>
+      </c>
+      <c r="AD15" t="s">
         <v>428</v>
       </c>
-      <c r="V15" t="s">
-        <v>45</v>
-      </c>
-      <c r="W15" t="s">
-        <v>74</v>
-      </c>
-      <c r="X15" t="s">
+      <c r="AE15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>408</v>
+      </c>
+      <c r="AH15" t="s">
         <v>429</v>
       </c>
-      <c r="Y15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA15" t="s">
+      <c r="AI15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>448</v>
+      </c>
+      <c r="AL15" t="s">
         <v>430</v>
       </c>
-      <c r="AB15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD15" t="s">
+      <c r="AM15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>457</v>
+      </c>
+      <c r="AP15" t="s">
         <v>431</v>
       </c>
-      <c r="AE15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG15" t="s">
+      <c r="AQ15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>261</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT15" t="s">
         <v>432</v>
       </c>
-      <c r="AH15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>262</v>
-      </c>
-      <c r="AJ15" t="s">
+      <c r="AU15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>484</v>
+      </c>
+      <c r="AX15" t="s">
         <v>433</v>
       </c>
-      <c r="AK15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM15" t="s">
+      <c r="AY15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>295</v>
+      </c>
+      <c r="BB15" t="s">
         <v>434</v>
       </c>
-      <c r="AN15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP15" t="s">
+      <c r="BC15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>161</v>
+      </c>
+      <c r="BF15" t="s">
         <v>435</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS15" t="s">
+      <c r="BG15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>439</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>453</v>
+      </c>
+      <c r="BN15" t="s">
         <v>436</v>
       </c>
-      <c r="AT15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>440</v>
-      </c>
-      <c r="AW15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY15" t="s">
+      <c r="BO15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BQ15" t="s">
+        <v>150</v>
+      </c>
+      <c r="BR15" t="s">
         <v>437</v>
       </c>
-      <c r="AZ15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA15" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB15" t="s">
+      <c r="BS15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BU15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BB16" t="s">
         <v>438</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="AP16" t="s">
-        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4307,10 +5552,2838 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1981F99-95ED-44DE-BDB0-2D4F2D0CC110}">
+  <dimension ref="A1:BC22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H1" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J1" t="s">
+        <v>517</v>
+      </c>
+      <c r="K1" t="s">
+        <v>520</v>
+      </c>
+      <c r="L1" t="s">
+        <v>521</v>
+      </c>
+      <c r="M1" t="s">
+        <v>519</v>
+      </c>
+      <c r="N1" t="s">
+        <v>524</v>
+      </c>
+      <c r="O1" t="s">
+        <v>525</v>
+      </c>
+      <c r="P1" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>526</v>
+      </c>
+      <c r="R1" t="s">
+        <v>527</v>
+      </c>
+      <c r="S1" t="s">
+        <v>528</v>
+      </c>
+      <c r="T1" t="s">
+        <v>529</v>
+      </c>
+      <c r="U1" t="s">
+        <v>530</v>
+      </c>
+      <c r="V1" t="s">
+        <v>531</v>
+      </c>
+      <c r="W1" t="s">
+        <v>532</v>
+      </c>
+      <c r="X1" t="s">
+        <v>533</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>534</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>536</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>540</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>541</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>542</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>543</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>546</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>547</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>550</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>552</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>553</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>554</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>555</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>556</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>557</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>558</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>559</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>560</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>561</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>562</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>563</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <f>'During Experiment'!C2</f>
+        <v>N</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="str">
+        <f>'During Experiment'!G2</f>
+        <v>N</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="str">
+        <f>'During Experiment'!K2</f>
+        <v>N</v>
+      </c>
+      <c r="I2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" t="str">
+        <f>'During Experiment'!O2</f>
+        <v>N</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="str">
+        <f>'During Experiment'!S2</f>
+        <v>N</v>
+      </c>
+      <c r="O2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>'During Experiment'!W2</f>
+        <v>N</v>
+      </c>
+      <c r="R2" t="s">
+        <v>575</v>
+      </c>
+      <c r="S2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" t="str">
+        <f>'During Experiment'!AA2</f>
+        <v>N</v>
+      </c>
+      <c r="U2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" t="str">
+        <f>'During Experiment'!AE2</f>
+        <v>N</v>
+      </c>
+      <c r="X2" t="s">
+        <v>575</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="str">
+        <f>'During Experiment'!AI2</f>
+        <v>J</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" t="str">
+        <f>'During Experiment'!AM2</f>
+        <v>N</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF2" t="str">
+        <f>'During Experiment'!AQ2</f>
+        <v>N</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI2" t="str">
+        <f>'During Experiment'!AU2</f>
+        <v>N</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL2" t="str">
+        <f>'During Experiment'!AY2</f>
+        <v>N</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO2" t="str">
+        <f>'During Experiment'!BC2</f>
+        <v>N</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR2" t="str">
+        <f>'During Experiment'!BG2</f>
+        <v>N</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU2" t="str">
+        <f>'During Experiment'!BK2</f>
+        <v>J</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX2" t="str">
+        <f>'During Experiment'!BO2</f>
+        <v>N</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA2" t="str">
+        <f>'During Experiment'!BS2</f>
+        <v>N</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <f>'During Experiment'!C3</f>
+        <v>J</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="str">
+        <f>'During Experiment'!G3</f>
+        <v>N</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="str">
+        <f>'During Experiment'!K3</f>
+        <v>J</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="str">
+        <f>'During Experiment'!O3</f>
+        <v>J</v>
+      </c>
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" t="str">
+        <f>'During Experiment'!S3</f>
+        <v>J</v>
+      </c>
+      <c r="O3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="str">
+        <f>'During Experiment'!W3</f>
+        <v>J</v>
+      </c>
+      <c r="R3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" t="str">
+        <f>'During Experiment'!AA3</f>
+        <v>N</v>
+      </c>
+      <c r="U3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="str">
+        <f>'During Experiment'!AE3</f>
+        <v>J</v>
+      </c>
+      <c r="X3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="str">
+        <f>'During Experiment'!AI3</f>
+        <v>N</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC3" t="str">
+        <f>'During Experiment'!AM3</f>
+        <v>J</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF3" t="str">
+        <f>'During Experiment'!AQ3</f>
+        <v>J</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" t="str">
+        <f>'During Experiment'!AU3</f>
+        <v>J</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL3" t="str">
+        <f>'During Experiment'!AY3</f>
+        <v>N</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO3" t="str">
+        <f>'During Experiment'!BC3</f>
+        <v>N</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR3" t="str">
+        <f>'During Experiment'!BG3</f>
+        <v>N</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU3" t="str">
+        <f>'During Experiment'!BK3</f>
+        <v>N</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX3" t="str">
+        <f>'During Experiment'!BO3</f>
+        <v>J</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA3" t="str">
+        <f>'During Experiment'!BS3</f>
+        <v>N</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>575</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <f>'During Experiment'!C4</f>
+        <v>N</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="str">
+        <f>'During Experiment'!G4</f>
+        <v>N</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="str">
+        <f>'During Experiment'!K4</f>
+        <v>N</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="str">
+        <f>'During Experiment'!O4</f>
+        <v>N</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="str">
+        <f>'During Experiment'!S4</f>
+        <v>J</v>
+      </c>
+      <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>'During Experiment'!W4</f>
+        <v>N</v>
+      </c>
+      <c r="R4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" t="str">
+        <f>'During Experiment'!AA4</f>
+        <v>N</v>
+      </c>
+      <c r="U4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" t="str">
+        <f>'During Experiment'!AE4</f>
+        <v>N</v>
+      </c>
+      <c r="X4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z4" t="str">
+        <f>'During Experiment'!AI4</f>
+        <v>N</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC4" t="str">
+        <f>'During Experiment'!AM4</f>
+        <v>N</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="str">
+        <f>'During Experiment'!AQ4</f>
+        <v>N</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI4" t="str">
+        <f>'During Experiment'!AU4</f>
+        <v>N</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL4" t="str">
+        <f>'During Experiment'!AY4</f>
+        <v>N</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO4" t="str">
+        <f>'During Experiment'!BC4</f>
+        <v>N</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>575</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR4" t="str">
+        <f>'During Experiment'!BG4</f>
+        <v>N</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU4" t="str">
+        <f>'During Experiment'!BK4</f>
+        <v>J</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX4" t="str">
+        <f>'During Experiment'!BO4</f>
+        <v>N</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>575</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA4" t="str">
+        <f>'During Experiment'!BS4</f>
+        <v>N</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <f>'During Experiment'!C5</f>
+        <v>J</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="str">
+        <f>'During Experiment'!G5</f>
+        <v>N</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="str">
+        <f>'During Experiment'!K5</f>
+        <v>N</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" t="str">
+        <f>'During Experiment'!O5</f>
+        <v>N</v>
+      </c>
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" t="str">
+        <f>'During Experiment'!S5</f>
+        <v>N</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="str">
+        <f>'During Experiment'!W5</f>
+        <v>N</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" t="str">
+        <f>'During Experiment'!AA5</f>
+        <v>N</v>
+      </c>
+      <c r="U5" t="s">
+        <v>45</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="str">
+        <f>'During Experiment'!AE5</f>
+        <v>N</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z5" t="str">
+        <f>'During Experiment'!AI5</f>
+        <v>N</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>575</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC5" t="str">
+        <f>'During Experiment'!AM5</f>
+        <v>N</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF5" t="str">
+        <f>'During Experiment'!AQ5</f>
+        <v>N</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>575</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI5" t="str">
+        <f>'During Experiment'!AU5</f>
+        <v>J</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL5" t="str">
+        <f>'During Experiment'!AY5</f>
+        <v>J</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO5" t="str">
+        <f>'During Experiment'!BC5</f>
+        <v>N</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR5" t="str">
+        <f>'During Experiment'!BG5</f>
+        <v>J</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU5" t="str">
+        <f>'During Experiment'!BK5</f>
+        <v>N</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX5" t="str">
+        <f>'During Experiment'!BO5</f>
+        <v>N</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA5" t="str">
+        <f>'During Experiment'!BS5</f>
+        <v>N</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <f>'During Experiment'!C6</f>
+        <v>N</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="str">
+        <f>'During Experiment'!G6</f>
+        <v>J</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="str">
+        <f>'During Experiment'!K6</f>
+        <v>N</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="str">
+        <f>'During Experiment'!O6</f>
+        <v>N</v>
+      </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" t="str">
+        <f>'During Experiment'!S6</f>
+        <v>N</v>
+      </c>
+      <c r="O6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>'During Experiment'!W6</f>
+        <v>N</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" t="str">
+        <f>'During Experiment'!AA6</f>
+        <v>N</v>
+      </c>
+      <c r="U6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V6" t="s">
+        <v>45</v>
+      </c>
+      <c r="W6" t="str">
+        <f>'During Experiment'!AE6</f>
+        <v>N</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="str">
+        <f>'During Experiment'!AI6</f>
+        <v>J</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC6" t="str">
+        <f>'During Experiment'!AM6</f>
+        <v>J</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF6" t="str">
+        <f>'During Experiment'!AQ6</f>
+        <v>N</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI6" t="str">
+        <f>'During Experiment'!AU6</f>
+        <v>N</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL6" t="str">
+        <f>'During Experiment'!AY6</f>
+        <v>N</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO6" t="str">
+        <f>'During Experiment'!BC6</f>
+        <v>N</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR6" t="str">
+        <f>'During Experiment'!BG6</f>
+        <v>J</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU6" t="str">
+        <f>'During Experiment'!BK6</f>
+        <v>N</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>575</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX6" t="str">
+        <f>'During Experiment'!BO6</f>
+        <v>J</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>575</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA6" t="str">
+        <f>'During Experiment'!BS6</f>
+        <v>N</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <f>'During Experiment'!C7</f>
+        <v>N</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="str">
+        <f>'During Experiment'!G7</f>
+        <v>N</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="str">
+        <f>'During Experiment'!K7</f>
+        <v>N</v>
+      </c>
+      <c r="I7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="str">
+        <f>'During Experiment'!O7</f>
+        <v>N</v>
+      </c>
+      <c r="L7" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" t="str">
+        <f>'During Experiment'!S7</f>
+        <v>N</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" t="str">
+        <f>'During Experiment'!W7</f>
+        <v>N</v>
+      </c>
+      <c r="R7" t="s">
+        <v>70</v>
+      </c>
+      <c r="S7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" t="str">
+        <f>'During Experiment'!AA7</f>
+        <v>N</v>
+      </c>
+      <c r="U7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" t="str">
+        <f>'During Experiment'!AE7</f>
+        <v>N</v>
+      </c>
+      <c r="X7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z7" t="str">
+        <f>'During Experiment'!AI7</f>
+        <v>N</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC7" t="str">
+        <f>'During Experiment'!AM7</f>
+        <v>N</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF7" t="str">
+        <f>'During Experiment'!AQ7</f>
+        <v>J</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>575</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI7" t="str">
+        <f>'During Experiment'!AU7</f>
+        <v>N</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL7" t="str">
+        <f>'During Experiment'!AY7</f>
+        <v>N</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO7" t="str">
+        <f>'During Experiment'!BC7</f>
+        <v>N</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR7" t="str">
+        <f>'During Experiment'!BG7</f>
+        <v>N</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU7" t="str">
+        <f>'During Experiment'!BK7</f>
+        <v>N</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX7" t="str">
+        <f>'During Experiment'!BO7</f>
+        <v>N</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA7" t="str">
+        <f>'During Experiment'!BS7</f>
+        <v>N</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>575</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <f>'During Experiment'!C8</f>
+        <v>J</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="str">
+        <f>'During Experiment'!G8</f>
+        <v>N</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="str">
+        <f>'During Experiment'!K8</f>
+        <v>N</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" t="str">
+        <f>'During Experiment'!O8</f>
+        <v>N</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="str">
+        <f>'During Experiment'!S8</f>
+        <v>N</v>
+      </c>
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="str">
+        <f>'During Experiment'!W8</f>
+        <v>N</v>
+      </c>
+      <c r="R8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" t="str">
+        <f>'During Experiment'!AA8</f>
+        <v>N</v>
+      </c>
+      <c r="U8" t="s">
+        <v>45</v>
+      </c>
+      <c r="V8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W8" t="str">
+        <f>'During Experiment'!AE8</f>
+        <v>N</v>
+      </c>
+      <c r="X8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" t="str">
+        <f>'During Experiment'!AI8</f>
+        <v>N</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC8" t="str">
+        <f>'During Experiment'!AM8</f>
+        <v>INVALID</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF8" t="str">
+        <f>'During Experiment'!AQ8</f>
+        <v>N</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI8" t="str">
+        <f>'During Experiment'!AU8</f>
+        <v>N</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL8" t="str">
+        <f>'During Experiment'!AY8</f>
+        <v>N</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO8" t="str">
+        <f>'During Experiment'!BC8</f>
+        <v>N</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR8" t="str">
+        <f>'During Experiment'!BG8</f>
+        <v>N</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU8" t="str">
+        <f>'During Experiment'!BK8</f>
+        <v>N</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>575</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX8" t="str">
+        <f>'During Experiment'!BO8</f>
+        <v>N</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>575</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA8" t="str">
+        <f>'During Experiment'!BS8</f>
+        <v>N</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <f>'During Experiment'!C9</f>
+        <v>J</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="str">
+        <f>'During Experiment'!G9</f>
+        <v>J</v>
+      </c>
+      <c r="F9" t="s">
+        <v>575</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="str">
+        <f>'During Experiment'!K9</f>
+        <v>N</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="str">
+        <f>'During Experiment'!O9</f>
+        <v>J</v>
+      </c>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" t="str">
+        <f>'During Experiment'!S9</f>
+        <v>N</v>
+      </c>
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q9" t="str">
+        <f>'During Experiment'!W9</f>
+        <v>J</v>
+      </c>
+      <c r="R9" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" t="str">
+        <f>'During Experiment'!AA9</f>
+        <v>N</v>
+      </c>
+      <c r="U9" t="s">
+        <v>45</v>
+      </c>
+      <c r="V9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W9" t="str">
+        <f>'During Experiment'!AE9</f>
+        <v>J</v>
+      </c>
+      <c r="X9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z9" t="str">
+        <f>'During Experiment'!AI9</f>
+        <v>N</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>575</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC9" t="str">
+        <f>'During Experiment'!AM9</f>
+        <v>J</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF9" t="str">
+        <f>'During Experiment'!AQ9</f>
+        <v>J</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI9" t="str">
+        <f>'During Experiment'!AU9</f>
+        <v>N</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL9" t="str">
+        <f>'During Experiment'!AY9</f>
+        <v>J</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>575</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO9" t="str">
+        <f>'During Experiment'!BC9</f>
+        <v>N</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR9" t="str">
+        <f>'During Experiment'!BG9</f>
+        <v>N</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU9" t="str">
+        <f>'During Experiment'!BK9</f>
+        <v>N</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>575</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX9" t="str">
+        <f>'During Experiment'!BO9</f>
+        <v>J</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA9" t="str">
+        <f>'During Experiment'!BS9</f>
+        <v>N</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <f>'During Experiment'!C10</f>
+        <v>N</v>
+      </c>
+      <c r="C10" t="s">
+        <v>575</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="str">
+        <f>'During Experiment'!G10</f>
+        <v>J</v>
+      </c>
+      <c r="F10" t="s">
+        <v>575</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="str">
+        <f>'During Experiment'!K10</f>
+        <v>N</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" t="str">
+        <f>'During Experiment'!O10</f>
+        <v>N</v>
+      </c>
+      <c r="L10" t="s">
+        <v>575</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="str">
+        <f>'During Experiment'!S10</f>
+        <v>J</v>
+      </c>
+      <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q10" t="str">
+        <f>'During Experiment'!W10</f>
+        <v>N</v>
+      </c>
+      <c r="R10" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" t="s">
+        <v>70</v>
+      </c>
+      <c r="T10" t="str">
+        <f>'During Experiment'!AA10</f>
+        <v>J</v>
+      </c>
+      <c r="U10" t="s">
+        <v>575</v>
+      </c>
+      <c r="V10" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" t="str">
+        <f>'During Experiment'!AE10</f>
+        <v>J</v>
+      </c>
+      <c r="X10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z10" t="str">
+        <f>'During Experiment'!AI10</f>
+        <v>N</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>575</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC10" t="str">
+        <f>'During Experiment'!AM10</f>
+        <v>J</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF10" t="str">
+        <f>'During Experiment'!AQ10</f>
+        <v>N</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI10" t="str">
+        <f>'During Experiment'!AU10</f>
+        <v>N</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="str">
+        <f>'During Experiment'!AY10</f>
+        <v>N</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>575</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO10" t="str">
+        <f>'During Experiment'!BC10</f>
+        <v>N</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR10" t="str">
+        <f>'During Experiment'!BG10</f>
+        <v>J</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU10" t="str">
+        <f>'During Experiment'!BK10</f>
+        <v>N</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX10" t="str">
+        <f>'During Experiment'!BO10</f>
+        <v>N</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA10" t="str">
+        <f>'During Experiment'!BS10</f>
+        <v>N</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <f>'During Experiment'!C11</f>
+        <v>N</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="str">
+        <f>'During Experiment'!G11</f>
+        <v>N</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" t="str">
+        <f>'During Experiment'!K11</f>
+        <v>N</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="str">
+        <f>'During Experiment'!O11</f>
+        <v>J</v>
+      </c>
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" t="str">
+        <f>'During Experiment'!S11</f>
+        <v>N</v>
+      </c>
+      <c r="O11" t="s">
+        <v>575</v>
+      </c>
+      <c r="P11" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q11" t="str">
+        <f>'During Experiment'!W11</f>
+        <v>N</v>
+      </c>
+      <c r="R11" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" t="s">
+        <v>70</v>
+      </c>
+      <c r="T11" t="str">
+        <f>'During Experiment'!AA11</f>
+        <v>N</v>
+      </c>
+      <c r="U11" t="s">
+        <v>70</v>
+      </c>
+      <c r="V11" t="s">
+        <v>45</v>
+      </c>
+      <c r="W11" t="str">
+        <f>'During Experiment'!AE11</f>
+        <v>J</v>
+      </c>
+      <c r="X11" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z11" t="str">
+        <f>'During Experiment'!AI11</f>
+        <v>J</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC11" t="str">
+        <f>'During Experiment'!AM11</f>
+        <v>J</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF11" t="str">
+        <f>'During Experiment'!AQ11</f>
+        <v>N</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI11" t="str">
+        <f>'During Experiment'!AU11</f>
+        <v>N</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL11" t="str">
+        <f>'During Experiment'!AY11</f>
+        <v>N</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO11" t="str">
+        <f>'During Experiment'!BC11</f>
+        <v>N</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR11" t="str">
+        <f>'During Experiment'!BG11</f>
+        <v>N</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU11" t="str">
+        <f>'During Experiment'!BK11</f>
+        <v>J</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX11" t="str">
+        <f>'During Experiment'!BO11</f>
+        <v>N</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA11" t="str">
+        <f>'During Experiment'!BS11</f>
+        <v>N</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <f>'During Experiment'!C12</f>
+        <v>N</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="str">
+        <f>'During Experiment'!G12</f>
+        <v>N</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="str">
+        <f>'During Experiment'!K12</f>
+        <v>N</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" t="str">
+        <f>'During Experiment'!O12</f>
+        <v>N</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" t="str">
+        <f>'During Experiment'!S12</f>
+        <v>N</v>
+      </c>
+      <c r="O12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="str">
+        <f>'During Experiment'!W12</f>
+        <v>J</v>
+      </c>
+      <c r="R12" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T12" t="str">
+        <f>'During Experiment'!AA12</f>
+        <v>N</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>70</v>
+      </c>
+      <c r="W12" t="str">
+        <f>'During Experiment'!AE12</f>
+        <v>J</v>
+      </c>
+      <c r="X12" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z12" t="str">
+        <f>'During Experiment'!AI12</f>
+        <v>N</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC12" t="str">
+        <f>'During Experiment'!AM12</f>
+        <v>N</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF12" t="str">
+        <f>'During Experiment'!AQ12</f>
+        <v>J</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI12" t="str">
+        <f>'During Experiment'!AU12</f>
+        <v>N</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL12" t="str">
+        <f>'During Experiment'!AY12</f>
+        <v>J</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO12" t="str">
+        <f>'During Experiment'!BC12</f>
+        <v>N</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR12" t="str">
+        <f>'During Experiment'!BG12</f>
+        <v>N</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>575</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU12" t="str">
+        <f>'During Experiment'!BK12</f>
+        <v>J</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX12" t="str">
+        <f>'During Experiment'!BO12</f>
+        <v>N</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA12" t="str">
+        <f>'During Experiment'!BS12</f>
+        <v>N</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>575</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <f>'During Experiment'!C13</f>
+        <v>J</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="str">
+        <f>'During Experiment'!G13</f>
+        <v>N</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" t="str">
+        <f>'During Experiment'!K13</f>
+        <v>J</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" t="str">
+        <f>'During Experiment'!O13</f>
+        <v>N</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" t="str">
+        <f>'During Experiment'!S13</f>
+        <v>N</v>
+      </c>
+      <c r="O13" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" t="str">
+        <f>'During Experiment'!W13</f>
+        <v>N</v>
+      </c>
+      <c r="R13" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" t="str">
+        <f>'During Experiment'!AA13</f>
+        <v>J</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>45</v>
+      </c>
+      <c r="W13" t="str">
+        <f>'During Experiment'!AE13</f>
+        <v>N</v>
+      </c>
+      <c r="X13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z13" t="str">
+        <f>'During Experiment'!AI13</f>
+        <v>J</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC13" t="str">
+        <f>'During Experiment'!AM13</f>
+        <v>N</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF13" t="str">
+        <f>'During Experiment'!AQ13</f>
+        <v>N</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI13" t="str">
+        <f>'During Experiment'!AU13</f>
+        <v>N</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL13" t="str">
+        <f>'During Experiment'!AY13</f>
+        <v>N</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO13" t="str">
+        <f>'During Experiment'!BC13</f>
+        <v>N</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR13" t="str">
+        <f>'During Experiment'!BG13</f>
+        <v>J</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU13" t="str">
+        <f>'During Experiment'!BK13</f>
+        <v>J</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX13" t="str">
+        <f>'During Experiment'!BO13</f>
+        <v>J</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA13" t="str">
+        <f>'During Experiment'!BS13</f>
+        <v>N</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <f>'During Experiment'!C14</f>
+        <v>N</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="str">
+        <f>'During Experiment'!G14</f>
+        <v>N</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="str">
+        <f>'During Experiment'!K14</f>
+        <v>J</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" t="str">
+        <f>'During Experiment'!O14</f>
+        <v>N</v>
+      </c>
+      <c r="L14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N14" t="str">
+        <f>'During Experiment'!S14</f>
+        <v>N</v>
+      </c>
+      <c r="O14" t="s">
+        <v>45</v>
+      </c>
+      <c r="P14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>'During Experiment'!W14</f>
+        <v>N</v>
+      </c>
+      <c r="R14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S14" t="s">
+        <v>70</v>
+      </c>
+      <c r="T14" t="str">
+        <f>'During Experiment'!AA14</f>
+        <v>N</v>
+      </c>
+      <c r="U14" t="s">
+        <v>575</v>
+      </c>
+      <c r="V14" t="s">
+        <v>70</v>
+      </c>
+      <c r="W14" t="str">
+        <f>'During Experiment'!AE14</f>
+        <v>N</v>
+      </c>
+      <c r="X14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z14" t="str">
+        <f>'During Experiment'!AI14</f>
+        <v>N</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC14" t="str">
+        <f>'During Experiment'!AM14</f>
+        <v>N</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF14" t="str">
+        <f>'During Experiment'!AQ14</f>
+        <v>N</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI14" t="str">
+        <f>'During Experiment'!AU14</f>
+        <v>N</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL14" t="str">
+        <f>'During Experiment'!AY14</f>
+        <v>N</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO14" t="str">
+        <f>'During Experiment'!BC14</f>
+        <v>N</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR14" t="str">
+        <f>'During Experiment'!BG14</f>
+        <v>N</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU14" t="str">
+        <f>'During Experiment'!BK14</f>
+        <v>N</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX14" t="str">
+        <f>'During Experiment'!BO14</f>
+        <v>N</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>575</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA14" t="str">
+        <f>'During Experiment'!BS14</f>
+        <v>N</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <f>'During Experiment'!C15</f>
+        <v>J</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="str">
+        <f>'During Experiment'!G15</f>
+        <v>N</v>
+      </c>
+      <c r="F15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="str">
+        <f>'During Experiment'!K15</f>
+        <v>N</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" t="str">
+        <f>'During Experiment'!O15</f>
+        <v>N</v>
+      </c>
+      <c r="L15" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" t="str">
+        <f>'During Experiment'!S15</f>
+        <v>N</v>
+      </c>
+      <c r="O15" t="s">
+        <v>45</v>
+      </c>
+      <c r="P15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" t="str">
+        <f>'During Experiment'!W15</f>
+        <v>N</v>
+      </c>
+      <c r="R15" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" t="str">
+        <f>'During Experiment'!AA15</f>
+        <v>N</v>
+      </c>
+      <c r="U15" t="s">
+        <v>45</v>
+      </c>
+      <c r="V15" t="s">
+        <v>45</v>
+      </c>
+      <c r="W15" t="str">
+        <f>'During Experiment'!AE15</f>
+        <v>N</v>
+      </c>
+      <c r="X15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" t="str">
+        <f>'During Experiment'!AI15</f>
+        <v>N</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC15" t="str">
+        <f>'During Experiment'!AM15</f>
+        <v>N</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF15" t="str">
+        <f>'During Experiment'!AQ15</f>
+        <v>N</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI15" t="str">
+        <f>'During Experiment'!AU15</f>
+        <v>N</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL15" t="str">
+        <f>'During Experiment'!AY15</f>
+        <v>N</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO15" t="str">
+        <f>'During Experiment'!BC15</f>
+        <v>N</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR15" t="str">
+        <f>'During Experiment'!BG15</f>
+        <v>N</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU15" t="str">
+        <f>'During Experiment'!BK15</f>
+        <v>N</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX15" t="str">
+        <f>'During Experiment'!BO15</f>
+        <v>N</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA15" t="str">
+        <f>'During Experiment'!BS15</f>
+        <v>N</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>565</v>
+      </c>
+      <c r="C20" t="s">
+        <v>566</v>
+      </c>
+      <c r="F20" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>568</v>
+      </c>
+      <c r="C21" t="s">
+        <v>569</v>
+      </c>
+      <c r="F21" t="s">
+        <v>570</v>
+      </c>
+      <c r="H21" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>571</v>
+      </c>
+      <c r="C22" t="s">
+        <v>572</v>
+      </c>
+      <c r="F22" t="s">
+        <v>573</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7494ADBD-369D-4A81-9C3F-F55E008A6811}">
   <dimension ref="B1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="8" max="8" width="64.42578125" customWidth="1"/>
     <col min="9" max="10" width="17.140625" customWidth="1"/>
     <col min="11" max="11" width="22.42578125" customWidth="1"/>
     <col min="12" max="12" width="21.140625" customWidth="1"/>
@@ -4391,7 +8464,7 @@
       <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>106</v>
       </c>
       <c r="I3">
@@ -4435,7 +8508,7 @@
       <c r="G4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>110</v>
       </c>
       <c r="I4">
@@ -4479,7 +8552,7 @@
       <c r="G5" t="s">
         <v>6</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>110</v>
       </c>
       <c r="I5">
@@ -4495,13 +8568,13 @@
         <v>4</v>
       </c>
       <c r="M5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N5" t="s">
         <v>108</v>
       </c>
       <c r="O5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
@@ -4523,8 +8596,8 @@
       <c r="G6" t="s">
         <v>6</v>
       </c>
-      <c r="H6" t="s">
-        <v>165</v>
+      <c r="H6" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -4539,13 +8612,13 @@
         <v>5</v>
       </c>
       <c r="M6" t="s">
+        <v>165</v>
+      </c>
+      <c r="N6" t="s">
         <v>166</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>167</v>
-      </c>
-      <c r="O6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
@@ -4568,7 +8641,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -4583,13 +8656,13 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N7" t="s">
         <v>108</v>
       </c>
       <c r="O7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
@@ -4611,8 +8684,8 @@
       <c r="G8" t="s">
         <v>6</v>
       </c>
-      <c r="H8" t="s">
-        <v>240</v>
+      <c r="H8" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -4627,13 +8700,13 @@
         <v>4</v>
       </c>
       <c r="M8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N8" t="s">
         <v>108</v>
       </c>
       <c r="O8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
@@ -4653,10 +8726,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
+        <v>243</v>
+      </c>
+      <c r="H9" t="s">
         <v>244</v>
-      </c>
-      <c r="H9" t="s">
-        <v>245</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -4671,13 +8744,13 @@
         <v>5</v>
       </c>
       <c r="M9" t="s">
+        <v>245</v>
+      </c>
+      <c r="N9" t="s">
+        <v>166</v>
+      </c>
+      <c r="O9" t="s">
         <v>246</v>
-      </c>
-      <c r="N9" t="s">
-        <v>167</v>
-      </c>
-      <c r="O9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
@@ -4697,10 +8770,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>244</v>
-      </c>
-      <c r="H10" t="s">
-        <v>269</v>
+        <v>243</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>268</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4715,13 +8788,13 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
+        <v>269</v>
+      </c>
+      <c r="N10" t="s">
+        <v>166</v>
+      </c>
+      <c r="O10" t="s">
         <v>270</v>
-      </c>
-      <c r="N10" t="s">
-        <v>167</v>
-      </c>
-      <c r="O10" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
@@ -4743,8 +8816,8 @@
       <c r="G11" t="s">
         <v>6</v>
       </c>
-      <c r="H11" t="s">
-        <v>297</v>
+      <c r="H11" s="4" t="s">
+        <v>296</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -4759,13 +8832,13 @@
         <v>3</v>
       </c>
       <c r="M11" t="s">
+        <v>297</v>
+      </c>
+      <c r="N11" t="s">
+        <v>166</v>
+      </c>
+      <c r="O11" t="s">
         <v>298</v>
-      </c>
-      <c r="N11" t="s">
-        <v>167</v>
-      </c>
-      <c r="O11" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
@@ -4788,7 +8861,7 @@
         <v>6</v>
       </c>
       <c r="H12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I12">
         <v>3</v>
@@ -4803,13 +8876,13 @@
         <v>3</v>
       </c>
       <c r="M12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
@@ -4832,7 +8905,7 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -4847,13 +8920,13 @@
         <v>4</v>
       </c>
       <c r="M13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N13" t="s">
         <v>108</v>
       </c>
       <c r="O13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
@@ -4873,10 +8946,10 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I14">
         <v>3</v>
@@ -4891,13 +8964,13 @@
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N14" t="s">
         <v>108</v>
       </c>
       <c r="O14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
@@ -4917,10 +8990,10 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -4935,13 +9008,13 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
+        <v>395</v>
+      </c>
+      <c r="N15" t="s">
         <v>396</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>397</v>
-      </c>
-      <c r="O15" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
@@ -4964,7 +9037,7 @@
         <v>6</v>
       </c>
       <c r="H16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I16">
         <v>3</v>
@@ -4979,13 +9052,13 @@
         <v>4</v>
       </c>
       <c r="M16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N16" t="s">
         <v>108</v>
       </c>
       <c r="O16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/data/questionaire/Responses.xlsx
+++ b/data/questionaire/Responses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschu\Documents\GitHub\ET_course_project_gender-bias\data\questionaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD33050-783E-4FC8-8CD6-85EF17AB45F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C3B2E4-3602-4F6A-BB7B-A149A5C95AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA0F6B31-0EC9-497B-B9A2-40478E56EC4B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="586">
   <si>
     <t>Subject</t>
   </si>
@@ -1796,6 +1796,9 @@
   </si>
   <si>
     <t>5.Code</t>
+  </si>
+  <si>
+    <t>6.Code</t>
   </si>
 </sst>
 </file>
@@ -2189,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FD6744-3628-47C4-86D6-6648182DC30F}">
-  <dimension ref="A1:BZ15"/>
+  <dimension ref="A1:CA15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -2213,47 +2216,48 @@
     <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="28.42578125" customWidth="1"/>
     <col min="23" max="23" width="2.7109375" customWidth="1"/>
-    <col min="24" max="25" width="14" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="3.140625" customWidth="1"/>
     <col min="29" max="29" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.140625" customWidth="1"/>
-    <col min="32" max="32" width="2.28515625" customWidth="1"/>
-    <col min="33" max="33" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.5703125" customWidth="1"/>
-    <col min="36" max="36" width="2.5703125" customWidth="1"/>
-    <col min="37" max="37" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.28515625" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" customWidth="1"/>
-    <col min="40" max="40" width="2.5703125" customWidth="1"/>
-    <col min="41" max="41" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="26.5703125" customWidth="1"/>
-    <col min="44" max="44" width="4.85546875" customWidth="1"/>
-    <col min="45" max="45" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="18.5703125" customWidth="1"/>
-    <col min="48" max="48" width="3.140625" customWidth="1"/>
-    <col min="49" max="49" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="22.140625" customWidth="1"/>
-    <col min="52" max="52" width="3.140625" customWidth="1"/>
-    <col min="53" max="54" width="31.7109375" customWidth="1"/>
-    <col min="56" max="56" width="2.7109375" customWidth="1"/>
-    <col min="57" max="58" width="16.7109375" customWidth="1"/>
-    <col min="60" max="60" width="2.85546875" customWidth="1"/>
-    <col min="61" max="61" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="18.5703125" customWidth="1"/>
-    <col min="64" max="64" width="2.42578125" customWidth="1"/>
-    <col min="65" max="65" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="18.5703125" customWidth="1"/>
-    <col min="68" max="68" width="2.5703125" customWidth="1"/>
-    <col min="69" max="69" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="18.5703125" customWidth="1"/>
-    <col min="72" max="72" width="2.85546875" customWidth="1"/>
-    <col min="73" max="73" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.5703125" customWidth="1"/>
-    <col min="76" max="76" width="2.7109375" customWidth="1"/>
+    <col min="30" max="31" width="20.140625" customWidth="1"/>
+    <col min="33" max="33" width="2.28515625" customWidth="1"/>
+    <col min="34" max="34" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.5703125" customWidth="1"/>
+    <col min="37" max="37" width="2.5703125" customWidth="1"/>
+    <col min="38" max="38" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.28515625" customWidth="1"/>
+    <col min="40" max="40" width="12.5703125" customWidth="1"/>
+    <col min="41" max="41" width="2.5703125" customWidth="1"/>
+    <col min="42" max="42" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="26.5703125" customWidth="1"/>
+    <col min="45" max="45" width="4.85546875" customWidth="1"/>
+    <col min="46" max="46" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.5703125" customWidth="1"/>
+    <col min="49" max="49" width="3.140625" customWidth="1"/>
+    <col min="50" max="50" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.140625" customWidth="1"/>
+    <col min="53" max="53" width="3.140625" customWidth="1"/>
+    <col min="54" max="55" width="31.7109375" customWidth="1"/>
+    <col min="57" max="57" width="2.7109375" customWidth="1"/>
+    <col min="58" max="59" width="16.7109375" customWidth="1"/>
+    <col min="61" max="61" width="2.85546875" customWidth="1"/>
+    <col min="62" max="62" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="18.5703125" customWidth="1"/>
+    <col min="65" max="65" width="2.42578125" customWidth="1"/>
+    <col min="66" max="66" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.5703125" customWidth="1"/>
+    <col min="69" max="69" width="2.5703125" customWidth="1"/>
+    <col min="70" max="70" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="18.5703125" customWidth="1"/>
+    <col min="73" max="73" width="2.85546875" customWidth="1"/>
+    <col min="74" max="74" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18.5703125" customWidth="1"/>
+    <col min="77" max="77" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2342,154 +2346,157 @@
         <v>59</v>
       </c>
       <c r="AD1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AE1" t="s">
         <v>441</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>19</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>62</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>443</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>21</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>22</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>65</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>444</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>23</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>24</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>68</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>446</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>25</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>26</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>72</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>449</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>27</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>28</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>75</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>450</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>29</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>30</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>77</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>452</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>31</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>32</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>79</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>453</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>33</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>34</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>80</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>454</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>35</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>36</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>81</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>456</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>37</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>38</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>82</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>457</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>39</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>40</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>83</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>460</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>41</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>42</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>84</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="2" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2577,155 +2584,155 @@
       <c r="AC2" t="s">
         <v>61</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>442</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>63</v>
       </c>
-      <c r="AF2" t="s">
-        <v>45</v>
-      </c>
       <c r="AG2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" t="s">
         <v>64</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>313</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>45</v>
-      </c>
       <c r="AK2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL2" t="s">
         <v>67</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>445</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>69</v>
       </c>
-      <c r="AN2" t="s">
-        <v>70</v>
-      </c>
       <c r="AO2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP2" t="s">
         <v>71</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>447</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>73</v>
       </c>
-      <c r="AR2" t="s">
-        <v>45</v>
-      </c>
       <c r="AS2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AT2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU2" t="s">
         <v>305</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>76</v>
       </c>
-      <c r="AV2" t="s">
-        <v>45</v>
-      </c>
       <c r="AW2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX2" t="s">
         <v>58</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>451</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>78</v>
       </c>
-      <c r="AZ2" t="s">
-        <v>45</v>
-      </c>
       <c r="BA2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB2" t="s">
         <v>58</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>150</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>85</v>
       </c>
-      <c r="BD2" t="s">
-        <v>45</v>
-      </c>
       <c r="BE2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF2" t="s">
         <v>86</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>144</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>87</v>
       </c>
-      <c r="BH2" t="s">
-        <v>45</v>
-      </c>
       <c r="BI2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>88</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>455</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>89</v>
       </c>
-      <c r="BL2" t="s">
-        <v>45</v>
-      </c>
       <c r="BM2" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="BN2" t="s">
         <v>90</v>
       </c>
       <c r="BO2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP2" t="s">
         <v>91</v>
       </c>
-      <c r="BP2" t="s">
-        <v>70</v>
-      </c>
       <c r="BQ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR2" t="s">
         <v>92</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>458</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>93</v>
       </c>
-      <c r="BT2" t="s">
-        <v>45</v>
-      </c>
       <c r="BU2" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="BV2" t="s">
         <v>94</v>
       </c>
       <c r="BW2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BX2" t="s">
         <v>95</v>
       </c>
-      <c r="BX2" t="s">
-        <v>45</v>
-      </c>
       <c r="BY2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BZ2" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2813,155 +2820,155 @@
       <c r="AC3" t="s">
         <v>113</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>56</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>114</v>
       </c>
-      <c r="AF3" t="s">
-        <v>45</v>
-      </c>
       <c r="AG3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI3" t="s">
         <v>462</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>115</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>70</v>
-      </c>
       <c r="AK3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL3" t="s">
         <v>116</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>328</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>117</v>
       </c>
-      <c r="AN3" t="s">
-        <v>45</v>
-      </c>
       <c r="AO3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AP3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>445</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AR3" t="s">
         <v>118</v>
       </c>
-      <c r="AR3" t="s">
-        <v>70</v>
-      </c>
       <c r="AS3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AT3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU3" t="s">
         <v>463</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AV3" t="s">
         <v>119</v>
       </c>
-      <c r="AV3" t="s">
-        <v>70</v>
-      </c>
       <c r="AW3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AX3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY3" t="s">
         <v>464</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AZ3" t="s">
         <v>120</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>70</v>
-      </c>
       <c r="BA3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC3" t="s">
         <v>465</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BD3" t="s">
         <v>121</v>
       </c>
-      <c r="BD3" t="s">
-        <v>45</v>
-      </c>
       <c r="BE3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BF3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG3" t="s">
         <v>466</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BH3" t="s">
         <v>122</v>
       </c>
-      <c r="BH3" t="s">
-        <v>45</v>
-      </c>
       <c r="BI3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BJ3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK3" t="s">
         <v>467</v>
       </c>
-      <c r="BK3" t="s">
+      <c r="BL3" t="s">
         <v>123</v>
       </c>
-      <c r="BL3" t="s">
-        <v>45</v>
-      </c>
       <c r="BM3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN3" t="s">
         <v>64</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BO3" t="s">
         <v>468</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BP3" t="s">
         <v>124</v>
       </c>
-      <c r="BP3" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BR3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS3" t="s">
         <v>469</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BT3" t="s">
         <v>125</v>
       </c>
-      <c r="BT3" t="s">
-        <v>70</v>
-      </c>
       <c r="BU3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BV3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW3" t="s">
         <v>231</v>
       </c>
-      <c r="BW3" t="s">
+      <c r="BX3" t="s">
         <v>126</v>
       </c>
-      <c r="BX3" t="s">
-        <v>45</v>
-      </c>
       <c r="BY3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ3" t="s">
         <v>127</v>
       </c>
-      <c r="BZ3" t="s">
+      <c r="CA3" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="4" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3049,155 +3056,155 @@
       <c r="AC4" t="s">
         <v>136</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>136</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>137</v>
       </c>
-      <c r="AF4" t="s">
-        <v>45</v>
-      </c>
       <c r="AG4" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="AH4" t="s">
         <v>138</v>
       </c>
       <c r="AI4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>139</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>45</v>
-      </c>
       <c r="AK4" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="AL4" t="s">
         <v>94</v>
       </c>
       <c r="AM4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN4" t="s">
         <v>140</v>
       </c>
-      <c r="AN4" t="s">
-        <v>45</v>
-      </c>
       <c r="AO4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP4" t="s">
         <v>141</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>471</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>142</v>
       </c>
-      <c r="AR4" t="s">
-        <v>45</v>
-      </c>
       <c r="AS4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT4" t="s">
         <v>94</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>472</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>143</v>
       </c>
-      <c r="AV4" t="s">
-        <v>45</v>
-      </c>
       <c r="AW4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX4" t="s">
         <v>144</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>473</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>145</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>45</v>
-      </c>
       <c r="BA4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB4" t="s">
         <v>58</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>231</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>146</v>
       </c>
-      <c r="BD4" t="s">
-        <v>45</v>
-      </c>
       <c r="BE4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF4" t="s">
         <v>58</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>474</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>147</v>
       </c>
-      <c r="BH4" t="s">
-        <v>45</v>
-      </c>
       <c r="BI4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ4" t="s">
         <v>148</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>475</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>149</v>
       </c>
-      <c r="BL4" t="s">
-        <v>45</v>
-      </c>
       <c r="BM4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN4" t="s">
         <v>150</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
         <v>476</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BP4" t="s">
         <v>151</v>
       </c>
-      <c r="BP4" t="s">
-        <v>70</v>
-      </c>
       <c r="BQ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR4" t="s">
         <v>58</v>
       </c>
-      <c r="BR4" t="s">
+      <c r="BS4" t="s">
         <v>477</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BT4" t="s">
         <v>152</v>
       </c>
-      <c r="BT4" t="s">
-        <v>45</v>
-      </c>
       <c r="BU4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV4" t="s">
         <v>153</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="BW4" t="s">
         <v>61</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>154</v>
       </c>
-      <c r="BX4" t="s">
-        <v>45</v>
-      </c>
       <c r="BY4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ4" t="s">
         <v>155</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CA4" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3285,155 +3292,155 @@
       <c r="AC5" t="s">
         <v>58</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>217</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>169</v>
       </c>
-      <c r="AF5" t="s">
-        <v>45</v>
-      </c>
       <c r="AG5" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AH5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI5" t="s">
         <v>267</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>170</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>45</v>
-      </c>
       <c r="AK5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL5" t="s">
         <v>58</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>281</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>171</v>
       </c>
-      <c r="AN5" t="s">
-        <v>45</v>
-      </c>
       <c r="AO5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP5" t="s">
         <v>172</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
         <v>445</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AR5" t="s">
         <v>173</v>
       </c>
-      <c r="AR5" t="s">
-        <v>45</v>
-      </c>
       <c r="AS5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT5" t="s">
         <v>64</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
         <v>481</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AV5" t="s">
         <v>174</v>
       </c>
-      <c r="AV5" t="s">
-        <v>45</v>
-      </c>
       <c r="AW5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX5" t="s">
         <v>175</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>482</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
         <v>176</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>70</v>
-      </c>
       <c r="BA5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB5" t="s">
         <v>177</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>483</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>178</v>
       </c>
-      <c r="BD5" t="s">
-        <v>70</v>
-      </c>
       <c r="BE5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BF5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG5" t="s">
         <v>484</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>179</v>
       </c>
-      <c r="BH5" t="s">
-        <v>45</v>
-      </c>
       <c r="BI5" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BJ5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK5" t="s">
         <v>67</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BL5" t="s">
         <v>180</v>
       </c>
-      <c r="BL5" t="s">
-        <v>70</v>
-      </c>
       <c r="BM5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BN5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO5" t="s">
         <v>448</v>
       </c>
-      <c r="BO5" t="s">
+      <c r="BP5" t="s">
         <v>181</v>
       </c>
-      <c r="BP5" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ5" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BR5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS5" t="s">
         <v>485</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="BT5" t="s">
         <v>182</v>
       </c>
-      <c r="BT5" t="s">
-        <v>45</v>
-      </c>
       <c r="BU5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV5" t="s">
         <v>175</v>
       </c>
-      <c r="BV5" t="s">
+      <c r="BW5" t="s">
         <v>486</v>
       </c>
-      <c r="BW5" t="s">
+      <c r="BX5" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" t="s">
-        <v>45</v>
-      </c>
       <c r="BY5" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BZ5" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA5" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="6" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3521,155 +3528,155 @@
       <c r="AC6" t="s">
         <v>74</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>289</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>189</v>
       </c>
-      <c r="AF6" t="s">
-        <v>45</v>
-      </c>
       <c r="AG6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AH6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI6" t="s">
         <v>491</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AJ6" t="s">
         <v>190</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>45</v>
-      </c>
       <c r="AK6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AL6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM6" t="s">
         <v>155</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>191</v>
       </c>
-      <c r="AN6" t="s">
-        <v>70</v>
-      </c>
       <c r="AO6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>148</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>192</v>
       </c>
-      <c r="AR6" t="s">
-        <v>70</v>
-      </c>
       <c r="AS6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT6" t="s">
         <v>172</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>318</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>193</v>
       </c>
-      <c r="AV6" t="s">
-        <v>45</v>
-      </c>
       <c r="AW6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX6" t="s">
         <v>175</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AY6" t="s">
         <v>86</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AZ6" t="s">
         <v>194</v>
       </c>
-      <c r="AZ6" t="s">
-        <v>45</v>
-      </c>
       <c r="BA6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BB6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC6" t="s">
         <v>484</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BD6" t="s">
         <v>195</v>
       </c>
-      <c r="BD6" t="s">
-        <v>45</v>
-      </c>
       <c r="BE6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF6" t="s">
         <v>196</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BG6" t="s">
         <v>492</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BH6" t="s">
         <v>197</v>
       </c>
-      <c r="BH6" t="s">
-        <v>45</v>
-      </c>
       <c r="BI6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ6" t="s">
         <v>198</v>
       </c>
-      <c r="BJ6" t="s">
+      <c r="BK6" t="s">
         <v>484</v>
       </c>
-      <c r="BK6" t="s">
+      <c r="BL6" t="s">
         <v>199</v>
       </c>
-      <c r="BL6" t="s">
-        <v>70</v>
-      </c>
       <c r="BM6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN6" t="s">
         <v>200</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="BO6" t="s">
         <v>493</v>
       </c>
-      <c r="BO6" t="s">
+      <c r="BP6" t="s">
         <v>199</v>
       </c>
-      <c r="BP6" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR6" t="s">
         <v>90</v>
       </c>
-      <c r="BR6" t="s">
+      <c r="BS6" t="s">
         <v>494</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BT6" t="s">
         <v>201</v>
       </c>
-      <c r="BT6" t="s">
-        <v>70</v>
-      </c>
       <c r="BU6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV6" t="s">
         <v>202</v>
       </c>
-      <c r="BV6" t="s">
+      <c r="BW6" t="s">
         <v>153</v>
       </c>
-      <c r="BW6" t="s">
+      <c r="BX6" t="s">
         <v>203</v>
       </c>
-      <c r="BX6" t="s">
-        <v>45</v>
-      </c>
       <c r="BY6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>204</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CA6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3757,155 +3764,155 @@
       <c r="AC7" t="s">
         <v>213</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>499</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>214</v>
       </c>
-      <c r="AF7" t="s">
-        <v>45</v>
-      </c>
       <c r="AG7" t="s">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="AH7" t="s">
         <v>215</v>
       </c>
       <c r="AI7" t="s">
+        <v>215</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>216</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>45</v>
-      </c>
       <c r="AK7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL7" t="s">
         <v>217</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AM7" t="s">
         <v>500</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>218</v>
       </c>
-      <c r="AN7" t="s">
-        <v>45</v>
-      </c>
       <c r="AO7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP7" t="s">
         <v>219</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AQ7" t="s">
         <v>489</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>220</v>
       </c>
-      <c r="AR7" t="s">
-        <v>45</v>
-      </c>
       <c r="AS7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT7" t="s">
         <v>221</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AU7" t="s">
         <v>440</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>222</v>
       </c>
-      <c r="AV7" t="s">
-        <v>70</v>
-      </c>
       <c r="AW7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX7" t="s">
         <v>134</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AY7" t="s">
         <v>501</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AZ7" t="s">
         <v>223</v>
       </c>
-      <c r="AZ7" t="s">
-        <v>45</v>
-      </c>
       <c r="BA7" t="s">
-        <v>224</v>
+        <v>45</v>
       </c>
       <c r="BB7" t="s">
         <v>224</v>
       </c>
       <c r="BC7" t="s">
+        <v>224</v>
+      </c>
+      <c r="BD7" t="s">
         <v>225</v>
       </c>
-      <c r="BD7" t="s">
-        <v>45</v>
-      </c>
       <c r="BE7" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="BF7" t="s">
         <v>67</v>
       </c>
       <c r="BG7" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH7" t="s">
         <v>226</v>
       </c>
-      <c r="BH7" t="s">
-        <v>45</v>
-      </c>
       <c r="BI7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ7" t="s">
         <v>54</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BK7" t="s">
         <v>305</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BL7" t="s">
         <v>227</v>
       </c>
-      <c r="BL7" t="s">
-        <v>45</v>
-      </c>
       <c r="BM7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN7" t="s">
         <v>228</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BO7" t="s">
         <v>502</v>
       </c>
-      <c r="BO7" t="s">
+      <c r="BP7" t="s">
         <v>229</v>
       </c>
-      <c r="BP7" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ7" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="BR7" t="s">
         <v>71</v>
       </c>
       <c r="BS7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT7" t="s">
         <v>230</v>
       </c>
-      <c r="BT7" t="s">
-        <v>45</v>
-      </c>
       <c r="BU7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV7" t="s">
         <v>231</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="BW7" t="s">
         <v>503</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BX7" t="s">
         <v>232</v>
       </c>
-      <c r="BX7" t="s">
-        <v>45</v>
-      </c>
       <c r="BY7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>54</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CA7" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3993,47 +4000,44 @@
       <c r="AC8" t="s">
         <v>74</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>144</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>248</v>
       </c>
-      <c r="AF8" t="s">
-        <v>45</v>
-      </c>
       <c r="AG8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AH8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI8" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AJ8" t="s">
         <v>249</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>45</v>
-      </c>
       <c r="AK8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AL8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM8" t="s">
         <v>504</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AN8" t="s">
         <v>250</v>
       </c>
-      <c r="AN8" t="s">
-        <v>45</v>
-      </c>
       <c r="AO8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AP8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>150</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>241</v>
       </c>
       <c r="AR8" t="s">
         <v>241</v>
@@ -4042,106 +4046,109 @@
         <v>241</v>
       </c>
       <c r="AT8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU8" t="s">
         <v>94</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AV8" t="s">
         <v>251</v>
       </c>
-      <c r="AV8" t="s">
-        <v>45</v>
-      </c>
       <c r="AW8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AX8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY8" t="s">
         <v>434</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" t="s">
         <v>252</v>
       </c>
-      <c r="AZ8" t="s">
-        <v>45</v>
-      </c>
       <c r="BA8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BB8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC8" t="s">
         <v>289</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BD8" t="s">
         <v>253</v>
       </c>
-      <c r="BD8" t="s">
-        <v>45</v>
-      </c>
       <c r="BE8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BF8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG8" t="s">
         <v>305</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BH8" t="s">
         <v>254</v>
       </c>
-      <c r="BH8" t="s">
-        <v>45</v>
-      </c>
       <c r="BI8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ8" t="s">
         <v>255</v>
       </c>
-      <c r="BJ8" t="s">
+      <c r="BK8" t="s">
         <v>90</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="BL8" t="s">
         <v>256</v>
       </c>
-      <c r="BL8" t="s">
-        <v>45</v>
-      </c>
       <c r="BM8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN8" t="s">
         <v>53</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BO8" t="s">
         <v>402</v>
       </c>
-      <c r="BO8" t="s">
+      <c r="BP8" t="s">
         <v>257</v>
       </c>
-      <c r="BP8" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR8" t="s">
         <v>258</v>
       </c>
-      <c r="BR8" t="s">
+      <c r="BS8" t="s">
         <v>313</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BT8" t="s">
         <v>259</v>
       </c>
-      <c r="BT8" t="s">
-        <v>45</v>
-      </c>
       <c r="BU8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV8" t="s">
         <v>260</v>
       </c>
-      <c r="BV8" t="s">
+      <c r="BW8" t="s">
         <v>440</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="BX8" t="s">
         <v>261</v>
       </c>
-      <c r="BX8" t="s">
-        <v>45</v>
-      </c>
       <c r="BY8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BZ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA8" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="9" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4229,155 +4236,155 @@
       <c r="AC9" t="s">
         <v>58</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>301</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AF9" t="s">
         <v>272</v>
       </c>
-      <c r="AF9" t="s">
-        <v>45</v>
-      </c>
       <c r="AG9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH9" t="s">
         <v>58</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="AI9" t="s">
         <v>469</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>273</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>70</v>
-      </c>
       <c r="AK9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL9" t="s">
         <v>64</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AM9" t="s">
         <v>467</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AN9" t="s">
         <v>274</v>
       </c>
-      <c r="AN9" t="s">
-        <v>45</v>
-      </c>
       <c r="AO9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP9" t="s">
         <v>275</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AQ9" t="s">
         <v>463</v>
       </c>
-      <c r="AQ9" t="s">
+      <c r="AR9" t="s">
         <v>276</v>
       </c>
-      <c r="AR9" t="s">
-        <v>70</v>
-      </c>
       <c r="AS9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT9" t="s">
         <v>64</v>
       </c>
-      <c r="AT9" t="s">
+      <c r="AU9" t="s">
         <v>458</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AV9" t="s">
         <v>277</v>
       </c>
-      <c r="AV9" t="s">
-        <v>70</v>
-      </c>
       <c r="AW9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX9" t="s">
         <v>58</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AY9" t="s">
         <v>462</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" t="s">
         <v>278</v>
       </c>
-      <c r="AZ9" t="s">
-        <v>45</v>
-      </c>
       <c r="BA9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB9" t="s">
         <v>279</v>
       </c>
-      <c r="BB9" t="s">
+      <c r="BC9" t="s">
         <v>464</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BD9" t="s">
         <v>280</v>
       </c>
-      <c r="BD9" t="s">
-        <v>70</v>
-      </c>
       <c r="BE9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF9" t="s">
         <v>281</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BG9" t="s">
         <v>466</v>
       </c>
-      <c r="BG9" t="s">
+      <c r="BH9" t="s">
         <v>282</v>
       </c>
-      <c r="BH9" t="s">
-        <v>45</v>
-      </c>
       <c r="BI9" t="s">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="BJ9" t="s">
         <v>283</v>
       </c>
       <c r="BK9" t="s">
+        <v>283</v>
+      </c>
+      <c r="BL9" t="s">
         <v>284</v>
       </c>
-      <c r="BL9" t="s">
-        <v>45</v>
-      </c>
       <c r="BM9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN9" t="s">
         <v>231</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BO9" t="s">
         <v>465</v>
       </c>
-      <c r="BO9" t="s">
+      <c r="BP9" t="s">
         <v>285</v>
       </c>
-      <c r="BP9" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR9" t="s">
         <v>175</v>
       </c>
-      <c r="BR9" t="s">
+      <c r="BS9" t="s">
         <v>328</v>
       </c>
-      <c r="BS9" t="s">
+      <c r="BT9" t="s">
         <v>286</v>
       </c>
-      <c r="BT9" t="s">
-        <v>70</v>
-      </c>
       <c r="BU9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV9" t="s">
         <v>287</v>
       </c>
-      <c r="BV9" t="s">
+      <c r="BW9" t="s">
         <v>445</v>
       </c>
-      <c r="BW9" t="s">
+      <c r="BX9" t="s">
         <v>288</v>
       </c>
-      <c r="BX9" t="s">
-        <v>45</v>
-      </c>
       <c r="BY9" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="BZ9" t="s">
         <v>289</v>
       </c>
+      <c r="CA9" t="s">
+        <v>289</v>
+      </c>
     </row>
-    <row r="10" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4465,155 +4472,155 @@
       <c r="AC10" t="s">
         <v>301</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="s">
         <v>301</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>302</v>
       </c>
-      <c r="AF10" t="s">
-        <v>70</v>
-      </c>
       <c r="AG10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH10" t="s">
         <v>71</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AI10" t="s">
         <v>477</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="AJ10" t="s">
         <v>303</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>70</v>
-      </c>
       <c r="AK10" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="AL10" t="s">
         <v>136</v>
       </c>
       <c r="AM10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN10" t="s">
         <v>304</v>
       </c>
-      <c r="AN10" t="s">
-        <v>45</v>
-      </c>
       <c r="AO10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP10" t="s">
         <v>305</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AQ10" t="s">
         <v>231</v>
       </c>
-      <c r="AQ10" t="s">
+      <c r="AR10" t="s">
         <v>306</v>
       </c>
-      <c r="AR10" t="s">
-        <v>70</v>
-      </c>
       <c r="AS10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT10" t="s">
         <v>141</v>
       </c>
-      <c r="AT10" t="s">
+      <c r="AU10" t="s">
         <v>471</v>
       </c>
-      <c r="AU10" t="s">
+      <c r="AV10" t="s">
         <v>307</v>
       </c>
-      <c r="AV10" t="s">
-        <v>45</v>
-      </c>
       <c r="AW10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX10" t="s">
         <v>58</v>
       </c>
-      <c r="AX10" t="s">
+      <c r="AY10" t="s">
         <v>473</v>
       </c>
-      <c r="AY10" t="s">
+      <c r="AZ10" t="s">
         <v>308</v>
       </c>
-      <c r="AZ10" t="s">
-        <v>45</v>
-      </c>
       <c r="BA10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB10" t="s">
         <v>155</v>
       </c>
-      <c r="BB10" t="s">
+      <c r="BC10" t="s">
         <v>478</v>
       </c>
-      <c r="BC10" t="s">
+      <c r="BD10" t="s">
         <v>309</v>
       </c>
-      <c r="BD10" t="s">
-        <v>45</v>
-      </c>
       <c r="BE10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF10" t="s">
         <v>289</v>
       </c>
-      <c r="BF10" t="s">
+      <c r="BG10" t="s">
         <v>472</v>
       </c>
-      <c r="BG10" t="s">
+      <c r="BH10" t="s">
         <v>310</v>
       </c>
-      <c r="BH10" t="s">
-        <v>45</v>
-      </c>
       <c r="BI10" t="s">
-        <v>311</v>
+        <v>45</v>
       </c>
       <c r="BJ10" t="s">
         <v>311</v>
       </c>
       <c r="BK10" t="s">
+        <v>311</v>
+      </c>
+      <c r="BL10" t="s">
         <v>312</v>
       </c>
-      <c r="BL10" t="s">
-        <v>70</v>
-      </c>
       <c r="BM10" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN10" t="s">
         <v>313</v>
       </c>
-      <c r="BN10" t="s">
+      <c r="BO10" t="s">
         <v>475</v>
       </c>
-      <c r="BO10" t="s">
+      <c r="BP10" t="s">
         <v>314</v>
       </c>
-      <c r="BP10" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ10" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="BR10" t="s">
         <v>61</v>
       </c>
       <c r="BS10" t="s">
+        <v>61</v>
+      </c>
+      <c r="BT10" t="s">
         <v>315</v>
       </c>
-      <c r="BT10" t="s">
-        <v>45</v>
-      </c>
       <c r="BU10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV10" t="s">
         <v>316</v>
       </c>
-      <c r="BV10" t="s">
+      <c r="BW10" t="s">
         <v>474</v>
       </c>
-      <c r="BW10" t="s">
+      <c r="BX10" t="s">
         <v>317</v>
       </c>
-      <c r="BX10" t="s">
-        <v>45</v>
-      </c>
       <c r="BY10" t="s">
-        <v>318</v>
+        <v>45</v>
       </c>
       <c r="BZ10" t="s">
         <v>318</v>
       </c>
+      <c r="CA10" t="s">
+        <v>318</v>
+      </c>
     </row>
-    <row r="11" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4701,155 +4708,155 @@
       <c r="AC11" t="s">
         <v>58</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AE11" t="s">
         <v>487</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AF11" t="s">
         <v>325</v>
       </c>
-      <c r="AF11" t="s">
-        <v>45</v>
-      </c>
       <c r="AG11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH11" t="s">
         <v>326</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AI11" t="s">
         <v>281</v>
       </c>
-      <c r="AI11" t="s">
+      <c r="AJ11" t="s">
         <v>327</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>70</v>
-      </c>
       <c r="AK11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL11" t="s">
         <v>328</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AM11" t="s">
         <v>482</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AN11" t="s">
         <v>329</v>
       </c>
-      <c r="AN11" t="s">
-        <v>70</v>
-      </c>
       <c r="AO11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP11" t="s">
         <v>208</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AQ11" t="s">
         <v>445</v>
       </c>
-      <c r="AQ11" t="s">
+      <c r="AR11" t="s">
         <v>330</v>
       </c>
-      <c r="AR11" t="s">
-        <v>70</v>
-      </c>
       <c r="AS11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT11" t="s">
         <v>213</v>
       </c>
-      <c r="AT11" t="s">
+      <c r="AU11" t="s">
         <v>481</v>
       </c>
-      <c r="AU11" t="s">
+      <c r="AV11" t="s">
         <v>332</v>
       </c>
-      <c r="AV11" t="s">
-        <v>45</v>
-      </c>
       <c r="AW11" t="s">
-        <v>331</v>
+        <v>45</v>
       </c>
       <c r="AX11" t="s">
         <v>331</v>
       </c>
       <c r="AY11" t="s">
+        <v>331</v>
+      </c>
+      <c r="AZ11" t="s">
         <v>333</v>
       </c>
-      <c r="AZ11" t="s">
-        <v>45</v>
-      </c>
       <c r="BA11" t="s">
-        <v>217</v>
+        <v>45</v>
       </c>
       <c r="BB11" t="s">
         <v>217</v>
       </c>
       <c r="BC11" t="s">
+        <v>217</v>
+      </c>
+      <c r="BD11" t="s">
         <v>334</v>
       </c>
-      <c r="BD11" t="s">
-        <v>45</v>
-      </c>
       <c r="BE11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF11" t="s">
         <v>335</v>
       </c>
-      <c r="BF11" t="s">
+      <c r="BG11" t="s">
         <v>267</v>
       </c>
-      <c r="BG11" t="s">
+      <c r="BH11" t="s">
         <v>336</v>
       </c>
-      <c r="BH11" t="s">
-        <v>45</v>
-      </c>
       <c r="BI11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ11" t="s">
         <v>337</v>
       </c>
-      <c r="BJ11" t="s">
+      <c r="BK11" t="s">
         <v>94</v>
       </c>
-      <c r="BK11" t="s">
+      <c r="BL11" t="s">
         <v>338</v>
       </c>
-      <c r="BL11" t="s">
-        <v>45</v>
-      </c>
       <c r="BM11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN11" t="s">
         <v>260</v>
       </c>
-      <c r="BN11" t="s">
+      <c r="BO11" t="s">
         <v>311</v>
       </c>
-      <c r="BO11" t="s">
+      <c r="BP11" t="s">
         <v>339</v>
       </c>
-      <c r="BP11" t="s">
-        <v>70</v>
-      </c>
       <c r="BQ11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BR11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS11" t="s">
         <v>479</v>
       </c>
-      <c r="BS11" t="s">
+      <c r="BT11" t="s">
         <v>340</v>
       </c>
-      <c r="BT11" t="s">
-        <v>45</v>
-      </c>
       <c r="BU11" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BV11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW11" t="s">
         <v>480</v>
       </c>
-      <c r="BW11" t="s">
+      <c r="BX11" t="s">
         <v>341</v>
       </c>
-      <c r="BX11" t="s">
-        <v>45</v>
-      </c>
       <c r="BY11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ11" t="s">
         <v>172</v>
       </c>
-      <c r="BZ11" t="s">
+      <c r="CA11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4937,155 +4944,155 @@
       <c r="AC12" t="s">
         <v>74</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>289</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AF12" t="s">
         <v>350</v>
       </c>
-      <c r="AF12" t="s">
-        <v>45</v>
-      </c>
       <c r="AG12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH12" t="s">
         <v>58</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AI12" t="s">
         <v>493</v>
       </c>
-      <c r="AI12" t="s">
+      <c r="AJ12" t="s">
         <v>351</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>70</v>
-      </c>
       <c r="AK12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL12" t="s">
         <v>352</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AM12" t="s">
         <v>153</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AN12" t="s">
         <v>353</v>
       </c>
-      <c r="AN12" t="s">
-        <v>45</v>
-      </c>
       <c r="AO12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP12" t="s">
         <v>196</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AQ12" t="s">
         <v>492</v>
       </c>
-      <c r="AQ12" t="s">
+      <c r="AR12" t="s">
         <v>354</v>
       </c>
-      <c r="AR12" t="s">
-        <v>45</v>
-      </c>
       <c r="AS12" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AT12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU12" t="s">
         <v>487</v>
       </c>
-      <c r="AU12" t="s">
+      <c r="AV12" t="s">
         <v>355</v>
       </c>
-      <c r="AV12" t="s">
-        <v>70</v>
-      </c>
       <c r="AW12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AX12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY12" t="s">
         <v>155</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="AZ12" t="s">
         <v>356</v>
       </c>
-      <c r="AZ12" t="s">
-        <v>45</v>
-      </c>
       <c r="BA12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB12" t="s">
         <v>297</v>
       </c>
-      <c r="BB12" t="s">
+      <c r="BC12" t="s">
         <v>86</v>
       </c>
-      <c r="BC12" t="s">
+      <c r="BD12" t="s">
         <v>357</v>
       </c>
-      <c r="BD12" t="s">
-        <v>70</v>
-      </c>
       <c r="BE12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG12" t="s">
         <v>490</v>
       </c>
-      <c r="BG12" t="s">
+      <c r="BH12" t="s">
         <v>358</v>
       </c>
-      <c r="BH12" t="s">
-        <v>45</v>
-      </c>
       <c r="BI12" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BJ12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK12" t="s">
         <v>148</v>
       </c>
-      <c r="BK12" t="s">
+      <c r="BL12" t="s">
         <v>359</v>
       </c>
-      <c r="BL12" t="s">
-        <v>45</v>
-      </c>
       <c r="BM12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN12" t="s">
         <v>90</v>
       </c>
-      <c r="BN12" t="s">
+      <c r="BO12" t="s">
         <v>494</v>
       </c>
-      <c r="BO12" t="s">
+      <c r="BP12" t="s">
         <v>360</v>
       </c>
-      <c r="BP12" t="s">
-        <v>70</v>
-      </c>
       <c r="BQ12" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR12" t="s">
         <v>64</v>
       </c>
-      <c r="BR12" t="s">
+      <c r="BS12" t="s">
         <v>489</v>
       </c>
-      <c r="BS12" t="s">
+      <c r="BT12" t="s">
         <v>361</v>
       </c>
-      <c r="BT12" t="s">
-        <v>45</v>
-      </c>
       <c r="BU12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV12" t="s">
         <v>64</v>
       </c>
-      <c r="BV12" t="s">
+      <c r="BW12" t="s">
         <v>88</v>
       </c>
-      <c r="BW12" t="s">
+      <c r="BX12" t="s">
         <v>362</v>
       </c>
-      <c r="BX12" t="s">
-        <v>45</v>
-      </c>
       <c r="BY12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ12" t="s">
         <v>363</v>
       </c>
-      <c r="BZ12" t="s">
+      <c r="CA12" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="13" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5173,155 +5180,155 @@
       <c r="AC13" t="s">
         <v>74</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="s">
         <v>497</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AF13" t="s">
         <v>376</v>
       </c>
-      <c r="AF13" t="s">
-        <v>70</v>
-      </c>
       <c r="AG13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AH13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="s">
         <v>495</v>
       </c>
-      <c r="AI13" t="s">
+      <c r="AJ13" t="s">
         <v>377</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>45</v>
-      </c>
       <c r="AK13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AL13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM13" t="s">
         <v>498</v>
       </c>
-      <c r="AM13" t="s">
+      <c r="AN13" t="s">
         <v>378</v>
       </c>
-      <c r="AN13" t="s">
-        <v>70</v>
-      </c>
       <c r="AO13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>440</v>
       </c>
-      <c r="AQ13" t="s">
+      <c r="AR13" t="s">
         <v>379</v>
       </c>
-      <c r="AR13" t="s">
-        <v>45</v>
-      </c>
       <c r="AS13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AT13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU13" t="s">
         <v>305</v>
       </c>
-      <c r="AU13" t="s">
+      <c r="AV13" t="s">
         <v>380</v>
       </c>
-      <c r="AV13" t="s">
-        <v>45</v>
-      </c>
       <c r="AW13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AX13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY13" t="s">
         <v>209</v>
       </c>
-      <c r="AY13" t="s">
+      <c r="AZ13" t="s">
         <v>381</v>
       </c>
-      <c r="AZ13" t="s">
-        <v>45</v>
-      </c>
       <c r="BA13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BB13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC13" t="s">
         <v>499</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BD13" t="s">
         <v>382</v>
       </c>
-      <c r="BD13" t="s">
-        <v>45</v>
-      </c>
       <c r="BE13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BF13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG13" t="s">
         <v>71</v>
       </c>
-      <c r="BG13" t="s">
+      <c r="BH13" t="s">
         <v>383</v>
       </c>
-      <c r="BH13" t="s">
-        <v>45</v>
-      </c>
       <c r="BI13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BJ13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK13" t="s">
         <v>500</v>
       </c>
-      <c r="BK13" t="s">
+      <c r="BL13" t="s">
         <v>384</v>
       </c>
-      <c r="BL13" t="s">
-        <v>70</v>
-      </c>
       <c r="BM13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BN13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO13" t="s">
         <v>224</v>
       </c>
-      <c r="BO13" t="s">
+      <c r="BP13" t="s">
         <v>385</v>
       </c>
-      <c r="BP13" t="s">
-        <v>70</v>
-      </c>
       <c r="BQ13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BR13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS13" t="s">
         <v>502</v>
       </c>
-      <c r="BS13" t="s">
+      <c r="BT13" t="s">
         <v>386</v>
       </c>
-      <c r="BT13" t="s">
-        <v>70</v>
-      </c>
       <c r="BU13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BV13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW13" t="s">
         <v>67</v>
       </c>
-      <c r="BW13" t="s">
+      <c r="BX13" t="s">
         <v>387</v>
       </c>
-      <c r="BX13" t="s">
-        <v>45</v>
-      </c>
       <c r="BY13" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BZ13" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA13" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5409,155 +5416,155 @@
       <c r="AC14" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AE14" t="s">
         <v>471</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AF14" t="s">
         <v>401</v>
       </c>
-      <c r="AF14" t="s">
-        <v>45</v>
-      </c>
       <c r="AG14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH14" t="s">
         <v>402</v>
       </c>
-      <c r="AH14" t="s">
+      <c r="AI14" t="s">
         <v>470</v>
       </c>
-      <c r="AI14" t="s">
+      <c r="AJ14" t="s">
         <v>403</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>45</v>
-      </c>
       <c r="AK14" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AL14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM14" t="s">
         <v>231</v>
       </c>
-      <c r="AM14" t="s">
+      <c r="AN14" t="s">
         <v>404</v>
       </c>
-      <c r="AN14" t="s">
-        <v>45</v>
-      </c>
       <c r="AO14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP14" t="s">
         <v>58</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AQ14" t="s">
         <v>474</v>
       </c>
-      <c r="AQ14" t="s">
+      <c r="AR14" t="s">
         <v>405</v>
       </c>
-      <c r="AR14" t="s">
-        <v>45</v>
-      </c>
       <c r="AS14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT14" t="s">
         <v>58</v>
       </c>
-      <c r="AT14" t="s">
+      <c r="AU14" t="s">
         <v>318</v>
       </c>
-      <c r="AU14" t="s">
+      <c r="AV14" t="s">
         <v>406</v>
       </c>
-      <c r="AV14" t="s">
-        <v>45</v>
-      </c>
       <c r="AW14" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AX14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY14" t="s">
         <v>301</v>
       </c>
-      <c r="AY14" t="s">
+      <c r="AZ14" t="s">
         <v>407</v>
       </c>
-      <c r="AZ14" t="s">
-        <v>45</v>
-      </c>
       <c r="BA14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB14" t="s">
         <v>64</v>
       </c>
-      <c r="BB14" t="s">
+      <c r="BC14" t="s">
         <v>475</v>
       </c>
-      <c r="BC14" t="s">
+      <c r="BD14" t="s">
         <v>408</v>
       </c>
-      <c r="BD14" t="s">
-        <v>45</v>
-      </c>
       <c r="BE14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF14" t="s">
         <v>64</v>
       </c>
-      <c r="BF14" t="s">
+      <c r="BG14" t="s">
         <v>472</v>
       </c>
-      <c r="BG14" t="s">
+      <c r="BH14" t="s">
         <v>409</v>
       </c>
-      <c r="BH14" t="s">
-        <v>45</v>
-      </c>
       <c r="BI14" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BJ14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK14" t="s">
         <v>136</v>
       </c>
-      <c r="BK14" t="s">
+      <c r="BL14" t="s">
         <v>410</v>
       </c>
-      <c r="BL14" t="s">
-        <v>45</v>
-      </c>
       <c r="BM14" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BN14" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO14" t="s">
         <v>219</v>
       </c>
-      <c r="BO14" t="s">
+      <c r="BP14" t="s">
         <v>411</v>
       </c>
-      <c r="BP14" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR14" t="s">
         <v>64</v>
       </c>
-      <c r="BR14" t="s">
+      <c r="BS14" t="s">
         <v>138</v>
       </c>
-      <c r="BS14" t="s">
+      <c r="BT14" t="s">
         <v>412</v>
       </c>
-      <c r="BT14" t="s">
-        <v>45</v>
-      </c>
       <c r="BU14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV14" t="s">
         <v>172</v>
       </c>
-      <c r="BV14" t="s">
+      <c r="BW14" t="s">
         <v>478</v>
       </c>
-      <c r="BW14" t="s">
+      <c r="BX14" t="s">
         <v>413</v>
       </c>
-      <c r="BX14" t="s">
-        <v>45</v>
-      </c>
       <c r="BY14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ14" t="s">
         <v>414</v>
       </c>
-      <c r="BZ14" t="s">
+      <c r="CA14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="15" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5645,151 +5652,151 @@
       <c r="AC15" t="s">
         <v>74</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AE15" t="s">
         <v>305</v>
       </c>
-      <c r="AE15" t="s">
+      <c r="AF15" t="s">
         <v>421</v>
       </c>
-      <c r="AF15" t="s">
-        <v>45</v>
-      </c>
       <c r="AG15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AH15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI15" t="s">
         <v>455</v>
       </c>
-      <c r="AI15" t="s">
+      <c r="AJ15" t="s">
         <v>422</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>45</v>
-      </c>
       <c r="AK15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AL15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM15" t="s">
         <v>402</v>
       </c>
-      <c r="AM15" t="s">
+      <c r="AN15" t="s">
         <v>423</v>
       </c>
-      <c r="AN15" t="s">
-        <v>45</v>
-      </c>
       <c r="AO15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AP15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ15" t="s">
         <v>442</v>
       </c>
-      <c r="AQ15" t="s">
+      <c r="AR15" t="s">
         <v>424</v>
       </c>
-      <c r="AR15" t="s">
-        <v>45</v>
-      </c>
       <c r="AS15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="AT15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU15" t="s">
         <v>451</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AV15" t="s">
         <v>425</v>
       </c>
-      <c r="AV15" t="s">
-        <v>45</v>
-      </c>
       <c r="AW15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX15" t="s">
         <v>255</v>
       </c>
-      <c r="AX15" t="s">
+      <c r="AY15" t="s">
         <v>90</v>
       </c>
-      <c r="AY15" t="s">
+      <c r="AZ15" t="s">
         <v>426</v>
       </c>
-      <c r="AZ15" t="s">
-        <v>45</v>
-      </c>
       <c r="BA15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BB15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC15" t="s">
         <v>478</v>
       </c>
-      <c r="BC15" t="s">
+      <c r="BD15" t="s">
         <v>427</v>
       </c>
-      <c r="BD15" t="s">
-        <v>45</v>
-      </c>
       <c r="BE15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BF15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG15" t="s">
         <v>289</v>
       </c>
-      <c r="BG15" t="s">
+      <c r="BH15" t="s">
         <v>428</v>
       </c>
-      <c r="BH15" t="s">
-        <v>45</v>
-      </c>
       <c r="BI15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ15" t="s">
         <v>432</v>
       </c>
-      <c r="BJ15" t="s">
+      <c r="BK15" t="s">
         <v>155</v>
       </c>
-      <c r="BK15" t="s">
+      <c r="BL15" t="s">
         <v>429</v>
       </c>
-      <c r="BL15" t="s">
-        <v>45</v>
-      </c>
       <c r="BM15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BN15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO15" t="s">
         <v>56</v>
       </c>
-      <c r="BO15" t="s">
+      <c r="BP15" t="s">
         <v>433</v>
       </c>
-      <c r="BP15" t="s">
-        <v>45</v>
-      </c>
       <c r="BQ15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BR15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS15" t="s">
         <v>447</v>
       </c>
-      <c r="BS15" t="s">
+      <c r="BT15" t="s">
         <v>430</v>
       </c>
-      <c r="BT15" t="s">
-        <v>45</v>
-      </c>
       <c r="BU15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BV15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW15" t="s">
         <v>144</v>
       </c>
-      <c r="BW15" t="s">
+      <c r="BX15" t="s">
         <v>431</v>
       </c>
-      <c r="BX15" t="s">
-        <v>45</v>
-      </c>
       <c r="BY15" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="BZ15" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA15" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6059,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="T2" t="str">
-        <f>'During Experiment'!AF2</f>
+        <f>'During Experiment'!AG2</f>
         <v>N</v>
       </c>
       <c r="U2" t="s">
@@ -6069,7 +6076,7 @@
         <v>70</v>
       </c>
       <c r="W2" t="str">
-        <f>'During Experiment'!AJ2</f>
+        <f>'During Experiment'!AK2</f>
         <v>N</v>
       </c>
       <c r="X2" t="s">
@@ -6079,7 +6086,7 @@
         <v>70</v>
       </c>
       <c r="Z2" t="str">
-        <f>'During Experiment'!AN2</f>
+        <f>'During Experiment'!AO2</f>
         <v>J</v>
       </c>
       <c r="AA2" t="s">
@@ -6089,7 +6096,7 @@
         <v>70</v>
       </c>
       <c r="AC2" t="str">
-        <f>'During Experiment'!AR2</f>
+        <f>'During Experiment'!AS2</f>
         <v>N</v>
       </c>
       <c r="AD2" t="s">
@@ -6099,7 +6106,7 @@
         <v>45</v>
       </c>
       <c r="AF2" t="str">
-        <f>'During Experiment'!AV2</f>
+        <f>'During Experiment'!AW2</f>
         <v>N</v>
       </c>
       <c r="AG2" t="s">
@@ -6109,7 +6116,7 @@
         <v>70</v>
       </c>
       <c r="AI2" t="str">
-        <f>'During Experiment'!AZ2</f>
+        <f>'During Experiment'!BA2</f>
         <v>N</v>
       </c>
       <c r="AJ2" t="s">
@@ -6119,7 +6126,7 @@
         <v>70</v>
       </c>
       <c r="AL2" t="str">
-        <f>'During Experiment'!BD2</f>
+        <f>'During Experiment'!BE2</f>
         <v>N</v>
       </c>
       <c r="AM2" t="s">
@@ -6129,7 +6136,7 @@
         <v>70</v>
       </c>
       <c r="AO2" t="str">
-        <f>'During Experiment'!BH2</f>
+        <f>'During Experiment'!BI2</f>
         <v>N</v>
       </c>
       <c r="AP2" t="s">
@@ -6139,7 +6146,7 @@
         <v>70</v>
       </c>
       <c r="AR2" t="str">
-        <f>'During Experiment'!BL2</f>
+        <f>'During Experiment'!BM2</f>
         <v>N</v>
       </c>
       <c r="AS2" t="s">
@@ -6149,7 +6156,7 @@
         <v>70</v>
       </c>
       <c r="AU2" t="str">
-        <f>'During Experiment'!BP2</f>
+        <f>'During Experiment'!BQ2</f>
         <v>J</v>
       </c>
       <c r="AV2" t="s">
@@ -6159,7 +6166,7 @@
         <v>70</v>
       </c>
       <c r="AX2" t="str">
-        <f>'During Experiment'!BT2</f>
+        <f>'During Experiment'!BU2</f>
         <v>N</v>
       </c>
       <c r="AY2" t="s">
@@ -6169,7 +6176,7 @@
         <v>70</v>
       </c>
       <c r="BA2" t="str">
-        <f>'During Experiment'!BX2</f>
+        <f>'During Experiment'!BY2</f>
         <v>N</v>
       </c>
       <c r="BB2" t="s">
@@ -6244,7 +6251,7 @@
         <v>45</v>
       </c>
       <c r="T3" t="str">
-        <f>'During Experiment'!AF3</f>
+        <f>'During Experiment'!AG3</f>
         <v>N</v>
       </c>
       <c r="U3" t="s">
@@ -6254,7 +6261,7 @@
         <v>45</v>
       </c>
       <c r="W3" t="str">
-        <f>'During Experiment'!AJ3</f>
+        <f>'During Experiment'!AK3</f>
         <v>J</v>
       </c>
       <c r="X3" t="s">
@@ -6264,7 +6271,7 @@
         <v>45</v>
       </c>
       <c r="Z3" t="str">
-        <f>'During Experiment'!AN3</f>
+        <f>'During Experiment'!AO3</f>
         <v>N</v>
       </c>
       <c r="AA3" t="s">
@@ -6274,7 +6281,7 @@
         <v>45</v>
       </c>
       <c r="AC3" t="str">
-        <f>'During Experiment'!AR3</f>
+        <f>'During Experiment'!AS3</f>
         <v>J</v>
       </c>
       <c r="AD3" t="s">
@@ -6284,7 +6291,7 @@
         <v>45</v>
       </c>
       <c r="AF3" t="str">
-        <f>'During Experiment'!AV3</f>
+        <f>'During Experiment'!AW3</f>
         <v>J</v>
       </c>
       <c r="AG3" t="s">
@@ -6294,7 +6301,7 @@
         <v>45</v>
       </c>
       <c r="AI3" t="str">
-        <f>'During Experiment'!AZ3</f>
+        <f>'During Experiment'!BA3</f>
         <v>J</v>
       </c>
       <c r="AJ3" t="s">
@@ -6304,7 +6311,7 @@
         <v>45</v>
       </c>
       <c r="AL3" t="str">
-        <f>'During Experiment'!BD3</f>
+        <f>'During Experiment'!BE3</f>
         <v>N</v>
       </c>
       <c r="AM3" t="s">
@@ -6314,7 +6321,7 @@
         <v>45</v>
       </c>
       <c r="AO3" t="str">
-        <f>'During Experiment'!BH3</f>
+        <f>'During Experiment'!BI3</f>
         <v>N</v>
       </c>
       <c r="AP3" t="s">
@@ -6324,7 +6331,7 @@
         <v>45</v>
       </c>
       <c r="AR3" t="str">
-        <f>'During Experiment'!BL3</f>
+        <f>'During Experiment'!BM3</f>
         <v>N</v>
       </c>
       <c r="AS3" t="s">
@@ -6334,7 +6341,7 @@
         <v>70</v>
       </c>
       <c r="AU3" t="str">
-        <f>'During Experiment'!BP3</f>
+        <f>'During Experiment'!BQ3</f>
         <v>N</v>
       </c>
       <c r="AV3" t="s">
@@ -6344,7 +6351,7 @@
         <v>45</v>
       </c>
       <c r="AX3" t="str">
-        <f>'During Experiment'!BT3</f>
+        <f>'During Experiment'!BU3</f>
         <v>J</v>
       </c>
       <c r="AY3" t="s">
@@ -6354,7 +6361,7 @@
         <v>45</v>
       </c>
       <c r="BA3" t="str">
-        <f>'During Experiment'!BX3</f>
+        <f>'During Experiment'!BY3</f>
         <v>N</v>
       </c>
       <c r="BB3" t="s">
@@ -6429,7 +6436,7 @@
         <v>70</v>
       </c>
       <c r="T4" t="str">
-        <f>'During Experiment'!AF4</f>
+        <f>'During Experiment'!AG4</f>
         <v>N</v>
       </c>
       <c r="U4" t="s">
@@ -6439,7 +6446,7 @@
         <v>70</v>
       </c>
       <c r="W4" t="str">
-        <f>'During Experiment'!AJ4</f>
+        <f>'During Experiment'!AK4</f>
         <v>N</v>
       </c>
       <c r="X4" t="s">
@@ -6449,7 +6456,7 @@
         <v>70</v>
       </c>
       <c r="Z4" t="str">
-        <f>'During Experiment'!AN4</f>
+        <f>'During Experiment'!AO4</f>
         <v>N</v>
       </c>
       <c r="AA4" t="s">
@@ -6459,7 +6466,7 @@
         <v>70</v>
       </c>
       <c r="AC4" t="str">
-        <f>'During Experiment'!AR4</f>
+        <f>'During Experiment'!AS4</f>
         <v>N</v>
       </c>
       <c r="AD4" t="s">
@@ -6469,7 +6476,7 @@
         <v>70</v>
       </c>
       <c r="AF4" t="str">
-        <f>'During Experiment'!AV4</f>
+        <f>'During Experiment'!AW4</f>
         <v>N</v>
       </c>
       <c r="AG4" t="s">
@@ -6479,7 +6486,7 @@
         <v>70</v>
       </c>
       <c r="AI4" t="str">
-        <f>'During Experiment'!AZ4</f>
+        <f>'During Experiment'!BA4</f>
         <v>N</v>
       </c>
       <c r="AJ4" t="s">
@@ -6489,7 +6496,7 @@
         <v>70</v>
       </c>
       <c r="AL4" t="str">
-        <f>'During Experiment'!BD4</f>
+        <f>'During Experiment'!BE4</f>
         <v>N</v>
       </c>
       <c r="AM4" t="s">
@@ -6499,7 +6506,7 @@
         <v>70</v>
       </c>
       <c r="AO4" t="str">
-        <f>'During Experiment'!BH4</f>
+        <f>'During Experiment'!BI4</f>
         <v>N</v>
       </c>
       <c r="AP4" t="s">
@@ -6509,7 +6516,7 @@
         <v>70</v>
       </c>
       <c r="AR4" t="str">
-        <f>'During Experiment'!BL4</f>
+        <f>'During Experiment'!BM4</f>
         <v>N</v>
       </c>
       <c r="AS4" t="s">
@@ -6519,7 +6526,7 @@
         <v>70</v>
       </c>
       <c r="AU4" t="str">
-        <f>'During Experiment'!BP4</f>
+        <f>'During Experiment'!BQ4</f>
         <v>J</v>
       </c>
       <c r="AV4" t="s">
@@ -6529,7 +6536,7 @@
         <v>70</v>
       </c>
       <c r="AX4" t="str">
-        <f>'During Experiment'!BT4</f>
+        <f>'During Experiment'!BU4</f>
         <v>N</v>
       </c>
       <c r="AY4" t="s">
@@ -6539,7 +6546,7 @@
         <v>70</v>
       </c>
       <c r="BA4" t="str">
-        <f>'During Experiment'!BX4</f>
+        <f>'During Experiment'!BY4</f>
         <v>N</v>
       </c>
       <c r="BB4" t="s">
@@ -6614,7 +6621,7 @@
         <v>70</v>
       </c>
       <c r="T5" t="str">
-        <f>'During Experiment'!AF5</f>
+        <f>'During Experiment'!AG5</f>
         <v>N</v>
       </c>
       <c r="U5" t="s">
@@ -6624,7 +6631,7 @@
         <v>45</v>
       </c>
       <c r="W5" t="str">
-        <f>'During Experiment'!AJ5</f>
+        <f>'During Experiment'!AK5</f>
         <v>N</v>
       </c>
       <c r="X5" t="s">
@@ -6634,7 +6641,7 @@
         <v>70</v>
       </c>
       <c r="Z5" t="str">
-        <f>'During Experiment'!AN5</f>
+        <f>'During Experiment'!AO5</f>
         <v>N</v>
       </c>
       <c r="AA5" t="s">
@@ -6644,7 +6651,7 @@
         <v>45</v>
       </c>
       <c r="AC5" t="str">
-        <f>'During Experiment'!AR5</f>
+        <f>'During Experiment'!AS5</f>
         <v>N</v>
       </c>
       <c r="AD5" t="s">
@@ -6654,7 +6661,7 @@
         <v>70</v>
       </c>
       <c r="AF5" t="str">
-        <f>'During Experiment'!AV5</f>
+        <f>'During Experiment'!AW5</f>
         <v>N</v>
       </c>
       <c r="AG5" t="s">
@@ -6664,7 +6671,7 @@
         <v>45</v>
       </c>
       <c r="AI5" t="str">
-        <f>'During Experiment'!AZ5</f>
+        <f>'During Experiment'!BA5</f>
         <v>J</v>
       </c>
       <c r="AJ5" t="s">
@@ -6674,7 +6681,7 @@
         <v>45</v>
       </c>
       <c r="AL5" t="str">
-        <f>'During Experiment'!BD5</f>
+        <f>'During Experiment'!BE5</f>
         <v>J</v>
       </c>
       <c r="AM5" t="s">
@@ -6684,7 +6691,7 @@
         <v>45</v>
       </c>
       <c r="AO5" t="str">
-        <f>'During Experiment'!BH5</f>
+        <f>'During Experiment'!BI5</f>
         <v>N</v>
       </c>
       <c r="AP5" t="s">
@@ -6694,7 +6701,7 @@
         <v>45</v>
       </c>
       <c r="AR5" t="str">
-        <f>'During Experiment'!BL5</f>
+        <f>'During Experiment'!BM5</f>
         <v>J</v>
       </c>
       <c r="AS5" t="s">
@@ -6704,7 +6711,7 @@
         <v>45</v>
       </c>
       <c r="AU5" t="str">
-        <f>'During Experiment'!BP5</f>
+        <f>'During Experiment'!BQ5</f>
         <v>N</v>
       </c>
       <c r="AV5" t="s">
@@ -6714,7 +6721,7 @@
         <v>45</v>
       </c>
       <c r="AX5" t="str">
-        <f>'During Experiment'!BT5</f>
+        <f>'During Experiment'!BU5</f>
         <v>N</v>
       </c>
       <c r="AY5" t="s">
@@ -6724,7 +6731,7 @@
         <v>45</v>
       </c>
       <c r="BA5" t="str">
-        <f>'During Experiment'!BX5</f>
+        <f>'During Experiment'!BY5</f>
         <v>N</v>
       </c>
       <c r="BB5" t="s">
@@ -6799,7 +6806,7 @@
         <v>45</v>
       </c>
       <c r="T6" t="str">
-        <f>'During Experiment'!AF6</f>
+        <f>'During Experiment'!AG6</f>
         <v>N</v>
       </c>
       <c r="U6" t="s">
@@ -6809,7 +6816,7 @@
         <v>45</v>
       </c>
       <c r="W6" t="str">
-        <f>'During Experiment'!AJ6</f>
+        <f>'During Experiment'!AK6</f>
         <v>N</v>
       </c>
       <c r="X6" t="s">
@@ -6819,7 +6826,7 @@
         <v>45</v>
       </c>
       <c r="Z6" t="str">
-        <f>'During Experiment'!AN6</f>
+        <f>'During Experiment'!AO6</f>
         <v>J</v>
       </c>
       <c r="AA6" t="s">
@@ -6829,7 +6836,7 @@
         <v>45</v>
       </c>
       <c r="AC6" t="str">
-        <f>'During Experiment'!AR6</f>
+        <f>'During Experiment'!AS6</f>
         <v>J</v>
       </c>
       <c r="AD6" t="s">
@@ -6839,7 +6846,7 @@
         <v>45</v>
       </c>
       <c r="AF6" t="str">
-        <f>'During Experiment'!AV6</f>
+        <f>'During Experiment'!AW6</f>
         <v>N</v>
       </c>
       <c r="AG6" t="s">
@@ -6849,7 +6856,7 @@
         <v>45</v>
       </c>
       <c r="AI6" t="str">
-        <f>'During Experiment'!AZ6</f>
+        <f>'During Experiment'!BA6</f>
         <v>N</v>
       </c>
       <c r="AJ6" t="s">
@@ -6859,7 +6866,7 @@
         <v>45</v>
       </c>
       <c r="AL6" t="str">
-        <f>'During Experiment'!BD6</f>
+        <f>'During Experiment'!BE6</f>
         <v>N</v>
       </c>
       <c r="AM6" t="s">
@@ -6869,7 +6876,7 @@
         <v>45</v>
       </c>
       <c r="AO6" t="str">
-        <f>'During Experiment'!BH6</f>
+        <f>'During Experiment'!BI6</f>
         <v>N</v>
       </c>
       <c r="AP6" t="s">
@@ -6879,7 +6886,7 @@
         <v>45</v>
       </c>
       <c r="AR6" t="str">
-        <f>'During Experiment'!BL6</f>
+        <f>'During Experiment'!BM6</f>
         <v>J</v>
       </c>
       <c r="AS6" t="s">
@@ -6889,7 +6896,7 @@
         <v>45</v>
       </c>
       <c r="AU6" t="str">
-        <f>'During Experiment'!BP6</f>
+        <f>'During Experiment'!BQ6</f>
         <v>N</v>
       </c>
       <c r="AV6" t="s">
@@ -6899,7 +6906,7 @@
         <v>70</v>
       </c>
       <c r="AX6" t="str">
-        <f>'During Experiment'!BT6</f>
+        <f>'During Experiment'!BU6</f>
         <v>J</v>
       </c>
       <c r="AY6" t="s">
@@ -6909,7 +6916,7 @@
         <v>45</v>
       </c>
       <c r="BA6" t="str">
-        <f>'During Experiment'!BX6</f>
+        <f>'During Experiment'!BY6</f>
         <v>N</v>
       </c>
       <c r="BB6" t="s">
@@ -6984,7 +6991,7 @@
         <v>45</v>
       </c>
       <c r="T7" t="str">
-        <f>'During Experiment'!AF7</f>
+        <f>'During Experiment'!AG7</f>
         <v>N</v>
       </c>
       <c r="U7" t="s">
@@ -6994,7 +7001,7 @@
         <v>70</v>
       </c>
       <c r="W7" t="str">
-        <f>'During Experiment'!AJ7</f>
+        <f>'During Experiment'!AK7</f>
         <v>N</v>
       </c>
       <c r="X7" t="s">
@@ -7004,7 +7011,7 @@
         <v>70</v>
       </c>
       <c r="Z7" t="str">
-        <f>'During Experiment'!AN7</f>
+        <f>'During Experiment'!AO7</f>
         <v>N</v>
       </c>
       <c r="AA7" t="s">
@@ -7014,7 +7021,7 @@
         <v>70</v>
       </c>
       <c r="AC7" t="str">
-        <f>'During Experiment'!AR7</f>
+        <f>'During Experiment'!AS7</f>
         <v>N</v>
       </c>
       <c r="AD7" t="s">
@@ -7024,7 +7031,7 @@
         <v>45</v>
       </c>
       <c r="AF7" t="str">
-        <f>'During Experiment'!AV7</f>
+        <f>'During Experiment'!AW7</f>
         <v>J</v>
       </c>
       <c r="AG7" t="s">
@@ -7034,7 +7041,7 @@
         <v>45</v>
       </c>
       <c r="AI7" t="str">
-        <f>'During Experiment'!AZ7</f>
+        <f>'During Experiment'!BA7</f>
         <v>N</v>
       </c>
       <c r="AJ7" t="s">
@@ -7044,7 +7051,7 @@
         <v>70</v>
       </c>
       <c r="AL7" t="str">
-        <f>'During Experiment'!BD7</f>
+        <f>'During Experiment'!BE7</f>
         <v>N</v>
       </c>
       <c r="AM7" t="s">
@@ -7054,7 +7061,7 @@
         <v>70</v>
       </c>
       <c r="AO7" t="str">
-        <f>'During Experiment'!BH7</f>
+        <f>'During Experiment'!BI7</f>
         <v>N</v>
       </c>
       <c r="AP7" t="s">
@@ -7064,7 +7071,7 @@
         <v>45</v>
       </c>
       <c r="AR7" t="str">
-        <f>'During Experiment'!BL7</f>
+        <f>'During Experiment'!BM7</f>
         <v>N</v>
       </c>
       <c r="AS7" t="s">
@@ -7074,7 +7081,7 @@
         <v>45</v>
       </c>
       <c r="AU7" t="str">
-        <f>'During Experiment'!BP7</f>
+        <f>'During Experiment'!BQ7</f>
         <v>N</v>
       </c>
       <c r="AV7" t="s">
@@ -7084,7 +7091,7 @@
         <v>70</v>
       </c>
       <c r="AX7" t="str">
-        <f>'During Experiment'!BT7</f>
+        <f>'During Experiment'!BU7</f>
         <v>N</v>
       </c>
       <c r="AY7" t="s">
@@ -7094,7 +7101,7 @@
         <v>70</v>
       </c>
       <c r="BA7" t="str">
-        <f>'During Experiment'!BX7</f>
+        <f>'During Experiment'!BY7</f>
         <v>N</v>
       </c>
       <c r="BB7" t="s">
@@ -7169,7 +7176,7 @@
         <v>45</v>
       </c>
       <c r="T8" t="str">
-        <f>'During Experiment'!AF8</f>
+        <f>'During Experiment'!AG8</f>
         <v>N</v>
       </c>
       <c r="U8" t="s">
@@ -7179,7 +7186,7 @@
         <v>45</v>
       </c>
       <c r="W8" t="str">
-        <f>'During Experiment'!AJ8</f>
+        <f>'During Experiment'!AK8</f>
         <v>N</v>
       </c>
       <c r="X8" t="s">
@@ -7189,7 +7196,7 @@
         <v>45</v>
       </c>
       <c r="Z8" t="str">
-        <f>'During Experiment'!AN8</f>
+        <f>'During Experiment'!AO8</f>
         <v>N</v>
       </c>
       <c r="AA8" t="s">
@@ -7199,7 +7206,7 @@
         <v>45</v>
       </c>
       <c r="AC8" t="str">
-        <f>'During Experiment'!AR8</f>
+        <f>'During Experiment'!AS8</f>
         <v>INVALID</v>
       </c>
       <c r="AD8" t="s">
@@ -7209,7 +7216,7 @@
         <v>45</v>
       </c>
       <c r="AF8" t="str">
-        <f>'During Experiment'!AV8</f>
+        <f>'During Experiment'!AW8</f>
         <v>N</v>
       </c>
       <c r="AG8" t="s">
@@ -7219,7 +7226,7 @@
         <v>45</v>
       </c>
       <c r="AI8" t="str">
-        <f>'During Experiment'!AZ8</f>
+        <f>'During Experiment'!BA8</f>
         <v>N</v>
       </c>
       <c r="AJ8" t="s">
@@ -7229,7 +7236,7 @@
         <v>45</v>
       </c>
       <c r="AL8" t="str">
-        <f>'During Experiment'!BD8</f>
+        <f>'During Experiment'!BE8</f>
         <v>N</v>
       </c>
       <c r="AM8" t="s">
@@ -7239,7 +7246,7 @@
         <v>45</v>
       </c>
       <c r="AO8" t="str">
-        <f>'During Experiment'!BH8</f>
+        <f>'During Experiment'!BI8</f>
         <v>N</v>
       </c>
       <c r="AP8" t="s">
@@ -7249,7 +7256,7 @@
         <v>45</v>
       </c>
       <c r="AR8" t="str">
-        <f>'During Experiment'!BL8</f>
+        <f>'During Experiment'!BM8</f>
         <v>N</v>
       </c>
       <c r="AS8" t="s">
@@ -7259,7 +7266,7 @@
         <v>45</v>
       </c>
       <c r="AU8" t="str">
-        <f>'During Experiment'!BP8</f>
+        <f>'During Experiment'!BQ8</f>
         <v>N</v>
       </c>
       <c r="AV8" t="s">
@@ -7269,7 +7276,7 @@
         <v>45</v>
       </c>
       <c r="AX8" t="str">
-        <f>'During Experiment'!BT8</f>
+        <f>'During Experiment'!BU8</f>
         <v>N</v>
       </c>
       <c r="AY8" t="s">
@@ -7279,7 +7286,7 @@
         <v>45</v>
       </c>
       <c r="BA8" t="str">
-        <f>'During Experiment'!BX8</f>
+        <f>'During Experiment'!BY8</f>
         <v>N</v>
       </c>
       <c r="BB8" t="s">
@@ -7354,7 +7361,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="str">
-        <f>'During Experiment'!AF9</f>
+        <f>'During Experiment'!AG9</f>
         <v>N</v>
       </c>
       <c r="U9" t="s">
@@ -7364,7 +7371,7 @@
         <v>70</v>
       </c>
       <c r="W9" t="str">
-        <f>'During Experiment'!AJ9</f>
+        <f>'During Experiment'!AK9</f>
         <v>J</v>
       </c>
       <c r="X9" t="s">
@@ -7374,7 +7381,7 @@
         <v>70</v>
       </c>
       <c r="Z9" t="str">
-        <f>'During Experiment'!AN9</f>
+        <f>'During Experiment'!AO9</f>
         <v>N</v>
       </c>
       <c r="AA9" t="s">
@@ -7384,7 +7391,7 @@
         <v>70</v>
       </c>
       <c r="AC9" t="str">
-        <f>'During Experiment'!AR9</f>
+        <f>'During Experiment'!AS9</f>
         <v>J</v>
       </c>
       <c r="AD9" t="s">
@@ -7394,7 +7401,7 @@
         <v>70</v>
       </c>
       <c r="AF9" t="str">
-        <f>'During Experiment'!AV9</f>
+        <f>'During Experiment'!AW9</f>
         <v>J</v>
       </c>
       <c r="AG9" t="s">
@@ -7404,7 +7411,7 @@
         <v>70</v>
       </c>
       <c r="AI9" t="str">
-        <f>'During Experiment'!AZ9</f>
+        <f>'During Experiment'!BA9</f>
         <v>N</v>
       </c>
       <c r="AJ9" t="s">
@@ -7414,7 +7421,7 @@
         <v>70</v>
       </c>
       <c r="AL9" t="str">
-        <f>'During Experiment'!BD9</f>
+        <f>'During Experiment'!BE9</f>
         <v>J</v>
       </c>
       <c r="AM9" t="s">
@@ -7424,7 +7431,7 @@
         <v>70</v>
       </c>
       <c r="AO9" t="str">
-        <f>'During Experiment'!BH9</f>
+        <f>'During Experiment'!BI9</f>
         <v>N</v>
       </c>
       <c r="AP9" t="s">
@@ -7434,7 +7441,7 @@
         <v>70</v>
       </c>
       <c r="AR9" t="str">
-        <f>'During Experiment'!BL9</f>
+        <f>'During Experiment'!BM9</f>
         <v>N</v>
       </c>
       <c r="AS9" t="s">
@@ -7444,7 +7451,7 @@
         <v>70</v>
       </c>
       <c r="AU9" t="str">
-        <f>'During Experiment'!BP9</f>
+        <f>'During Experiment'!BQ9</f>
         <v>N</v>
       </c>
       <c r="AV9" t="s">
@@ -7454,7 +7461,7 @@
         <v>45</v>
       </c>
       <c r="AX9" t="str">
-        <f>'During Experiment'!BT9</f>
+        <f>'During Experiment'!BU9</f>
         <v>J</v>
       </c>
       <c r="AY9" t="s">
@@ -7464,7 +7471,7 @@
         <v>70</v>
       </c>
       <c r="BA9" t="str">
-        <f>'During Experiment'!BX9</f>
+        <f>'During Experiment'!BY9</f>
         <v>N</v>
       </c>
       <c r="BB9" t="s">
@@ -7539,7 +7546,7 @@
         <v>70</v>
       </c>
       <c r="T10" t="str">
-        <f>'During Experiment'!AF10</f>
+        <f>'During Experiment'!AG10</f>
         <v>J</v>
       </c>
       <c r="U10" t="s">
@@ -7549,7 +7556,7 @@
         <v>70</v>
       </c>
       <c r="W10" t="str">
-        <f>'During Experiment'!AJ10</f>
+        <f>'During Experiment'!AK10</f>
         <v>J</v>
       </c>
       <c r="X10" t="s">
@@ -7559,7 +7566,7 @@
         <v>70</v>
       </c>
       <c r="Z10" t="str">
-        <f>'During Experiment'!AN10</f>
+        <f>'During Experiment'!AO10</f>
         <v>N</v>
       </c>
       <c r="AA10" t="s">
@@ -7569,7 +7576,7 @@
         <v>70</v>
       </c>
       <c r="AC10" t="str">
-        <f>'During Experiment'!AR10</f>
+        <f>'During Experiment'!AS10</f>
         <v>J</v>
       </c>
       <c r="AD10" t="s">
@@ -7579,7 +7586,7 @@
         <v>70</v>
       </c>
       <c r="AF10" t="str">
-        <f>'During Experiment'!AV10</f>
+        <f>'During Experiment'!AW10</f>
         <v>N</v>
       </c>
       <c r="AG10" t="s">
@@ -7589,7 +7596,7 @@
         <v>70</v>
       </c>
       <c r="AI10" t="str">
-        <f>'During Experiment'!AZ10</f>
+        <f>'During Experiment'!BA10</f>
         <v>N</v>
       </c>
       <c r="AJ10" t="s">
@@ -7599,7 +7606,7 @@
         <v>70</v>
       </c>
       <c r="AL10" t="str">
-        <f>'During Experiment'!BD10</f>
+        <f>'During Experiment'!BE10</f>
         <v>N</v>
       </c>
       <c r="AM10" t="s">
@@ -7609,7 +7616,7 @@
         <v>70</v>
       </c>
       <c r="AO10" t="str">
-        <f>'During Experiment'!BH10</f>
+        <f>'During Experiment'!BI10</f>
         <v>N</v>
       </c>
       <c r="AP10" t="s">
@@ -7619,7 +7626,7 @@
         <v>70</v>
       </c>
       <c r="AR10" t="str">
-        <f>'During Experiment'!BL10</f>
+        <f>'During Experiment'!BM10</f>
         <v>J</v>
       </c>
       <c r="AS10" t="s">
@@ -7629,7 +7636,7 @@
         <v>70</v>
       </c>
       <c r="AU10" t="str">
-        <f>'During Experiment'!BP10</f>
+        <f>'During Experiment'!BQ10</f>
         <v>N</v>
       </c>
       <c r="AV10" t="s">
@@ -7639,7 +7646,7 @@
         <v>70</v>
       </c>
       <c r="AX10" t="str">
-        <f>'During Experiment'!BT10</f>
+        <f>'During Experiment'!BU10</f>
         <v>N</v>
       </c>
       <c r="AY10" t="s">
@@ -7649,7 +7656,7 @@
         <v>45</v>
       </c>
       <c r="BA10" t="str">
-        <f>'During Experiment'!BX10</f>
+        <f>'During Experiment'!BY10</f>
         <v>N</v>
       </c>
       <c r="BB10" t="s">
@@ -7724,7 +7731,7 @@
         <v>70</v>
       </c>
       <c r="T11" t="str">
-        <f>'During Experiment'!AF11</f>
+        <f>'During Experiment'!AG11</f>
         <v>N</v>
       </c>
       <c r="U11" t="s">
@@ -7734,7 +7741,7 @@
         <v>45</v>
       </c>
       <c r="W11" t="str">
-        <f>'During Experiment'!AJ11</f>
+        <f>'During Experiment'!AK11</f>
         <v>J</v>
       </c>
       <c r="X11" t="s">
@@ -7744,7 +7751,7 @@
         <v>70</v>
       </c>
       <c r="Z11" t="str">
-        <f>'During Experiment'!AN11</f>
+        <f>'During Experiment'!AO11</f>
         <v>J</v>
       </c>
       <c r="AA11" t="s">
@@ -7754,7 +7761,7 @@
         <v>45</v>
       </c>
       <c r="AC11" t="str">
-        <f>'During Experiment'!AR11</f>
+        <f>'During Experiment'!AS11</f>
         <v>J</v>
       </c>
       <c r="AD11" t="s">
@@ -7764,7 +7771,7 @@
         <v>45</v>
       </c>
       <c r="AF11" t="str">
-        <f>'During Experiment'!AV11</f>
+        <f>'During Experiment'!AW11</f>
         <v>N</v>
       </c>
       <c r="AG11" t="s">
@@ -7774,7 +7781,7 @@
         <v>70</v>
       </c>
       <c r="AI11" t="str">
-        <f>'During Experiment'!AZ11</f>
+        <f>'During Experiment'!BA11</f>
         <v>N</v>
       </c>
       <c r="AJ11" t="s">
@@ -7784,7 +7791,7 @@
         <v>70</v>
       </c>
       <c r="AL11" t="str">
-        <f>'During Experiment'!BD11</f>
+        <f>'During Experiment'!BE11</f>
         <v>N</v>
       </c>
       <c r="AM11" t="s">
@@ -7794,7 +7801,7 @@
         <v>45</v>
       </c>
       <c r="AO11" t="str">
-        <f>'During Experiment'!BH11</f>
+        <f>'During Experiment'!BI11</f>
         <v>N</v>
       </c>
       <c r="AP11" t="s">
@@ -7804,7 +7811,7 @@
         <v>45</v>
       </c>
       <c r="AR11" t="str">
-        <f>'During Experiment'!BL11</f>
+        <f>'During Experiment'!BM11</f>
         <v>N</v>
       </c>
       <c r="AS11" t="s">
@@ -7814,7 +7821,7 @@
         <v>45</v>
       </c>
       <c r="AU11" t="str">
-        <f>'During Experiment'!BP11</f>
+        <f>'During Experiment'!BQ11</f>
         <v>J</v>
       </c>
       <c r="AV11" t="s">
@@ -7824,7 +7831,7 @@
         <v>45</v>
       </c>
       <c r="AX11" t="str">
-        <f>'During Experiment'!BT11</f>
+        <f>'During Experiment'!BU11</f>
         <v>N</v>
       </c>
       <c r="AY11" t="s">
@@ -7834,7 +7841,7 @@
         <v>45</v>
       </c>
       <c r="BA11" t="str">
-        <f>'During Experiment'!BX11</f>
+        <f>'During Experiment'!BY11</f>
         <v>N</v>
       </c>
       <c r="BB11" t="s">
@@ -7909,7 +7916,7 @@
         <v>45</v>
       </c>
       <c r="T12" t="str">
-        <f>'During Experiment'!AF12</f>
+        <f>'During Experiment'!AG12</f>
         <v>N</v>
       </c>
       <c r="U12" t="s">
@@ -7919,7 +7926,7 @@
         <v>70</v>
       </c>
       <c r="W12" t="str">
-        <f>'During Experiment'!AJ12</f>
+        <f>'During Experiment'!AK12</f>
         <v>J</v>
       </c>
       <c r="X12" t="s">
@@ -7929,7 +7936,7 @@
         <v>45</v>
       </c>
       <c r="Z12" t="str">
-        <f>'During Experiment'!AN12</f>
+        <f>'During Experiment'!AO12</f>
         <v>N</v>
       </c>
       <c r="AA12" t="s">
@@ -7939,7 +7946,7 @@
         <v>45</v>
       </c>
       <c r="AC12" t="str">
-        <f>'During Experiment'!AR12</f>
+        <f>'During Experiment'!AS12</f>
         <v>N</v>
       </c>
       <c r="AD12" t="s">
@@ -7949,7 +7956,7 @@
         <v>45</v>
       </c>
       <c r="AF12" t="str">
-        <f>'During Experiment'!AV12</f>
+        <f>'During Experiment'!AW12</f>
         <v>J</v>
       </c>
       <c r="AG12" t="s">
@@ -7959,7 +7966,7 @@
         <v>45</v>
       </c>
       <c r="AI12" t="str">
-        <f>'During Experiment'!AZ12</f>
+        <f>'During Experiment'!BA12</f>
         <v>N</v>
       </c>
       <c r="AJ12" t="s">
@@ -7969,7 +7976,7 @@
         <v>45</v>
       </c>
       <c r="AL12" t="str">
-        <f>'During Experiment'!BD12</f>
+        <f>'During Experiment'!BE12</f>
         <v>J</v>
       </c>
       <c r="AM12" t="s">
@@ -7979,7 +7986,7 @@
         <v>45</v>
       </c>
       <c r="AO12" t="str">
-        <f>'During Experiment'!BH12</f>
+        <f>'During Experiment'!BI12</f>
         <v>N</v>
       </c>
       <c r="AP12" t="s">
@@ -7989,7 +7996,7 @@
         <v>45</v>
       </c>
       <c r="AR12" t="str">
-        <f>'During Experiment'!BL12</f>
+        <f>'During Experiment'!BM12</f>
         <v>N</v>
       </c>
       <c r="AS12" t="s">
@@ -7999,7 +8006,7 @@
         <v>70</v>
       </c>
       <c r="AU12" t="str">
-        <f>'During Experiment'!BP12</f>
+        <f>'During Experiment'!BQ12</f>
         <v>J</v>
       </c>
       <c r="AV12" t="s">
@@ -8009,7 +8016,7 @@
         <v>70</v>
       </c>
       <c r="AX12" t="str">
-        <f>'During Experiment'!BT12</f>
+        <f>'During Experiment'!BU12</f>
         <v>N</v>
       </c>
       <c r="AY12" t="s">
@@ -8019,7 +8026,7 @@
         <v>70</v>
       </c>
       <c r="BA12" t="str">
-        <f>'During Experiment'!BX12</f>
+        <f>'During Experiment'!BY12</f>
         <v>N</v>
       </c>
       <c r="BB12" t="s">
@@ -8094,7 +8101,7 @@
         <v>45</v>
       </c>
       <c r="T13" t="str">
-        <f>'During Experiment'!AF13</f>
+        <f>'During Experiment'!AG13</f>
         <v>J</v>
       </c>
       <c r="U13" t="s">
@@ -8104,7 +8111,7 @@
         <v>45</v>
       </c>
       <c r="W13" t="str">
-        <f>'During Experiment'!AJ13</f>
+        <f>'During Experiment'!AK13</f>
         <v>N</v>
       </c>
       <c r="X13" t="s">
@@ -8114,7 +8121,7 @@
         <v>45</v>
       </c>
       <c r="Z13" t="str">
-        <f>'During Experiment'!AN13</f>
+        <f>'During Experiment'!AO13</f>
         <v>J</v>
       </c>
       <c r="AA13" t="s">
@@ -8124,7 +8131,7 @@
         <v>45</v>
       </c>
       <c r="AC13" t="str">
-        <f>'During Experiment'!AR13</f>
+        <f>'During Experiment'!AS13</f>
         <v>N</v>
       </c>
       <c r="AD13" t="s">
@@ -8134,7 +8141,7 @@
         <v>45</v>
       </c>
       <c r="AF13" t="str">
-        <f>'During Experiment'!AV13</f>
+        <f>'During Experiment'!AW13</f>
         <v>N</v>
       </c>
       <c r="AG13" t="s">
@@ -8144,7 +8151,7 @@
         <v>45</v>
       </c>
       <c r="AI13" t="str">
-        <f>'During Experiment'!AZ13</f>
+        <f>'During Experiment'!BA13</f>
         <v>N</v>
       </c>
       <c r="AJ13" t="s">
@@ -8154,7 +8161,7 @@
         <v>45</v>
       </c>
       <c r="AL13" t="str">
-        <f>'During Experiment'!BD13</f>
+        <f>'During Experiment'!BE13</f>
         <v>N</v>
       </c>
       <c r="AM13" t="s">
@@ -8164,7 +8171,7 @@
         <v>45</v>
       </c>
       <c r="AO13" t="str">
-        <f>'During Experiment'!BH13</f>
+        <f>'During Experiment'!BI13</f>
         <v>N</v>
       </c>
       <c r="AP13" t="s">
@@ -8174,7 +8181,7 @@
         <v>45</v>
       </c>
       <c r="AR13" t="str">
-        <f>'During Experiment'!BL13</f>
+        <f>'During Experiment'!BM13</f>
         <v>J</v>
       </c>
       <c r="AS13" t="s">
@@ -8184,7 +8191,7 @@
         <v>45</v>
       </c>
       <c r="AU13" t="str">
-        <f>'During Experiment'!BP13</f>
+        <f>'During Experiment'!BQ13</f>
         <v>J</v>
       </c>
       <c r="AV13" t="s">
@@ -8194,7 +8201,7 @@
         <v>45</v>
       </c>
       <c r="AX13" t="str">
-        <f>'During Experiment'!BT13</f>
+        <f>'During Experiment'!BU13</f>
         <v>J</v>
       </c>
       <c r="AY13" t="s">
@@ -8204,7 +8211,7 @@
         <v>45</v>
       </c>
       <c r="BA13" t="str">
-        <f>'During Experiment'!BX13</f>
+        <f>'During Experiment'!BY13</f>
         <v>N</v>
       </c>
       <c r="BB13" t="s">
@@ -8279,7 +8286,7 @@
         <v>70</v>
       </c>
       <c r="T14" t="str">
-        <f>'During Experiment'!AF14</f>
+        <f>'During Experiment'!AG14</f>
         <v>N</v>
       </c>
       <c r="U14" t="s">
@@ -8289,7 +8296,7 @@
         <v>70</v>
       </c>
       <c r="W14" t="str">
-        <f>'During Experiment'!AJ14</f>
+        <f>'During Experiment'!AK14</f>
         <v>N</v>
       </c>
       <c r="X14" t="s">
@@ -8299,7 +8306,7 @@
         <v>45</v>
       </c>
       <c r="Z14" t="str">
-        <f>'During Experiment'!AN14</f>
+        <f>'During Experiment'!AO14</f>
         <v>N</v>
       </c>
       <c r="AA14" t="s">
@@ -8309,7 +8316,7 @@
         <v>70</v>
       </c>
       <c r="AC14" t="str">
-        <f>'During Experiment'!AR14</f>
+        <f>'During Experiment'!AS14</f>
         <v>N</v>
       </c>
       <c r="AD14" t="s">
@@ -8319,7 +8326,7 @@
         <v>70</v>
       </c>
       <c r="AF14" t="str">
-        <f>'During Experiment'!AV14</f>
+        <f>'During Experiment'!AW14</f>
         <v>N</v>
       </c>
       <c r="AG14" t="s">
@@ -8329,7 +8336,7 @@
         <v>45</v>
       </c>
       <c r="AI14" t="str">
-        <f>'During Experiment'!AZ14</f>
+        <f>'During Experiment'!BA14</f>
         <v>N</v>
       </c>
       <c r="AJ14" t="s">
@@ -8339,7 +8346,7 @@
         <v>70</v>
       </c>
       <c r="AL14" t="str">
-        <f>'During Experiment'!BD14</f>
+        <f>'During Experiment'!BE14</f>
         <v>N</v>
       </c>
       <c r="AM14" t="s">
@@ -8349,7 +8356,7 @@
         <v>70</v>
       </c>
       <c r="AO14" t="str">
-        <f>'During Experiment'!BH14</f>
+        <f>'During Experiment'!BI14</f>
         <v>N</v>
       </c>
       <c r="AP14" t="s">
@@ -8359,7 +8366,7 @@
         <v>45</v>
       </c>
       <c r="AR14" t="str">
-        <f>'During Experiment'!BL14</f>
+        <f>'During Experiment'!BM14</f>
         <v>N</v>
       </c>
       <c r="AS14" t="s">
@@ -8369,7 +8376,7 @@
         <v>45</v>
       </c>
       <c r="AU14" t="str">
-        <f>'During Experiment'!BP14</f>
+        <f>'During Experiment'!BQ14</f>
         <v>N</v>
       </c>
       <c r="AV14" t="s">
@@ -8379,7 +8386,7 @@
         <v>70</v>
       </c>
       <c r="AX14" t="str">
-        <f>'During Experiment'!BT14</f>
+        <f>'During Experiment'!BU14</f>
         <v>N</v>
       </c>
       <c r="AY14" t="s">
@@ -8389,7 +8396,7 @@
         <v>45</v>
       </c>
       <c r="BA14" t="str">
-        <f>'During Experiment'!BX14</f>
+        <f>'During Experiment'!BY14</f>
         <v>N</v>
       </c>
       <c r="BB14" t="s">
@@ -8464,7 +8471,7 @@
         <v>45</v>
       </c>
       <c r="T15" t="str">
-        <f>'During Experiment'!AF15</f>
+        <f>'During Experiment'!AG15</f>
         <v>N</v>
       </c>
       <c r="U15" t="s">
@@ -8474,7 +8481,7 @@
         <v>45</v>
       </c>
       <c r="W15" t="str">
-        <f>'During Experiment'!AJ15</f>
+        <f>'During Experiment'!AK15</f>
         <v>N</v>
       </c>
       <c r="X15" t="s">
@@ -8484,7 +8491,7 @@
         <v>45</v>
       </c>
       <c r="Z15" t="str">
-        <f>'During Experiment'!AN15</f>
+        <f>'During Experiment'!AO15</f>
         <v>N</v>
       </c>
       <c r="AA15" t="s">
@@ -8494,7 +8501,7 @@
         <v>45</v>
       </c>
       <c r="AC15" t="str">
-        <f>'During Experiment'!AR15</f>
+        <f>'During Experiment'!AS15</f>
         <v>N</v>
       </c>
       <c r="AD15" t="s">
@@ -8504,7 +8511,7 @@
         <v>45</v>
       </c>
       <c r="AF15" t="str">
-        <f>'During Experiment'!AV15</f>
+        <f>'During Experiment'!AW15</f>
         <v>N</v>
       </c>
       <c r="AG15" t="s">
@@ -8514,7 +8521,7 @@
         <v>45</v>
       </c>
       <c r="AI15" t="str">
-        <f>'During Experiment'!AZ15</f>
+        <f>'During Experiment'!BA15</f>
         <v>N</v>
       </c>
       <c r="AJ15" t="s">
@@ -8524,7 +8531,7 @@
         <v>45</v>
       </c>
       <c r="AL15" t="str">
-        <f>'During Experiment'!BD15</f>
+        <f>'During Experiment'!BE15</f>
         <v>N</v>
       </c>
       <c r="AM15" t="s">
@@ -8534,7 +8541,7 @@
         <v>45</v>
       </c>
       <c r="AO15" t="str">
-        <f>'During Experiment'!BH15</f>
+        <f>'During Experiment'!BI15</f>
         <v>N</v>
       </c>
       <c r="AP15" t="s">
@@ -8544,7 +8551,7 @@
         <v>45</v>
       </c>
       <c r="AR15" t="str">
-        <f>'During Experiment'!BL15</f>
+        <f>'During Experiment'!BM15</f>
         <v>N</v>
       </c>
       <c r="AS15" t="s">
@@ -8554,7 +8561,7 @@
         <v>45</v>
       </c>
       <c r="AU15" t="str">
-        <f>'During Experiment'!BP15</f>
+        <f>'During Experiment'!BQ15</f>
         <v>N</v>
       </c>
       <c r="AV15" t="s">
@@ -8564,7 +8571,7 @@
         <v>45</v>
       </c>
       <c r="AX15" t="str">
-        <f>'During Experiment'!BT15</f>
+        <f>'During Experiment'!BU15</f>
         <v>N</v>
       </c>
       <c r="AY15" t="s">
@@ -8574,7 +8581,7 @@
         <v>45</v>
       </c>
       <c r="BA15" t="str">
-        <f>'During Experiment'!BX15</f>
+        <f>'During Experiment'!BY15</f>
         <v>N</v>
       </c>
       <c r="BB15" t="s">

--- a/data/questionaire/Responses.xlsx
+++ b/data/questionaire/Responses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschu\Documents\GitHub\ET_course_project_gender-bias\data\questionaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C3B2E4-3602-4F6A-BB7B-A149A5C95AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9047D112-46FF-4C0B-BF2A-2D547CF00A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA0F6B31-0EC9-497B-B9A2-40478E56EC4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AA0F6B31-0EC9-497B-B9A2-40478E56EC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="During Experiment" sheetId="1" r:id="rId1"/>
@@ -349,9 +349,6 @@
     <t>kann man machen, für ihn wäre es kein problem wenns nicht gemacht wird</t>
   </si>
   <si>
-    <t>Links zur Mitte</t>
-  </si>
-  <si>
     <t>in der schule, vor ein paar jahren als es diskutiert wurde etwa abi zeit</t>
   </si>
   <si>
@@ -523,9 +520,6 @@
     <t>gut</t>
   </si>
   <si>
-    <t>Links</t>
-  </si>
-  <si>
     <t>in der 9. oder 10. klasse</t>
   </si>
   <si>
@@ -1213,9 +1207,6 @@
     <t>einerseits nicht so wichitg, aber es tut nicht weh also kann man es machen</t>
   </si>
   <si>
-    <t>Mitte</t>
-  </si>
-  <si>
     <t>so vor drei jahren</t>
   </si>
   <si>
@@ -1799,6 +1790,15 @@
   </si>
   <si>
     <t>6.Code</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Centre</t>
+  </si>
+  <si>
+    <t>Left of centre</t>
   </si>
 </sst>
 </file>
@@ -2271,10 +2271,10 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G1" t="s">
         <v>9</v>
@@ -2286,10 +2286,10 @@
         <v>49</v>
       </c>
       <c r="J1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="K1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
@@ -2301,10 +2301,10 @@
         <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="P1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Q1" t="s">
         <v>13</v>
@@ -2316,10 +2316,10 @@
         <v>51</v>
       </c>
       <c r="T1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="U1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="V1" t="s">
         <v>15</v>
@@ -2331,10 +2331,10 @@
         <v>52</v>
       </c>
       <c r="Y1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="Z1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AA1" t="s">
         <v>17</v>
@@ -2346,10 +2346,10 @@
         <v>59</v>
       </c>
       <c r="AD1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AE1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AF1" t="s">
         <v>19</v>
@@ -2361,7 +2361,7 @@
         <v>62</v>
       </c>
       <c r="AI1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AJ1" t="s">
         <v>21</v>
@@ -2373,7 +2373,7 @@
         <v>65</v>
       </c>
       <c r="AM1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AN1" t="s">
         <v>23</v>
@@ -2385,7 +2385,7 @@
         <v>68</v>
       </c>
       <c r="AQ1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AR1" t="s">
         <v>25</v>
@@ -2397,7 +2397,7 @@
         <v>72</v>
       </c>
       <c r="AU1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AV1" t="s">
         <v>27</v>
@@ -2409,7 +2409,7 @@
         <v>75</v>
       </c>
       <c r="AY1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AZ1" t="s">
         <v>29</v>
@@ -2421,7 +2421,7 @@
         <v>77</v>
       </c>
       <c r="BC1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="BD1" t="s">
         <v>31</v>
@@ -2433,7 +2433,7 @@
         <v>79</v>
       </c>
       <c r="BG1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="BH1" t="s">
         <v>33</v>
@@ -2445,7 +2445,7 @@
         <v>80</v>
       </c>
       <c r="BK1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="BL1" t="s">
         <v>35</v>
@@ -2457,7 +2457,7 @@
         <v>81</v>
       </c>
       <c r="BO1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="BP1" t="s">
         <v>37</v>
@@ -2469,7 +2469,7 @@
         <v>82</v>
       </c>
       <c r="BS1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="BT1" t="s">
         <v>39</v>
@@ -2481,7 +2481,7 @@
         <v>83</v>
       </c>
       <c r="BW1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="BX1" t="s">
         <v>41</v>
@@ -2493,7 +2493,7 @@
         <v>84</v>
       </c>
       <c r="CA1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:79" x14ac:dyDescent="0.25">
@@ -2510,10 +2510,10 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="G2" t="s">
         <v>44</v>
@@ -2525,10 +2525,10 @@
         <v>53</v>
       </c>
       <c r="J2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="K2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -2540,10 +2540,10 @@
         <v>54</v>
       </c>
       <c r="O2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="P2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Q2" t="s">
         <v>55</v>
@@ -2555,7 +2555,7 @@
         <v>56</v>
       </c>
       <c r="T2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="U2" t="s">
         <v>56</v>
@@ -2570,10 +2570,10 @@
         <v>58</v>
       </c>
       <c r="Y2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="Z2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AA2" t="s">
         <v>60</v>
@@ -2585,7 +2585,7 @@
         <v>61</v>
       </c>
       <c r="AE2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AF2" t="s">
         <v>63</v>
@@ -2597,7 +2597,7 @@
         <v>64</v>
       </c>
       <c r="AI2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AJ2" t="s">
         <v>66</v>
@@ -2609,7 +2609,7 @@
         <v>67</v>
       </c>
       <c r="AM2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AN2" t="s">
         <v>69</v>
@@ -2621,7 +2621,7 @@
         <v>71</v>
       </c>
       <c r="AQ2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AR2" t="s">
         <v>73</v>
@@ -2633,7 +2633,7 @@
         <v>74</v>
       </c>
       <c r="AU2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AV2" t="s">
         <v>76</v>
@@ -2645,7 +2645,7 @@
         <v>58</v>
       </c>
       <c r="AY2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AZ2" t="s">
         <v>78</v>
@@ -2657,7 +2657,7 @@
         <v>58</v>
       </c>
       <c r="BC2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BD2" t="s">
         <v>85</v>
@@ -2669,7 +2669,7 @@
         <v>86</v>
       </c>
       <c r="BG2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BH2" t="s">
         <v>87</v>
@@ -2681,7 +2681,7 @@
         <v>88</v>
       </c>
       <c r="BK2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="BL2" t="s">
         <v>89</v>
@@ -2705,7 +2705,7 @@
         <v>92</v>
       </c>
       <c r="BS2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="BT2" t="s">
         <v>93</v>
@@ -2729,7 +2729,7 @@
         <v>74</v>
       </c>
       <c r="CA2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:79" x14ac:dyDescent="0.25">
@@ -2737,52 +2737,52 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G3" t="s">
         <v>107</v>
       </c>
-      <c r="E3" t="s">
-        <v>576</v>
-      </c>
-      <c r="F3" t="s">
-        <v>461</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s">
+        <v>574</v>
+      </c>
+      <c r="K3" t="s">
+        <v>299</v>
+      </c>
+      <c r="L3" t="s">
         <v>108</v>
       </c>
-      <c r="H3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s">
-        <v>577</v>
-      </c>
-      <c r="K3" t="s">
-        <v>301</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" t="s">
+        <v>574</v>
+      </c>
+      <c r="P3" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q3" t="s">
         <v>109</v>
-      </c>
-      <c r="M3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" t="s">
-        <v>577</v>
-      </c>
-      <c r="P3" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>110</v>
       </c>
       <c r="R3" t="s">
         <v>70</v>
@@ -2791,136 +2791,136 @@
         <v>64</v>
       </c>
       <c r="T3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="U3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="V3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>572</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA3" t="s">
         <v>111</v>
       </c>
-      <c r="W3" t="s">
-        <v>70</v>
-      </c>
-      <c r="X3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>575</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC3" t="s">
         <v>112</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>113</v>
       </c>
       <c r="AE3" t="s">
         <v>56</v>
       </c>
       <c r="AF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>459</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>114</v>
       </c>
-      <c r="AG3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AK3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>326</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>442</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>460</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>461</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC3" t="s">
         <v>462</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>328</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>445</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU3" t="s">
+      <c r="BD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG3" t="s">
         <v>463</v>
       </c>
-      <c r="AV3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BH3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK3" t="s">
         <v>464</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>70</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>465</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>466</v>
-      </c>
-      <c r="BH3" t="s">
+      <c r="BL3" t="s">
         <v>122</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>467</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>123</v>
       </c>
       <c r="BM3" t="s">
         <v>45</v>
@@ -2929,43 +2929,43 @@
         <v>64</v>
       </c>
       <c r="BO3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="BP3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>466</v>
+      </c>
+      <c r="BT3" t="s">
         <v>124</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>469</v>
-      </c>
-      <c r="BT3" t="s">
+      <c r="BU3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>229</v>
+      </c>
+      <c r="BX3" t="s">
         <v>125</v>
       </c>
-      <c r="BU3" t="s">
-        <v>70</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>231</v>
-      </c>
-      <c r="BX3" t="s">
+      <c r="BY3" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ3" t="s">
         <v>126</v>
       </c>
-      <c r="BY3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>127</v>
-      </c>
       <c r="CA3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:79" x14ac:dyDescent="0.25">
@@ -2973,22 +2973,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>574</v>
+      </c>
+      <c r="F4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G4" t="s">
         <v>129</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>577</v>
-      </c>
-      <c r="F4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G4" t="s">
-        <v>130</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -2997,28 +2997,28 @@
         <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" t="s">
+        <v>572</v>
+      </c>
+      <c r="P4" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q4" t="s">
         <v>131</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" t="s">
-        <v>575</v>
-      </c>
-      <c r="P4" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>132</v>
       </c>
       <c r="R4" t="s">
         <v>45</v>
@@ -3027,52 +3027,52 @@
         <v>64</v>
       </c>
       <c r="T4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="U4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="V4" t="s">
+        <v>132</v>
+      </c>
+      <c r="W4" t="s">
+        <v>70</v>
+      </c>
+      <c r="X4" t="s">
         <v>133</v>
       </c>
-      <c r="W4" t="s">
-        <v>70</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
+        <v>572</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA4" t="s">
         <v>134</v>
       </c>
-      <c r="Y4" t="s">
-        <v>575</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>470</v>
-      </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC4" t="s">
         <v>135</v>
       </c>
-      <c r="AB4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF4" t="s">
         <v>136</v>
       </c>
-      <c r="AE4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH4" t="s">
         <v>137</v>
       </c>
-      <c r="AG4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>138</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>139</v>
       </c>
       <c r="AK4" t="s">
         <v>45</v>
@@ -3084,19 +3084,19 @@
         <v>94</v>
       </c>
       <c r="AN4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP4" t="s">
         <v>140</v>
       </c>
-      <c r="AO4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
+        <v>468</v>
+      </c>
+      <c r="AR4" t="s">
         <v>141</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>471</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>142</v>
       </c>
       <c r="AS4" t="s">
         <v>45</v>
@@ -3105,22 +3105,22 @@
         <v>94</v>
       </c>
       <c r="AU4" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AV4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX4" t="s">
         <v>143</v>
       </c>
-      <c r="AW4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
+        <v>470</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>144</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>473</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>145</v>
       </c>
       <c r="BA4" t="s">
         <v>45</v>
@@ -3129,10 +3129,10 @@
         <v>58</v>
       </c>
       <c r="BC4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="BD4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BE4" t="s">
         <v>45</v>
@@ -3141,34 +3141,34 @@
         <v>58</v>
       </c>
       <c r="BG4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="BH4" t="s">
+        <v>146</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ4" t="s">
         <v>147</v>
       </c>
-      <c r="BI4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
+        <v>472</v>
+      </c>
+      <c r="BL4" t="s">
         <v>148</v>
       </c>
-      <c r="BK4" t="s">
-        <v>475</v>
-      </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN4" t="s">
         <v>149</v>
       </c>
-      <c r="BM4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
+        <v>473</v>
+      </c>
+      <c r="BP4" t="s">
         <v>150</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>476</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>151</v>
       </c>
       <c r="BQ4" t="s">
         <v>70</v>
@@ -3177,31 +3177,31 @@
         <v>58</v>
       </c>
       <c r="BS4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="BT4" t="s">
+        <v>151</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV4" t="s">
         <v>152</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>153</v>
       </c>
       <c r="BW4" t="s">
         <v>61</v>
       </c>
       <c r="BX4" t="s">
+        <v>153</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ4" t="s">
         <v>154</v>
       </c>
-      <c r="BY4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>155</v>
-      </c>
       <c r="CA4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:79" x14ac:dyDescent="0.25">
@@ -3209,7 +3209,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
         <v>70</v>
@@ -3218,13 +3218,13 @@
         <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F5" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="G5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -3233,13 +3233,13 @@
         <v>74</v>
       </c>
       <c r="J5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K5" t="s">
         <v>94</v>
       </c>
       <c r="L5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M5" t="s">
         <v>45</v>
@@ -3248,13 +3248,13 @@
         <v>64</v>
       </c>
       <c r="O5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R5" t="s">
         <v>45</v>
@@ -3263,13 +3263,13 @@
         <v>58</v>
       </c>
       <c r="T5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="U5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="V5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W5" t="s">
         <v>45</v>
@@ -3278,13 +3278,13 @@
         <v>58</v>
       </c>
       <c r="Y5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="Z5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AA5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AB5" t="s">
         <v>45</v>
@@ -3293,10 +3293,10 @@
         <v>58</v>
       </c>
       <c r="AE5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AF5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG5" t="s">
         <v>45</v>
@@ -3305,10 +3305,10 @@
         <v>74</v>
       </c>
       <c r="AI5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AJ5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AK5" t="s">
         <v>45</v>
@@ -3317,22 +3317,22 @@
         <v>58</v>
       </c>
       <c r="AM5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AN5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>442</v>
+      </c>
+      <c r="AR5" t="s">
         <v>171</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>172</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>445</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>173</v>
       </c>
       <c r="AS5" t="s">
         <v>45</v>
@@ -3341,46 +3341,46 @@
         <v>64</v>
       </c>
       <c r="AU5" t="s">
+        <v>478</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>479</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>175</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>480</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>176</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG5" t="s">
         <v>481</v>
       </c>
-      <c r="AV5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>175</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>482</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>176</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>70</v>
-      </c>
-      <c r="BB5" t="s">
+      <c r="BH5" t="s">
         <v>177</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>483</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>178</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>484</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>179</v>
       </c>
       <c r="BI5" t="s">
         <v>45</v>
@@ -3392,43 +3392,43 @@
         <v>67</v>
       </c>
       <c r="BL5" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>445</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>179</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>482</v>
+      </c>
+      <c r="BT5" t="s">
         <v>180</v>
       </c>
-      <c r="BM5" t="s">
-        <v>70</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>74</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>448</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>181</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>74</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>485</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>182</v>
-      </c>
       <c r="BU5" t="s">
         <v>45</v>
       </c>
       <c r="BV5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="BW5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="BX5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BY5" t="s">
         <v>45</v>
@@ -3437,7 +3437,7 @@
         <v>74</v>
       </c>
       <c r="CA5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:79" x14ac:dyDescent="0.25">
@@ -3445,202 +3445,202 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>573</v>
+      </c>
+      <c r="F6" t="s">
+        <v>469</v>
+      </c>
+      <c r="G6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s">
+        <v>576</v>
+      </c>
+      <c r="K6" t="s">
+        <v>485</v>
+      </c>
+      <c r="L6" t="s">
         <v>183</v>
       </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>576</v>
-      </c>
-      <c r="F6" t="s">
-        <v>472</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" t="s">
+        <v>573</v>
+      </c>
+      <c r="P6" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q6" t="s">
         <v>184</v>
       </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s">
-        <v>579</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
+        <v>74</v>
+      </c>
+      <c r="T6" t="s">
+        <v>575</v>
+      </c>
+      <c r="U6" t="s">
+        <v>484</v>
+      </c>
+      <c r="V6" t="s">
+        <v>185</v>
+      </c>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>577</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>487</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI6" t="s">
         <v>488</v>
       </c>
-      <c r="L6" t="s">
-        <v>185</v>
-      </c>
-      <c r="M6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" t="s">
-        <v>74</v>
-      </c>
-      <c r="O6" t="s">
-        <v>576</v>
-      </c>
-      <c r="P6" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>186</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="s">
-        <v>74</v>
-      </c>
-      <c r="T6" t="s">
-        <v>578</v>
-      </c>
-      <c r="U6" t="s">
-        <v>487</v>
-      </c>
-      <c r="V6" t="s">
-        <v>187</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>580</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>490</v>
-      </c>
-      <c r="AA6" t="s">
+      <c r="AJ6" t="s">
         <v>188</v>
       </c>
-      <c r="AB6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AF6" t="s">
+      <c r="AK6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN6" t="s">
         <v>189</v>
       </c>
-      <c r="AG6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>491</v>
-      </c>
-      <c r="AJ6" t="s">
+      <c r="AO6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>147</v>
+      </c>
+      <c r="AR6" t="s">
         <v>190</v>
       </c>
-      <c r="AK6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN6" t="s">
+      <c r="AS6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>316</v>
+      </c>
+      <c r="AV6" t="s">
         <v>191</v>
       </c>
-      <c r="AO6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>192</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>172</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>318</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>193</v>
-      </c>
       <c r="AW6" t="s">
         <v>45</v>
       </c>
       <c r="AX6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AY6" t="s">
         <v>86</v>
       </c>
       <c r="AZ6" t="s">
+        <v>192</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>481</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>193</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF6" t="s">
         <v>194</v>
       </c>
-      <c r="BA6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>484</v>
-      </c>
-      <c r="BD6" t="s">
+      <c r="BG6" t="s">
+        <v>489</v>
+      </c>
+      <c r="BH6" t="s">
         <v>195</v>
       </c>
-      <c r="BE6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF6" t="s">
+      <c r="BI6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ6" t="s">
         <v>196</v>
       </c>
-      <c r="BG6" t="s">
-        <v>492</v>
-      </c>
-      <c r="BH6" t="s">
+      <c r="BK6" t="s">
+        <v>481</v>
+      </c>
+      <c r="BL6" t="s">
         <v>197</v>
       </c>
-      <c r="BI6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ6" t="s">
+      <c r="BM6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN6" t="s">
         <v>198</v>
       </c>
-      <c r="BK6" t="s">
-        <v>484</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>199</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>200</v>
-      </c>
       <c r="BO6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="BP6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BQ6" t="s">
         <v>45</v>
@@ -3649,28 +3649,28 @@
         <v>90</v>
       </c>
       <c r="BS6" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="BT6" t="s">
+        <v>199</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>200</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>152</v>
+      </c>
+      <c r="BX6" t="s">
         <v>201</v>
       </c>
-      <c r="BU6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BV6" t="s">
+      <c r="BY6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>202</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>153</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>203</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>204</v>
       </c>
       <c r="CA6" t="s">
         <v>88</v>
@@ -3681,166 +3681,166 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>576</v>
+      </c>
+      <c r="F7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J7" t="s">
+        <v>577</v>
+      </c>
+      <c r="K7" t="s">
+        <v>493</v>
+      </c>
+      <c r="L7" t="s">
         <v>205</v>
       </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>579</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7" t="s">
+        <v>572</v>
+      </c>
+      <c r="P7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>208</v>
+      </c>
+      <c r="R7" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" t="s">
+        <v>106</v>
+      </c>
+      <c r="T7" t="s">
+        <v>572</v>
+      </c>
+      <c r="U7" t="s">
+        <v>494</v>
+      </c>
+      <c r="V7" t="s">
+        <v>209</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>575</v>
+      </c>
+      <c r="Z7" t="s">
         <v>495</v>
       </c>
-      <c r="G7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="s">
-        <v>204</v>
-      </c>
-      <c r="J7" t="s">
-        <v>580</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="AA7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE7" t="s">
         <v>496</v>
       </c>
-      <c r="L7" t="s">
-        <v>207</v>
-      </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" t="s">
-        <v>209</v>
-      </c>
-      <c r="O7" t="s">
-        <v>575</v>
-      </c>
-      <c r="P7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>210</v>
-      </c>
-      <c r="R7" t="s">
-        <v>45</v>
-      </c>
-      <c r="S7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T7" t="s">
-        <v>575</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="AF7" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>215</v>
+      </c>
+      <c r="AM7" t="s">
         <v>497</v>
       </c>
-      <c r="V7" t="s">
-        <v>211</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>578</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AN7" t="s">
+        <v>216</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>486</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>218</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>219</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>437</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>220</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY7" t="s">
         <v>498</v>
       </c>
-      <c r="AA7" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>499</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>214</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>216</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>217</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>218</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>219</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>489</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>220</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT7" t="s">
+      <c r="AZ7" t="s">
         <v>221</v>
       </c>
-      <c r="AU7" t="s">
-        <v>440</v>
-      </c>
-      <c r="AV7" t="s">
+      <c r="BA7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB7" t="s">
         <v>222</v>
       </c>
-      <c r="AW7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>501</v>
-      </c>
-      <c r="AZ7" t="s">
+      <c r="BC7" t="s">
+        <v>222</v>
+      </c>
+      <c r="BD7" t="s">
         <v>223</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>224</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>225</v>
       </c>
       <c r="BE7" t="s">
         <v>45</v>
@@ -3852,7 +3852,7 @@
         <v>67</v>
       </c>
       <c r="BH7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BI7" t="s">
         <v>45</v>
@@ -3861,22 +3861,22 @@
         <v>54</v>
       </c>
       <c r="BK7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="BL7" t="s">
+        <v>225</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>226</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>499</v>
+      </c>
+      <c r="BP7" t="s">
         <v>227</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>228</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>502</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>229</v>
       </c>
       <c r="BQ7" t="s">
         <v>45</v>
@@ -3888,19 +3888,19 @@
         <v>71</v>
       </c>
       <c r="BT7" t="s">
+        <v>228</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>229</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>500</v>
+      </c>
+      <c r="BX7" t="s">
         <v>230</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>45</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>231</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>503</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>232</v>
       </c>
       <c r="BY7" t="s">
         <v>45</v>
@@ -3909,7 +3909,7 @@
         <v>54</v>
       </c>
       <c r="CA7" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:79" x14ac:dyDescent="0.25">
@@ -3917,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -3926,110 +3926,110 @@
         <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
       </c>
       <c r="G8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>574</v>
+      </c>
+      <c r="K8" t="s">
+        <v>444</v>
+      </c>
+      <c r="L8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O8" t="s">
+        <v>573</v>
+      </c>
+      <c r="P8" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q8" t="s">
         <v>243</v>
       </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s">
-        <v>577</v>
-      </c>
-      <c r="K8" t="s">
-        <v>447</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="R8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" t="s">
+        <v>575</v>
+      </c>
+      <c r="U8" t="s">
+        <v>475</v>
+      </c>
+      <c r="V8" t="s">
         <v>244</v>
       </c>
-      <c r="M8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" t="s">
-        <v>576</v>
-      </c>
-      <c r="P8" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="W8" t="s">
+        <v>45</v>
+      </c>
+      <c r="X8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>573</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>439</v>
+      </c>
+      <c r="AA8" t="s">
         <v>245</v>
       </c>
-      <c r="R8" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" t="s">
-        <v>74</v>
-      </c>
-      <c r="T8" t="s">
-        <v>578</v>
-      </c>
-      <c r="U8" t="s">
-        <v>478</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="AB8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>143</v>
+      </c>
+      <c r="AF8" t="s">
         <v>246</v>
       </c>
-      <c r="W8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>576</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>442</v>
-      </c>
-      <c r="AA8" t="s">
+      <c r="AG8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>247</v>
       </c>
-      <c r="AB8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AK8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>501</v>
+      </c>
+      <c r="AN8" t="s">
         <v>248</v>
       </c>
-      <c r="AG8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>504</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>250</v>
-      </c>
       <c r="AO8" t="s">
         <v>45</v>
       </c>
@@ -4037,70 +4037,70 @@
         <v>74</v>
       </c>
       <c r="AQ8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AR8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AS8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AT8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AU8" t="s">
         <v>94</v>
       </c>
       <c r="AV8" t="s">
+        <v>249</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>250</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>287</v>
+      </c>
+      <c r="BD8" t="s">
         <v>251</v>
       </c>
-      <c r="AW8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>434</v>
-      </c>
-      <c r="AZ8" t="s">
+      <c r="BE8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>303</v>
+      </c>
+      <c r="BH8" t="s">
         <v>252</v>
       </c>
-      <c r="BA8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>289</v>
-      </c>
-      <c r="BD8" t="s">
+      <c r="BI8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ8" t="s">
         <v>253</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>305</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>254</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>255</v>
       </c>
       <c r="BK8" t="s">
         <v>90</v>
       </c>
       <c r="BL8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="BM8" t="s">
         <v>45</v>
@@ -4109,35 +4109,35 @@
         <v>53</v>
       </c>
       <c r="BO8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="BP8" t="s">
+        <v>255</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>256</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>311</v>
+      </c>
+      <c r="BT8" t="s">
         <v>257</v>
       </c>
-      <c r="BQ8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR8" t="s">
+      <c r="BU8" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV8" t="s">
         <v>258</v>
       </c>
-      <c r="BS8" t="s">
-        <v>313</v>
-      </c>
-      <c r="BT8" t="s">
+      <c r="BW8" t="s">
+        <v>437</v>
+      </c>
+      <c r="BX8" t="s">
         <v>259</v>
       </c>
-      <c r="BU8" t="s">
-        <v>45</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>260</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>440</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>261</v>
-      </c>
       <c r="BY8" t="s">
         <v>45</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>74</v>
       </c>
       <c r="CA8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:79" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C9" t="s">
         <v>70</v>
@@ -4162,28 +4162,28 @@
         <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
       </c>
       <c r="G9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J9" t="s">
+        <v>573</v>
+      </c>
+      <c r="K9" t="s">
+        <v>458</v>
+      </c>
+      <c r="L9" t="s">
         <v>266</v>
-      </c>
-      <c r="H9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" t="s">
-        <v>267</v>
-      </c>
-      <c r="J9" t="s">
-        <v>576</v>
-      </c>
-      <c r="K9" t="s">
-        <v>461</v>
-      </c>
-      <c r="L9" t="s">
-        <v>268</v>
       </c>
       <c r="M9" t="s">
         <v>45</v>
@@ -4192,13 +4192,13 @@
         <v>64</v>
       </c>
       <c r="O9" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="P9" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="Q9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="R9" t="s">
         <v>70</v>
@@ -4207,28 +4207,28 @@
         <v>64</v>
       </c>
       <c r="T9" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="U9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="V9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="W9" t="s">
         <v>45</v>
       </c>
       <c r="X9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y9" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="Z9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AA9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AB9" t="s">
         <v>70</v>
@@ -4237,10 +4237,10 @@
         <v>58</v>
       </c>
       <c r="AE9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AF9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG9" t="s">
         <v>45</v>
@@ -4249,10 +4249,10 @@
         <v>58</v>
       </c>
       <c r="AI9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AJ9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AK9" t="s">
         <v>70</v>
@@ -4261,22 +4261,22 @@
         <v>64</v>
       </c>
       <c r="AM9" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AN9" t="s">
+        <v>272</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>273</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>460</v>
+      </c>
+      <c r="AR9" t="s">
         <v>274</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>275</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>463</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>276</v>
       </c>
       <c r="AS9" t="s">
         <v>70</v>
@@ -4285,10 +4285,10 @@
         <v>64</v>
       </c>
       <c r="AU9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AV9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AW9" t="s">
         <v>70</v>
@@ -4297,91 +4297,91 @@
         <v>58</v>
       </c>
       <c r="AY9" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>276</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>277</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>461</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>279</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>463</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>280</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>281</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>281</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>282</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>229</v>
+      </c>
+      <c r="BO9" t="s">
         <v>462</v>
       </c>
-      <c r="AZ9" t="s">
-        <v>278</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>279</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>464</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>280</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>281</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>466</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>282</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ9" t="s">
+      <c r="BP9" t="s">
         <v>283</v>
       </c>
-      <c r="BK9" t="s">
-        <v>283</v>
-      </c>
-      <c r="BL9" t="s">
+      <c r="BQ9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>326</v>
+      </c>
+      <c r="BT9" t="s">
         <v>284</v>
       </c>
-      <c r="BM9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>231</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>465</v>
-      </c>
-      <c r="BP9" t="s">
+      <c r="BU9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV9" t="s">
         <v>285</v>
       </c>
-      <c r="BQ9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>175</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>328</v>
-      </c>
-      <c r="BT9" t="s">
+      <c r="BW9" t="s">
+        <v>442</v>
+      </c>
+      <c r="BX9" t="s">
         <v>286</v>
       </c>
-      <c r="BU9" t="s">
-        <v>70</v>
-      </c>
-      <c r="BV9" t="s">
+      <c r="BY9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ9" t="s">
         <v>287</v>
       </c>
-      <c r="BW9" t="s">
-        <v>445</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>288</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>45</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>289</v>
-      </c>
       <c r="CA9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:79" x14ac:dyDescent="0.25">
@@ -4389,22 +4389,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" t="s">
+        <v>572</v>
+      </c>
+      <c r="F10" t="s">
+        <v>467</v>
+      </c>
+      <c r="G10" t="s">
         <v>293</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>294</v>
-      </c>
-      <c r="E10" t="s">
-        <v>575</v>
-      </c>
-      <c r="F10" t="s">
-        <v>470</v>
-      </c>
-      <c r="G10" t="s">
-        <v>295</v>
       </c>
       <c r="H10" t="s">
         <v>70</v>
@@ -4413,70 +4413,70 @@
         <v>56</v>
       </c>
       <c r="J10" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L10" t="s">
+        <v>294</v>
+      </c>
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O10" t="s">
+        <v>577</v>
+      </c>
+      <c r="P10" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q10" t="s">
         <v>296</v>
       </c>
-      <c r="M10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" t="s">
-        <v>297</v>
-      </c>
-      <c r="O10" t="s">
-        <v>580</v>
-      </c>
-      <c r="P10" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>298</v>
-      </c>
       <c r="R10" t="s">
         <v>45</v>
       </c>
       <c r="S10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="T10" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="U10" t="s">
         <v>94</v>
       </c>
       <c r="V10" t="s">
+        <v>297</v>
+      </c>
+      <c r="W10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>575</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>473</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>298</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC10" t="s">
         <v>299</v>
       </c>
-      <c r="W10" t="s">
-        <v>70</v>
-      </c>
-      <c r="X10" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>578</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>476</v>
-      </c>
-      <c r="AA10" t="s">
+      <c r="AE10" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF10" t="s">
         <v>300</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>301</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>301</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>302</v>
       </c>
       <c r="AG10" t="s">
         <v>70</v>
@@ -4485,46 +4485,46 @@
         <v>71</v>
       </c>
       <c r="AI10" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AJ10" t="s">
+        <v>301</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP10" t="s">
         <v>303</v>
       </c>
-      <c r="AK10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>136</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN10" t="s">
+      <c r="AQ10" t="s">
+        <v>229</v>
+      </c>
+      <c r="AR10" t="s">
         <v>304</v>
       </c>
-      <c r="AO10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP10" t="s">
+      <c r="AS10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>140</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>468</v>
+      </c>
+      <c r="AV10" t="s">
         <v>305</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>231</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>306</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>141</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>471</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>307</v>
       </c>
       <c r="AW10" t="s">
         <v>45</v>
@@ -4533,58 +4533,58 @@
         <v>58</v>
       </c>
       <c r="AY10" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AZ10" t="s">
+        <v>306</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>154</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>475</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>307</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>287</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>469</v>
+      </c>
+      <c r="BH10" t="s">
         <v>308</v>
       </c>
-      <c r="BA10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>478</v>
-      </c>
-      <c r="BD10" t="s">
+      <c r="BI10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ10" t="s">
         <v>309</v>
       </c>
-      <c r="BE10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>289</v>
-      </c>
-      <c r="BG10" t="s">
+      <c r="BK10" t="s">
+        <v>309</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>310</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>311</v>
+      </c>
+      <c r="BO10" t="s">
         <v>472</v>
       </c>
-      <c r="BH10" t="s">
-        <v>310</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>311</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>311</v>
-      </c>
-      <c r="BL10" t="s">
+      <c r="BP10" t="s">
         <v>312</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>70</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>313</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>475</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>314</v>
       </c>
       <c r="BQ10" t="s">
         <v>45</v>
@@ -4596,28 +4596,28 @@
         <v>61</v>
       </c>
       <c r="BT10" t="s">
+        <v>313</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>314</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>471</v>
+      </c>
+      <c r="BX10" t="s">
         <v>315</v>
       </c>
-      <c r="BU10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BV10" t="s">
+      <c r="BY10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BZ10" t="s">
         <v>316</v>
       </c>
-      <c r="BW10" t="s">
-        <v>474</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>317</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>45</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>318</v>
-      </c>
       <c r="CA10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11" spans="1:79" x14ac:dyDescent="0.25">
@@ -4625,7 +4625,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
@@ -4634,73 +4634,73 @@
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F11" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G11" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" t="s">
+        <v>575</v>
+      </c>
+      <c r="K11" t="s">
+        <v>480</v>
+      </c>
+      <c r="L11" t="s">
+        <v>319</v>
+      </c>
+      <c r="M11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" t="s">
+        <v>574</v>
+      </c>
+      <c r="P11" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q11" t="s">
         <v>320</v>
       </c>
-      <c r="H11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J11" t="s">
-        <v>578</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="R11" t="s">
+        <v>70</v>
+      </c>
+      <c r="S11" t="s">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s">
+        <v>572</v>
+      </c>
+      <c r="U11" t="s">
+        <v>217</v>
+      </c>
+      <c r="V11" t="s">
+        <v>321</v>
+      </c>
+      <c r="W11" t="s">
+        <v>45</v>
+      </c>
+      <c r="X11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>573</v>
+      </c>
+      <c r="Z11" t="s">
         <v>483</v>
       </c>
-      <c r="L11" t="s">
-        <v>321</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11" t="s">
-        <v>74</v>
-      </c>
-      <c r="O11" t="s">
-        <v>577</v>
-      </c>
-      <c r="P11" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="AA11" t="s">
         <v>322</v>
-      </c>
-      <c r="R11" t="s">
-        <v>70</v>
-      </c>
-      <c r="S11" t="s">
-        <v>74</v>
-      </c>
-      <c r="T11" t="s">
-        <v>575</v>
-      </c>
-      <c r="U11" t="s">
-        <v>219</v>
-      </c>
-      <c r="V11" t="s">
-        <v>323</v>
-      </c>
-      <c r="W11" t="s">
-        <v>45</v>
-      </c>
-      <c r="X11" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>576</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>486</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>324</v>
       </c>
       <c r="AB11" t="s">
         <v>45</v>
@@ -4709,148 +4709,148 @@
         <v>58</v>
       </c>
       <c r="AE11" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AF11" t="s">
+        <v>323</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>324</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>279</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>325</v>
       </c>
-      <c r="AG11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="AK11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL11" t="s">
         <v>326</v>
       </c>
-      <c r="AI11" t="s">
-        <v>281</v>
-      </c>
-      <c r="AJ11" t="s">
+      <c r="AM11" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN11" t="s">
         <v>327</v>
       </c>
-      <c r="AK11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL11" t="s">
+      <c r="AO11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>442</v>
+      </c>
+      <c r="AR11" t="s">
         <v>328</v>
       </c>
-      <c r="AM11" t="s">
-        <v>482</v>
-      </c>
-      <c r="AN11" t="s">
+      <c r="AS11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>478</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX11" t="s">
         <v>329</v>
       </c>
-      <c r="AO11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>208</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>445</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>330</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>213</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>481</v>
-      </c>
-      <c r="AV11" t="s">
+      <c r="AY11" t="s">
+        <v>329</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>331</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>215</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>215</v>
+      </c>
+      <c r="BD11" t="s">
         <v>332</v>
       </c>
-      <c r="AW11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>331</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>331</v>
-      </c>
-      <c r="AZ11" t="s">
+      <c r="BE11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF11" t="s">
         <v>333</v>
       </c>
-      <c r="BA11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>217</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>217</v>
-      </c>
-      <c r="BD11" t="s">
+      <c r="BG11" t="s">
+        <v>265</v>
+      </c>
+      <c r="BH11" t="s">
         <v>334</v>
       </c>
-      <c r="BE11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF11" t="s">
+      <c r="BI11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ11" t="s">
         <v>335</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>267</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>336</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>337</v>
       </c>
       <c r="BK11" t="s">
         <v>94</v>
       </c>
       <c r="BL11" t="s">
+        <v>336</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>258</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>309</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>337</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>476</v>
+      </c>
+      <c r="BT11" t="s">
         <v>338</v>
       </c>
-      <c r="BM11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>260</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>311</v>
-      </c>
-      <c r="BP11" t="s">
+      <c r="BU11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>477</v>
+      </c>
+      <c r="BX11" t="s">
         <v>339</v>
       </c>
-      <c r="BQ11" t="s">
-        <v>70</v>
-      </c>
-      <c r="BR11" t="s">
-        <v>74</v>
-      </c>
-      <c r="BS11" t="s">
-        <v>479</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>340</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>74</v>
-      </c>
-      <c r="BW11" t="s">
-        <v>480</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>341</v>
-      </c>
       <c r="BY11" t="s">
         <v>45</v>
       </c>
       <c r="BZ11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="CA11" t="s">
         <v>67</v>
@@ -4861,7 +4861,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
@@ -4870,13 +4870,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F12" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -4885,13 +4885,13 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M12" t="s">
         <v>45</v>
@@ -4900,13 +4900,13 @@
         <v>92</v>
       </c>
       <c r="O12" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="P12" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="R12" t="s">
         <v>45</v>
@@ -4915,40 +4915,40 @@
         <v>64</v>
       </c>
       <c r="T12" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="U12" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="V12" t="s">
+        <v>346</v>
+      </c>
+      <c r="W12" t="s">
+        <v>45</v>
+      </c>
+      <c r="X12" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>576</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>485</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>347</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>287</v>
+      </c>
+      <c r="AF12" t="s">
         <v>348</v>
-      </c>
-      <c r="W12" t="s">
-        <v>45</v>
-      </c>
-      <c r="X12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>579</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>488</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>349</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>289</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>350</v>
       </c>
       <c r="AG12" t="s">
         <v>45</v>
@@ -4957,94 +4957,94 @@
         <v>58</v>
       </c>
       <c r="AI12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AJ12" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>350</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN12" t="s">
         <v>351</v>
       </c>
-      <c r="AK12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL12" t="s">
+      <c r="AO12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>194</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>489</v>
+      </c>
+      <c r="AR12" t="s">
         <v>352</v>
       </c>
-      <c r="AM12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AN12" t="s">
+      <c r="AS12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>484</v>
+      </c>
+      <c r="AV12" t="s">
         <v>353</v>
       </c>
-      <c r="AO12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>196</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>492</v>
-      </c>
-      <c r="AR12" t="s">
+      <c r="AW12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ12" t="s">
         <v>354</v>
       </c>
-      <c r="AS12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>487</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>356</v>
-      </c>
       <c r="BA12" t="s">
         <v>45</v>
       </c>
       <c r="BB12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="BC12" t="s">
         <v>86</v>
       </c>
       <c r="BD12" t="s">
+        <v>355</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>487</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>356</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>147</v>
+      </c>
+      <c r="BL12" t="s">
         <v>357</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>490</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>358</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>359</v>
       </c>
       <c r="BM12" t="s">
         <v>45</v>
@@ -5053,10 +5053,10 @@
         <v>90</v>
       </c>
       <c r="BO12" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="BP12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="BQ12" t="s">
         <v>70</v>
@@ -5065,10 +5065,10 @@
         <v>64</v>
       </c>
       <c r="BS12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BT12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="BU12" t="s">
         <v>45</v>
@@ -5080,16 +5080,16 @@
         <v>88</v>
       </c>
       <c r="BX12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="BY12" t="s">
         <v>45</v>
       </c>
       <c r="BZ12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="CA12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:79" x14ac:dyDescent="0.25">
@@ -5097,166 +5097,166 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>577</v>
+      </c>
+      <c r="F13" t="s">
+        <v>493</v>
+      </c>
+      <c r="G13" t="s">
+        <v>369</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s">
+        <v>574</v>
+      </c>
+      <c r="K13" t="s">
+        <v>498</v>
+      </c>
+      <c r="L13" t="s">
         <v>370</v>
       </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>580</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13" t="s">
+        <v>573</v>
+      </c>
+      <c r="P13" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>371</v>
+      </c>
+      <c r="R13" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T13" t="s">
+        <v>573</v>
+      </c>
+      <c r="U13" t="s">
+        <v>469</v>
+      </c>
+      <c r="V13" t="s">
+        <v>372</v>
+      </c>
+      <c r="W13" t="s">
+        <v>45</v>
+      </c>
+      <c r="X13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>576</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>500</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>494</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>492</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>495</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>376</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>437</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>377</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>303</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>378</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>207</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>379</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC13" t="s">
         <v>496</v>
       </c>
-      <c r="G13" t="s">
-        <v>371</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" t="s">
-        <v>577</v>
-      </c>
-      <c r="K13" t="s">
-        <v>501</v>
-      </c>
-      <c r="L13" t="s">
-        <v>372</v>
-      </c>
-      <c r="M13" t="s">
-        <v>70</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" t="s">
-        <v>576</v>
-      </c>
-      <c r="P13" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>373</v>
-      </c>
-      <c r="R13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" t="s">
-        <v>74</v>
-      </c>
-      <c r="T13" t="s">
-        <v>576</v>
-      </c>
-      <c r="U13" t="s">
-        <v>472</v>
-      </c>
-      <c r="V13" t="s">
-        <v>374</v>
-      </c>
-      <c r="W13" t="s">
-        <v>45</v>
-      </c>
-      <c r="X13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>579</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>503</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>497</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>376</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>495</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>377</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>498</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>378</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>440</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>379</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>305</v>
-      </c>
-      <c r="AV13" t="s">
+      <c r="BD13" t="s">
         <v>380</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>209</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>381</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>499</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>382</v>
       </c>
       <c r="BE13" t="s">
         <v>45</v>
@@ -5268,43 +5268,43 @@
         <v>71</v>
       </c>
       <c r="BH13" t="s">
+        <v>381</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>497</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>382</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>222</v>
+      </c>
+      <c r="BP13" t="s">
         <v>383</v>
       </c>
-      <c r="BI13" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>500</v>
-      </c>
-      <c r="BL13" t="s">
+      <c r="BQ13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>499</v>
+      </c>
+      <c r="BT13" t="s">
         <v>384</v>
-      </c>
-      <c r="BM13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BN13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BO13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>385</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BS13" t="s">
-        <v>502</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>386</v>
       </c>
       <c r="BU13" t="s">
         <v>70</v>
@@ -5316,7 +5316,7 @@
         <v>67</v>
       </c>
       <c r="BX13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BY13" t="s">
         <v>45</v>
@@ -5325,7 +5325,7 @@
         <v>74</v>
       </c>
       <c r="CA13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:79" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -5342,13 +5342,13 @@
         <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G14" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -5357,13 +5357,13 @@
         <v>74</v>
       </c>
       <c r="J14" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="K14" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L14" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M14" t="s">
         <v>70</v>
@@ -5372,13 +5372,13 @@
         <v>61</v>
       </c>
       <c r="O14" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="P14" t="s">
         <v>61</v>
       </c>
       <c r="Q14" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="R14" t="s">
         <v>45</v>
@@ -5387,13 +5387,13 @@
         <v>74</v>
       </c>
       <c r="T14" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="U14" t="s">
         <v>94</v>
       </c>
       <c r="V14" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="W14" t="s">
         <v>45</v>
@@ -5402,13 +5402,13 @@
         <v>74</v>
       </c>
       <c r="Y14" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="Z14" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AA14" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AB14" t="s">
         <v>45</v>
@@ -5417,34 +5417,34 @@
         <v>64</v>
       </c>
       <c r="AE14" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AF14" t="s">
+        <v>398</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>400</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>229</v>
+      </c>
+      <c r="AN14" t="s">
         <v>401</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>402</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>470</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>403</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>231</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>404</v>
       </c>
       <c r="AO14" t="s">
         <v>45</v>
@@ -5453,10 +5453,10 @@
         <v>58</v>
       </c>
       <c r="AQ14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AR14" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AS14" t="s">
         <v>45</v>
@@ -5465,10 +5465,10 @@
         <v>58</v>
       </c>
       <c r="AU14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AV14" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AW14" t="s">
         <v>45</v>
@@ -5477,10 +5477,10 @@
         <v>74</v>
       </c>
       <c r="AY14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AZ14" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="BA14" t="s">
         <v>45</v>
@@ -5489,10 +5489,10 @@
         <v>64</v>
       </c>
       <c r="BC14" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="BD14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="BE14" t="s">
         <v>45</v>
@@ -5501,10 +5501,10 @@
         <v>64</v>
       </c>
       <c r="BG14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="BH14" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="BI14" t="s">
         <v>45</v>
@@ -5513,10 +5513,10 @@
         <v>74</v>
       </c>
       <c r="BK14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BL14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="BM14" t="s">
         <v>45</v>
@@ -5525,10 +5525,10 @@
         <v>74</v>
       </c>
       <c r="BO14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BP14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="BQ14" t="s">
         <v>45</v>
@@ -5537,31 +5537,31 @@
         <v>64</v>
       </c>
       <c r="BS14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BT14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="BU14" t="s">
         <v>45</v>
       </c>
       <c r="BV14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="BW14" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="BX14" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="BY14" t="s">
         <v>45</v>
       </c>
       <c r="BZ14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="CA14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:79" x14ac:dyDescent="0.25">
@@ -5569,7 +5569,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C15" t="s">
         <v>70</v>
@@ -5578,13 +5578,13 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -5593,166 +5593,166 @@
         <v>64</v>
       </c>
       <c r="J15" t="s">
+        <v>572</v>
+      </c>
+      <c r="K15" t="s">
+        <v>431</v>
+      </c>
+      <c r="L15" t="s">
+        <v>414</v>
+      </c>
+      <c r="M15" t="s">
+        <v>45</v>
+      </c>
+      <c r="N15" t="s">
+        <v>74</v>
+      </c>
+      <c r="O15" t="s">
         <v>575</v>
       </c>
-      <c r="K15" t="s">
-        <v>434</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>415</v>
+      </c>
+      <c r="R15" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" t="s">
+        <v>74</v>
+      </c>
+      <c r="T15" t="s">
+        <v>572</v>
+      </c>
+      <c r="U15" t="s">
+        <v>311</v>
+      </c>
+      <c r="V15" t="s">
+        <v>416</v>
+      </c>
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>573</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>455</v>
+      </c>
+      <c r="AA15" t="s">
         <v>417</v>
       </c>
-      <c r="M15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N15" t="s">
-        <v>74</v>
-      </c>
-      <c r="O15" t="s">
-        <v>578</v>
-      </c>
-      <c r="P15" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="AB15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF15" t="s">
         <v>418</v>
       </c>
-      <c r="R15" t="s">
-        <v>45</v>
-      </c>
-      <c r="S15" t="s">
-        <v>74</v>
-      </c>
-      <c r="T15" t="s">
-        <v>575</v>
-      </c>
-      <c r="U15" t="s">
-        <v>313</v>
-      </c>
-      <c r="V15" t="s">
+      <c r="AG15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>452</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>419</v>
       </c>
-      <c r="W15" t="s">
-        <v>45</v>
-      </c>
-      <c r="X15" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>576</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA15" t="s">
+      <c r="AK15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>399</v>
+      </c>
+      <c r="AN15" t="s">
         <v>420</v>
       </c>
-      <c r="AB15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF15" t="s">
+      <c r="AO15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>439</v>
+      </c>
+      <c r="AR15" t="s">
         <v>421</v>
       </c>
-      <c r="AG15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>455</v>
-      </c>
-      <c r="AJ15" t="s">
+      <c r="AS15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>448</v>
+      </c>
+      <c r="AV15" t="s">
         <v>422</v>
       </c>
-      <c r="AK15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>402</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>423</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>442</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>424</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>451</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>425</v>
-      </c>
       <c r="AW15" t="s">
         <v>45</v>
       </c>
       <c r="AX15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AY15" t="s">
         <v>90</v>
       </c>
       <c r="AZ15" t="s">
+        <v>423</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>475</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>424</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>287</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>425</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>429</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL15" t="s">
         <v>426</v>
-      </c>
-      <c r="BA15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>478</v>
-      </c>
-      <c r="BD15" t="s">
-        <v>427</v>
-      </c>
-      <c r="BE15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>74</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>289</v>
-      </c>
-      <c r="BH15" t="s">
-        <v>428</v>
-      </c>
-      <c r="BI15" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ15" t="s">
-        <v>432</v>
-      </c>
-      <c r="BK15" t="s">
-        <v>155</v>
-      </c>
-      <c r="BL15" t="s">
-        <v>429</v>
       </c>
       <c r="BM15" t="s">
         <v>45</v>
@@ -5764,7 +5764,7 @@
         <v>56</v>
       </c>
       <c r="BP15" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="BQ15" t="s">
         <v>45</v>
@@ -5773,10 +5773,10 @@
         <v>74</v>
       </c>
       <c r="BS15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="BT15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="BU15" t="s">
         <v>45</v>
@@ -5785,10 +5785,10 @@
         <v>74</v>
       </c>
       <c r="BW15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BX15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="BY15" t="s">
         <v>45</v>
@@ -5839,166 +5839,166 @@
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G1" t="s">
+        <v>503</v>
+      </c>
+      <c r="H1" t="s">
+        <v>555</v>
+      </c>
+      <c r="I1" t="s">
+        <v>506</v>
+      </c>
+      <c r="J1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K1" t="s">
         <v>556</v>
       </c>
-      <c r="C1" t="s">
-        <v>505</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="L1" t="s">
+        <v>508</v>
+      </c>
+      <c r="M1" t="s">
+        <v>507</v>
+      </c>
+      <c r="N1" t="s">
+        <v>557</v>
+      </c>
+      <c r="O1" t="s">
+        <v>511</v>
+      </c>
+      <c r="P1" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>558</v>
+      </c>
+      <c r="R1" t="s">
+        <v>512</v>
+      </c>
+      <c r="S1" t="s">
         <v>513</v>
       </c>
-      <c r="E1" t="s">
-        <v>557</v>
-      </c>
-      <c r="F1" t="s">
-        <v>507</v>
-      </c>
-      <c r="G1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H1" t="s">
-        <v>558</v>
-      </c>
-      <c r="I1" t="s">
-        <v>509</v>
-      </c>
-      <c r="J1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="T1" t="s">
         <v>559</v>
       </c>
-      <c r="L1" t="s">
-        <v>511</v>
-      </c>
-      <c r="M1" t="s">
-        <v>510</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
+        <v>514</v>
+      </c>
+      <c r="V1" t="s">
+        <v>515</v>
+      </c>
+      <c r="W1" t="s">
         <v>560</v>
       </c>
-      <c r="O1" t="s">
-        <v>514</v>
-      </c>
-      <c r="P1" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z1" t="s">
         <v>561</v>
       </c>
-      <c r="R1" t="s">
-        <v>515</v>
-      </c>
-      <c r="S1" t="s">
-        <v>516</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>519</v>
+      </c>
+      <c r="AC1" t="s">
         <v>562</v>
       </c>
-      <c r="U1" t="s">
-        <v>517</v>
-      </c>
-      <c r="V1" t="s">
-        <v>518</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="AD1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>521</v>
+      </c>
+      <c r="AF1" t="s">
         <v>563</v>
       </c>
-      <c r="X1" t="s">
-        <v>519</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>520</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="AG1" t="s">
+        <v>522</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AI1" t="s">
         <v>564</v>
       </c>
-      <c r="AA1" t="s">
-        <v>521</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>522</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AJ1" t="s">
+        <v>524</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>525</v>
+      </c>
+      <c r="AL1" t="s">
         <v>565</v>
       </c>
-      <c r="AD1" t="s">
-        <v>523</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>524</v>
-      </c>
-      <c r="AF1" t="s">
+      <c r="AM1" t="s">
+        <v>526</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>527</v>
+      </c>
+      <c r="AO1" t="s">
         <v>566</v>
       </c>
-      <c r="AG1" t="s">
-        <v>525</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>526</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AP1" t="s">
+        <v>528</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AR1" t="s">
         <v>567</v>
       </c>
-      <c r="AJ1" t="s">
-        <v>527</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>528</v>
-      </c>
-      <c r="AL1" t="s">
+      <c r="AS1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>531</v>
+      </c>
+      <c r="AU1" t="s">
         <v>568</v>
       </c>
-      <c r="AM1" t="s">
-        <v>529</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>530</v>
-      </c>
-      <c r="AO1" t="s">
+      <c r="AV1" t="s">
+        <v>532</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>533</v>
+      </c>
+      <c r="AX1" t="s">
         <v>569</v>
       </c>
-      <c r="AP1" t="s">
-        <v>531</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>532</v>
-      </c>
-      <c r="AR1" t="s">
+      <c r="AY1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>535</v>
+      </c>
+      <c r="BA1" t="s">
         <v>570</v>
       </c>
-      <c r="AS1" t="s">
-        <v>533</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>534</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>571</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>535</v>
-      </c>
-      <c r="AW1" t="s">
+      <c r="BB1" t="s">
         <v>536</v>
       </c>
-      <c r="AX1" t="s">
-        <v>572</v>
-      </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>537</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>538</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>573</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>539</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
@@ -6060,7 +6060,7 @@
         <v>N</v>
       </c>
       <c r="R2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="S2" t="s">
         <v>70</v>
@@ -6080,7 +6080,7 @@
         <v>N</v>
       </c>
       <c r="X2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Y2" t="s">
         <v>70</v>
@@ -6365,7 +6365,7 @@
         <v>N</v>
       </c>
       <c r="BB3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="BC3" t="s">
         <v>45</v>
@@ -6510,7 +6510,7 @@
         <v>N</v>
       </c>
       <c r="AP4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AQ4" t="s">
         <v>70</v>
@@ -6540,7 +6540,7 @@
         <v>N</v>
       </c>
       <c r="AY4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AZ4" t="s">
         <v>70</v>
@@ -6645,7 +6645,7 @@
         <v>N</v>
       </c>
       <c r="AA5" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AB5" t="s">
         <v>45</v>
@@ -6665,7 +6665,7 @@
         <v>N</v>
       </c>
       <c r="AG5" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AH5" t="s">
         <v>45</v>
@@ -6900,7 +6900,7 @@
         <v>N</v>
       </c>
       <c r="AV6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AW6" t="s">
         <v>70</v>
@@ -6910,7 +6910,7 @@
         <v>J</v>
       </c>
       <c r="AY6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AZ6" t="s">
         <v>45</v>
@@ -7035,7 +7035,7 @@
         <v>J</v>
       </c>
       <c r="AG7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AH7" t="s">
         <v>45</v>
@@ -7105,7 +7105,7 @@
         <v>N</v>
       </c>
       <c r="BB7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="BC7" t="s">
         <v>45</v>
@@ -7270,7 +7270,7 @@
         <v>N</v>
       </c>
       <c r="AV8" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AW8" t="s">
         <v>45</v>
@@ -7280,7 +7280,7 @@
         <v>N</v>
       </c>
       <c r="AY8" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AZ8" t="s">
         <v>45</v>
@@ -7315,7 +7315,7 @@
         <v>J</v>
       </c>
       <c r="F9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G9" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>N</v>
       </c>
       <c r="AA9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AB9" t="s">
         <v>70</v>
@@ -7425,7 +7425,7 @@
         <v>J</v>
       </c>
       <c r="AM9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AN9" t="s">
         <v>70</v>
@@ -7455,7 +7455,7 @@
         <v>N</v>
       </c>
       <c r="AV9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AW9" t="s">
         <v>45</v>
@@ -7490,7 +7490,7 @@
         <v>N</v>
       </c>
       <c r="C10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D10" t="s">
         <v>70</v>
@@ -7500,7 +7500,7 @@
         <v>J</v>
       </c>
       <c r="F10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G10" t="s">
         <v>70</v>
@@ -7520,7 +7520,7 @@
         <v>N</v>
       </c>
       <c r="L10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="M10" t="s">
         <v>70</v>
@@ -7550,7 +7550,7 @@
         <v>J</v>
       </c>
       <c r="U10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="V10" t="s">
         <v>70</v>
@@ -7570,7 +7570,7 @@
         <v>N</v>
       </c>
       <c r="AA10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AB10" t="s">
         <v>70</v>
@@ -7610,7 +7610,7 @@
         <v>N</v>
       </c>
       <c r="AM10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AN10" t="s">
         <v>70</v>
@@ -7715,7 +7715,7 @@
         <v>N</v>
       </c>
       <c r="O11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="P11" t="s">
         <v>70</v>
@@ -8000,7 +8000,7 @@
         <v>N</v>
       </c>
       <c r="AS12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AT12" t="s">
         <v>70</v>
@@ -8030,7 +8030,7 @@
         <v>N</v>
       </c>
       <c r="BB12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="BC12" t="s">
         <v>45</v>
@@ -8290,7 +8290,7 @@
         <v>N</v>
       </c>
       <c r="U14" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="V14" t="s">
         <v>70</v>
@@ -8390,7 +8390,7 @@
         <v>N</v>
       </c>
       <c r="AY14" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AZ14" t="s">
         <v>45</v>
@@ -8593,38 +8593,38 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C20" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C21" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F21" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H21" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C22" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F22" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -8669,16 +8669,16 @@
         <v>96</v>
       </c>
       <c r="H1" t="s">
+        <v>549</v>
+      </c>
+      <c r="I1" t="s">
+        <v>550</v>
+      </c>
+      <c r="J1" t="s">
+        <v>551</v>
+      </c>
+      <c r="K1" t="s">
         <v>552</v>
-      </c>
-      <c r="I1" t="s">
-        <v>553</v>
-      </c>
-      <c r="J1" t="s">
-        <v>554</v>
-      </c>
-      <c r="K1" t="s">
-        <v>555</v>
       </c>
       <c r="L1" t="s">
         <v>97</v>
@@ -8728,10 +8728,10 @@
         <v>101</v>
       </c>
       <c r="M2" t="s">
+        <v>585</v>
+      </c>
+      <c r="N2" t="s">
         <v>102</v>
-      </c>
-      <c r="N2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -8754,7 +8754,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -8769,13 +8769,13 @@
         <v>3</v>
       </c>
       <c r="L3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" t="s">
+        <v>585</v>
+      </c>
+      <c r="N3" t="s">
         <v>105</v>
-      </c>
-      <c r="M3" t="s">
-        <v>102</v>
-      </c>
-      <c r="N3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -8798,7 +8798,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -8813,13 +8813,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M4" t="s">
+        <v>585</v>
+      </c>
+      <c r="N4" t="s">
         <v>156</v>
-      </c>
-      <c r="M4" t="s">
-        <v>102</v>
-      </c>
-      <c r="N4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -8842,7 +8842,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -8857,13 +8857,13 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" t="s">
+        <v>583</v>
+      </c>
+      <c r="N5" t="s">
         <v>159</v>
-      </c>
-      <c r="M5" t="s">
-        <v>160</v>
-      </c>
-      <c r="N5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -8886,7 +8886,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -8901,13 +8901,13 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M6" t="s">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="N6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -8930,7 +8930,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -8945,13 +8945,13 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M7" t="s">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="N7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -8971,10 +8971,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -8989,13 +8989,13 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M8" t="s">
-        <v>160</v>
+        <v>583</v>
       </c>
       <c r="N8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -9015,10 +9015,10 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -9033,13 +9033,13 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M9" t="s">
-        <v>160</v>
+        <v>583</v>
       </c>
       <c r="N9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -9062,7 +9062,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -9077,13 +9077,13 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M10" t="s">
-        <v>160</v>
+        <v>583</v>
       </c>
       <c r="N10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -9106,7 +9106,7 @@
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -9121,13 +9121,13 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M11" t="s">
-        <v>160</v>
+        <v>583</v>
       </c>
       <c r="N11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -9150,7 +9150,7 @@
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -9165,13 +9165,13 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M12" t="s">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="N12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -9191,10 +9191,10 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -9209,13 +9209,13 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M13" t="s">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="N13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -9235,10 +9235,10 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -9253,13 +9253,13 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M14" t="s">
-        <v>390</v>
+        <v>584</v>
       </c>
       <c r="N14" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -9282,7 +9282,7 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -9297,13 +9297,13 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M15" t="s">
-        <v>102</v>
+        <v>585</v>
       </c>
       <c r="N15" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
